--- a/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
@@ -25,18 +25,12 @@
     <sheet name="Kashmore_Exp" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Kashmore_Vul" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="Kashmore_Dmg" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Naushahro Feroze_Exp" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="Naushahro Feroze_Vul" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="Naushahro Feroze_Dmg" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Qambar Shahdadkot_Exp" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="Qambar Shahdadkot_Vul" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="Qambar Shahdadkot_Dmg" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Shaheed Benazirabad_Exp" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="Shaheed Benazirabad_Vul" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Shaheed Benazirabad_Dmg" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="Shikarpur_Exp" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="Shikarpur_Vul" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="Shikarpur_Dmg" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="Qambar Shahdadkot_Exp" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Qambar Shahdadkot_Vul" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Qambar Shahdadkot_Dmg" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Shikarpur_Exp" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Shikarpur_Vul" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Shikarpur_Dmg" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -9772,7 +9766,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Exp</t>
+          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -9843,37 +9837,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>2522.97</v>
+        <v>34980.66</v>
       </c>
       <c r="C4" t="n">
-        <v>556416</v>
+        <v>5947704</v>
       </c>
       <c r="D4" t="n">
-        <v>437184</v>
+        <v>4673196</v>
       </c>
       <c r="E4" t="n">
-        <v>140400</v>
+        <v>1478700</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>6210</v>
+        <v>100230</v>
       </c>
       <c r="H4" t="n">
-        <v>210</v>
+        <v>10110</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>18870</v>
+        <v>230460</v>
       </c>
     </row>
     <row r="5">
@@ -9881,37 +9875,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3818.97</v>
+        <v>41602.59</v>
       </c>
       <c r="C5" t="n">
-        <v>641088</v>
+        <v>5687136</v>
       </c>
       <c r="D5" t="n">
-        <v>503712</v>
+        <v>4468464</v>
       </c>
       <c r="E5" t="n">
-        <v>105300</v>
+        <v>1096200</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>9090</v>
+        <v>99990</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>12960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>21300</v>
+        <v>265500</v>
       </c>
     </row>
     <row r="6">
@@ -9919,37 +9913,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3829.95</v>
+        <v>29693.97</v>
       </c>
       <c r="C6" t="n">
-        <v>395136</v>
+        <v>2344104</v>
       </c>
       <c r="D6" t="n">
-        <v>310464</v>
+        <v>1841796</v>
       </c>
       <c r="E6" t="n">
-        <v>62100</v>
+        <v>238500</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>7710</v>
+        <v>62220</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>5220</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>21210</v>
+        <v>124020</v>
       </c>
     </row>
     <row r="7">
@@ -9957,37 +9951,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2491.2</v>
+        <v>21279.42</v>
       </c>
       <c r="C7" t="n">
-        <v>185472</v>
+        <v>1401624</v>
       </c>
       <c r="D7" t="n">
-        <v>145728</v>
+        <v>1101276</v>
       </c>
       <c r="E7" t="n">
-        <v>31500</v>
+        <v>100800</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>4770</v>
+        <v>39660</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>780</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8580</v>
+        <v>69480</v>
       </c>
     </row>
     <row r="8">
@@ -9995,37 +9989,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1287.72</v>
+        <v>8452.799999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>55944</v>
+        <v>608832</v>
       </c>
       <c r="D8" t="n">
-        <v>43956</v>
+        <v>478368</v>
       </c>
       <c r="E8" t="n">
-        <v>5400</v>
+        <v>22500</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1530</v>
+        <v>10890</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>3540</v>
+        <v>32610</v>
       </c>
     </row>
     <row r="9">
@@ -10033,22 +10027,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>628.74</v>
+        <v>690.48</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="n">
-        <v>13860</v>
+        <v>62568</v>
       </c>
       <c r="E9" t="n">
-        <v>7200</v>
+        <v>1800</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>840</v>
+        <v>1980</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -10063,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>840</v>
+        <v>8430</v>
       </c>
     </row>
     <row r="10">
@@ -10071,13 +10065,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>385.47</v>
+        <v>227.25</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>16128</v>
       </c>
       <c r="D10" t="n">
-        <v>1584</v>
+        <v>12672</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -10086,7 +10080,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>660</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -10101,7 +10095,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>540</v>
+        <v>3720</v>
       </c>
     </row>
     <row r="11">
@@ -10109,13 +10103,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>216</v>
+        <v>208.71</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>3528</v>
       </c>
       <c r="D11" t="n">
-        <v>2376</v>
+        <v>2772</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -10124,10 +10118,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -10139,7 +10133,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="12">
@@ -10147,22 +10141,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.05</v>
+        <v>39.6</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>3024</v>
       </c>
       <c r="D12" t="n">
-        <v>792</v>
+        <v>2376</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -10177,7 +10171,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="13">
@@ -10185,13 +10179,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>169.29</v>
+        <v>16.38</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -10215,7 +10209,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14">
@@ -10223,22 +10217,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.93</v>
+        <v>16.47</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>396</v>
+        <v>1188</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -10253,7 +10247,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -10261,13 +10255,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>7.92</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1188</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -10276,7 +10270,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -10291,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16">
@@ -10299,13 +10293,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>4.32</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -10314,7 +10308,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -10329,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17">
@@ -10337,13 +10331,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0.54</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -10352,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -10367,7 +10361,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18">
@@ -10375,13 +10369,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -10390,7 +10384,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3660</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -10405,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19">
@@ -10413,13 +10407,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -10428,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -10454,10 +10448,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -10530,10 +10524,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -10568,10 +10562,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -10606,10 +10600,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -11636,7 +11630,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Vul</t>
+          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -11745,37 +11739,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1718.54</v>
+        <v>18721.17</v>
       </c>
       <c r="C5" t="n">
-        <v>352598.4</v>
+        <v>3127924.8</v>
       </c>
       <c r="D5" t="n">
-        <v>166728.67</v>
+        <v>1479061.58</v>
       </c>
       <c r="E5" t="n">
-        <v>11614.59</v>
+        <v>120910.86</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>4665.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4473</v>
+        <v>55755</v>
       </c>
     </row>
     <row r="6">
@@ -11783,37 +11777,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>3063.96</v>
+        <v>23755.18</v>
       </c>
       <c r="C6" t="n">
-        <v>355622.4</v>
+        <v>2109693.6</v>
       </c>
       <c r="D6" t="n">
-        <v>157405.25</v>
+        <v>933790.5699999999</v>
       </c>
       <c r="E6" t="n">
-        <v>10494.9</v>
+        <v>40306.5</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>385.5</v>
+        <v>3111</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2975.4</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7847.7</v>
+        <v>45887.4</v>
       </c>
     </row>
     <row r="7">
@@ -11821,37 +11815,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>2366.64</v>
+        <v>20215.45</v>
       </c>
       <c r="C7" t="n">
-        <v>185472</v>
+        <v>1401624</v>
       </c>
       <c r="D7" t="n">
-        <v>92974.46000000001</v>
+        <v>702614.09</v>
       </c>
       <c r="E7" t="n">
-        <v>6700.05</v>
+        <v>21440.16</v>
       </c>
       <c r="F7" t="n">
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>715.5</v>
+        <v>5949</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>569.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5148</v>
+        <v>41688</v>
       </c>
     </row>
     <row r="8">
@@ -11859,37 +11853,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>1287.72</v>
+        <v>8452.799999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>55944</v>
+        <v>608832</v>
       </c>
       <c r="D8" t="n">
-        <v>32351.62</v>
+        <v>352078.85</v>
       </c>
       <c r="E8" t="n">
-        <v>1324.62</v>
+        <v>5519.25</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>994.5</v>
+        <v>7078.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2513.4</v>
+        <v>23153.1</v>
       </c>
     </row>
     <row r="9">
@@ -11897,22 +11891,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>628.74</v>
+        <v>690.48</v>
       </c>
       <c r="C9" t="n">
-        <v>17640</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="n">
-        <v>11129.58</v>
+        <v>50242.1</v>
       </c>
       <c r="E9" t="n">
-        <v>1927.44</v>
+        <v>481.86</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>714</v>
+        <v>1683</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -11927,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>680.4</v>
+        <v>6828.3</v>
       </c>
     </row>
     <row r="10">
@@ -11935,13 +11929,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>385.47</v>
+        <v>227.25</v>
       </c>
       <c r="C10" t="n">
-        <v>2016</v>
+        <v>16128</v>
       </c>
       <c r="D10" t="n">
-        <v>1378.08</v>
+        <v>11024.64</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -11950,7 +11944,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>390</v>
+        <v>660</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -11965,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>480.6</v>
+        <v>3310.8</v>
       </c>
     </row>
     <row r="11">
@@ -11973,13 +11967,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>216</v>
+        <v>208.71</v>
       </c>
       <c r="C11" t="n">
-        <v>3024</v>
+        <v>3528</v>
       </c>
       <c r="D11" t="n">
-        <v>2134.84</v>
+        <v>2490.64</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -11988,10 +11982,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12003,7 +11997,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>300</v>
+        <v>3540</v>
       </c>
     </row>
     <row r="12">
@@ -12011,22 +12005,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>157.05</v>
+        <v>39.6</v>
       </c>
       <c r="C12" t="n">
-        <v>1008</v>
+        <v>3024</v>
       </c>
       <c r="D12" t="n">
-        <v>734.1799999999999</v>
+        <v>2202.55</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>430.2</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12041,7 +12035,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>90</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="13">
@@ -12049,13 +12043,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>169.29</v>
+        <v>16.38</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1128.01</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12079,7 +12073,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>150</v>
+        <v>450</v>
       </c>
     </row>
     <row r="14">
@@ -12087,22 +12081,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>42.93</v>
+        <v>16.47</v>
       </c>
       <c r="C14" t="n">
-        <v>504</v>
+        <v>1512</v>
       </c>
       <c r="D14" t="n">
-        <v>384.91</v>
+        <v>1154.74</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>512.37</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -12117,7 +12111,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>540</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15">
@@ -12125,13 +12119,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>4.32</v>
+        <v>7.92</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1512</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1171.37</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -12140,7 +12134,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -12155,7 +12149,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16">
@@ -12163,13 +12157,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>0.99</v>
+        <v>4.32</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -12178,7 +12172,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -12193,7 +12187,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="17">
@@ -12201,13 +12195,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>1.26</v>
+        <v>0.54</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -12216,7 +12210,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -12231,7 +12225,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
     </row>
     <row r="18">
@@ -12239,13 +12233,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>3528</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>2772</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -12254,7 +12248,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3660</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -12269,7 +12263,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19">
@@ -12277,13 +12271,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -12292,7 +12286,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -12318,10 +12312,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -12394,10 +12388,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1008</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>792</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -12432,10 +12426,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>504</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -12470,10 +12464,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>3024</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2376</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -12568,7 +12562,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Naushahro Feroze | Mode: Dmg</t>
+          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -12677,37 +12671,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3780780.3</v>
+        <v>41186564.1</v>
       </c>
       <c r="C5" t="n">
-        <v>19392912</v>
+        <v>172035864</v>
       </c>
       <c r="D5" t="n">
-        <v>16894616.33</v>
+        <v>149873310.31</v>
       </c>
       <c r="E5" t="n">
-        <v>2139872.06</v>
+        <v>22276616.85</v>
       </c>
       <c r="F5" t="n">
-        <v>4166.7</v>
+        <v>8333.4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1290738.24</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>122499.3</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>42135.66</v>
+        <v>525212.1</v>
       </c>
     </row>
     <row r="6">
@@ -12715,37 +12709,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>6740712</v>
+        <v>52261387.2</v>
       </c>
       <c r="C6" t="n">
-        <v>19559232</v>
+        <v>116033148</v>
       </c>
       <c r="D6" t="n">
-        <v>15949873.78</v>
+        <v>94620998.66</v>
       </c>
       <c r="E6" t="n">
-        <v>1933580.38</v>
+        <v>7426069.56</v>
       </c>
       <c r="F6" t="n">
-        <v>16666.8</v>
+        <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>7131.75</v>
+        <v>57553.5</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>823144.41</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>87499.5</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>73925.33</v>
+        <v>432259.31</v>
       </c>
     </row>
     <row r="7">
@@ -12753,37 +12747,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>5206608</v>
+        <v>44473987.8</v>
       </c>
       <c r="C7" t="n">
-        <v>10200960</v>
+        <v>77089320</v>
       </c>
       <c r="D7" t="n">
-        <v>9421102.439999999</v>
+        <v>71195885.54000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1234417.21</v>
+        <v>3950135.08</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>13236.75</v>
+        <v>110056.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>157524.51</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>81666.2</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>48494.16</v>
+        <v>392700.96</v>
       </c>
     </row>
     <row r="8">
@@ -12791,37 +12785,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>2832984</v>
+        <v>18596160</v>
       </c>
       <c r="C8" t="n">
-        <v>3076920</v>
+        <v>33485760</v>
       </c>
       <c r="D8" t="n">
-        <v>3278189.25</v>
+        <v>35676149.67</v>
       </c>
       <c r="E8" t="n">
-        <v>244047.99</v>
+        <v>1016866.62</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>18398.25</v>
+        <v>130952.25</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>14109.15</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>49583.05</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23676.23</v>
+        <v>218102.2</v>
       </c>
     </row>
     <row r="9">
@@ -12829,22 +12823,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1383228</v>
+        <v>1519056</v>
       </c>
       <c r="C9" t="n">
-        <v>970200</v>
+        <v>4379760</v>
       </c>
       <c r="D9" t="n">
-        <v>1127760.34</v>
+        <v>5091032.4</v>
       </c>
       <c r="E9" t="n">
-        <v>355111.55</v>
+        <v>88777.89</v>
       </c>
       <c r="F9" t="n">
-        <v>41667</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>13209</v>
+        <v>31135.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12859,7 +12853,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6409.37</v>
+        <v>64322.59</v>
       </c>
     </row>
     <row r="10">
@@ -12867,13 +12861,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>848034</v>
+        <v>499950</v>
       </c>
       <c r="C10" t="n">
-        <v>110880</v>
+        <v>887040</v>
       </c>
       <c r="D10" t="n">
-        <v>139640.85</v>
+        <v>1117126.77</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12882,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>7215</v>
+        <v>12210</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12897,7 +12891,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>4527.25</v>
+        <v>31187.74</v>
       </c>
     </row>
     <row r="11">
@@ -12905,13 +12899,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>475200</v>
+        <v>459162</v>
       </c>
       <c r="C11" t="n">
-        <v>166320</v>
+        <v>194040</v>
       </c>
       <c r="D11" t="n">
-        <v>216322.93</v>
+        <v>252376.75</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12920,10 +12914,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2220</v>
+        <v>2775</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8299.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12935,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2826</v>
+        <v>33346.8</v>
       </c>
     </row>
     <row r="12">
@@ -12943,22 +12937,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>345510</v>
+        <v>87120</v>
       </c>
       <c r="C12" t="n">
-        <v>55440</v>
+        <v>166320</v>
       </c>
       <c r="D12" t="n">
-        <v>74394.86</v>
+        <v>223184.59</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>79260.05</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2220</v>
+        <v>4440</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12973,7 +12967,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>847.8</v>
+        <v>14412.6</v>
       </c>
     </row>
     <row r="13">
@@ -12981,13 +12975,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>372438</v>
+        <v>36036</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>114300.85</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13011,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1413</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="14">
@@ -13019,22 +13013,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>94446</v>
+        <v>36234</v>
       </c>
       <c r="C14" t="n">
-        <v>27720</v>
+        <v>83160</v>
       </c>
       <c r="D14" t="n">
-        <v>39003.13</v>
+        <v>117009.4</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>94399.05</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8325</v>
+        <v>2775</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13049,7 +13043,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5086.8</v>
+        <v>1695.6</v>
       </c>
     </row>
     <row r="15">
@@ -13057,13 +13051,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>9504</v>
+        <v>17424</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>83160</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>118694.72</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13072,7 +13066,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1665</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13087,7 +13081,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2543.4</v>
       </c>
     </row>
     <row r="16">
@@ -13095,13 +13089,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>2178</v>
+        <v>9504</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13110,7 +13104,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2775</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13125,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3391.2</v>
       </c>
     </row>
     <row r="17">
@@ -13133,13 +13127,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>2772</v>
+        <v>1188</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13148,7 +13142,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3885</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13163,7 +13157,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4239</v>
       </c>
     </row>
     <row r="18">
@@ -13171,13 +13165,13 @@
         <v>700</v>
       </c>
       <c r="B18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>194040</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>280886.76</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13186,7 +13180,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>67710</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13201,7 +13195,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3391.2</v>
       </c>
     </row>
     <row r="19">
@@ -13209,13 +13203,13 @@
         <v>750</v>
       </c>
       <c r="B19" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13224,7 +13218,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>555</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13250,10 +13244,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13326,10 +13320,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>55440</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>80253.36</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13364,10 +13358,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27720</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>40126.68</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13402,10 +13396,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>166320</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>240760.08</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13500,7 +13494,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Exp</t>
+          <t>Region: Shikarpur | Mode: Exp</t>
         </is>
       </c>
     </row>
@@ -13571,37 +13565,37 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>34980.66</v>
+        <v>22073.04</v>
       </c>
       <c r="C4" t="n">
-        <v>5947704</v>
+        <v>2247840</v>
       </c>
       <c r="D4" t="n">
-        <v>4673196</v>
+        <v>1766160</v>
       </c>
       <c r="E4" t="n">
-        <v>1478700</v>
+        <v>820800</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>100230</v>
+        <v>61770</v>
       </c>
       <c r="H4" t="n">
-        <v>10110</v>
+        <v>4620</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>230460</v>
+        <v>222870</v>
       </c>
     </row>
     <row r="5">
@@ -13609,37 +13603,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>41602.59</v>
+        <v>5566.14</v>
       </c>
       <c r="C5" t="n">
-        <v>5687136</v>
+        <v>434952</v>
       </c>
       <c r="D5" t="n">
-        <v>4468464</v>
+        <v>341748</v>
       </c>
       <c r="E5" t="n">
-        <v>1096200</v>
+        <v>190800</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>99990</v>
+        <v>13080</v>
       </c>
       <c r="H5" t="n">
-        <v>12960</v>
+        <v>1140</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>265500</v>
+        <v>62880</v>
       </c>
     </row>
     <row r="6">
@@ -13647,37 +13641,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>29693.97</v>
+        <v>527.76</v>
       </c>
       <c r="C6" t="n">
-        <v>2344104</v>
+        <v>55440</v>
       </c>
       <c r="D6" t="n">
-        <v>1841796</v>
+        <v>43560</v>
       </c>
       <c r="E6" t="n">
-        <v>238500</v>
+        <v>15300</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>62220</v>
+        <v>1350</v>
       </c>
       <c r="H6" t="n">
-        <v>5220</v>
+        <v>210</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>124020</v>
+        <v>9930</v>
       </c>
     </row>
     <row r="7">
@@ -13685,37 +13679,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>21279.42</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1401624</v>
+        <v>9576</v>
       </c>
       <c r="D7" t="n">
-        <v>1101276</v>
+        <v>7524</v>
       </c>
       <c r="E7" t="n">
-        <v>100800</v>
+        <v>2700</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>39660</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>780</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>69480</v>
+        <v>630</v>
       </c>
     </row>
     <row r="8">
@@ -13723,37 +13717,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>8452.799999999999</v>
+        <v>6.3</v>
       </c>
       <c r="C8" t="n">
-        <v>608832</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>478368</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>22500</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>10890</v>
+        <v>60</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>32610</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9">
@@ -13761,22 +13755,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>690.48</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>79632</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>62568</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1980</v>
+        <v>30</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -13791,7 +13785,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>8430</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -13799,13 +13793,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>227.25</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>16128</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>12672</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -13814,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -13829,7 +13823,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3720</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -13837,13 +13831,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>208.71</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -13852,22 +13846,22 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>30</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3540</v>
       </c>
     </row>
     <row r="12">
@@ -13875,22 +13869,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>39.6</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -13905,7 +13899,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1530</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -13913,13 +13907,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>16.38</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -13928,7 +13922,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13943,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13951,22 +13945,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>16.47</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13981,7 +13975,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13989,13 +13983,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>7.92</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1188</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14004,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14019,7 +14013,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14027,13 +14021,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14042,7 +14036,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14057,7 +14051,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14065,13 +14059,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -14080,7 +14074,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -14095,7 +14089,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -14106,10 +14100,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -14118,7 +14112,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3660</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -14133,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -14144,10 +14138,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -14156,7 +14150,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -14182,10 +14176,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -14258,10 +14252,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -14296,10 +14290,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -14334,10 +14328,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -14432,7 +14426,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Vul</t>
+          <t>Region: Shikarpur | Mode: Vul</t>
         </is>
       </c>
     </row>
@@ -14541,37 +14535,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>18721.17</v>
+        <v>2504.76</v>
       </c>
       <c r="C5" t="n">
-        <v>3127924.8</v>
+        <v>239223.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1479061.58</v>
+        <v>113118.59</v>
       </c>
       <c r="E5" t="n">
-        <v>120910.86</v>
+        <v>21045.24</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4665.6</v>
+        <v>410.4</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>55755</v>
+        <v>13204.8</v>
       </c>
     </row>
     <row r="6">
@@ -14579,37 +14573,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>23755.18</v>
+        <v>422.21</v>
       </c>
       <c r="C6" t="n">
-        <v>2109693.6</v>
+        <v>49896</v>
       </c>
       <c r="D6" t="n">
-        <v>933790.5699999999</v>
+        <v>22084.92</v>
       </c>
       <c r="E6" t="n">
-        <v>40306.5</v>
+        <v>2585.7</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>3111</v>
+        <v>67.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2975.4</v>
+        <v>119.7</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>45887.4</v>
+        <v>3674.1</v>
       </c>
     </row>
     <row r="7">
@@ -14617,37 +14611,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>20215.45</v>
+        <v>85.67</v>
       </c>
       <c r="C7" t="n">
-        <v>1401624</v>
+        <v>9576</v>
       </c>
       <c r="D7" t="n">
-        <v>702614.09</v>
+        <v>4800.31</v>
       </c>
       <c r="E7" t="n">
-        <v>21440.16</v>
+        <v>574.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5949</v>
+        <v>4.5</v>
       </c>
       <c r="H7" t="n">
-        <v>569.4</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>41688</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8">
@@ -14655,37 +14649,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>8452.799999999999</v>
+        <v>6.3</v>
       </c>
       <c r="C8" t="n">
-        <v>608832</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>352078.85</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>5519.25</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>7078.5</v>
+        <v>39</v>
       </c>
       <c r="H8" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.85</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23153.1</v>
+        <v>127.8</v>
       </c>
     </row>
     <row r="9">
@@ -14693,22 +14687,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>690.48</v>
+        <v>0.09</v>
       </c>
       <c r="C9" t="n">
-        <v>79632</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>50242.1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>481.86</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1683</v>
+        <v>25.5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -14723,7 +14717,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>6828.3</v>
+        <v>72.90000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -14731,13 +14725,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>227.25</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>16128</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>11024.64</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -14746,7 +14740,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -14761,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3310.8</v>
+        <v>160.2</v>
       </c>
     </row>
     <row r="11">
@@ -14769,13 +14763,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>208.71</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>2490.64</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -14784,22 +14778,22 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>30</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3540</v>
       </c>
     </row>
     <row r="12">
@@ -14807,22 +14801,22 @@
         <v>400</v>
       </c>
       <c r="B12" t="n">
-        <v>39.6</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>2202.55</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>430.2</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -14837,7 +14831,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1530</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -14845,13 +14839,13 @@
         <v>450</v>
       </c>
       <c r="B13" t="n">
-        <v>16.38</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>1128.01</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -14860,7 +14854,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -14875,7 +14869,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -14883,22 +14877,22 @@
         <v>500</v>
       </c>
       <c r="B14" t="n">
-        <v>16.47</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>1154.74</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>512.37</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -14913,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -14921,13 +14915,13 @@
         <v>550</v>
       </c>
       <c r="B15" t="n">
-        <v>7.92</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>1512</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1171.37</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -14936,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -14951,7 +14945,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -14959,13 +14953,13 @@
         <v>600</v>
       </c>
       <c r="B16" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -14974,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -14989,7 +14983,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -14997,13 +14991,13 @@
         <v>650</v>
       </c>
       <c r="B17" t="n">
-        <v>0.54</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15012,7 +15006,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -15027,7 +15021,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -15038,10 +15032,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>3528</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2772</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15050,7 +15044,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3660</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -15065,7 +15059,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -15076,10 +15070,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15088,7 +15082,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -15114,10 +15108,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15190,10 +15184,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>1008</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>792</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -15228,10 +15222,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>504</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -15266,10 +15260,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>3024</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>2376</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -15364,7 +15358,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Region: Qambar Shahdadkot | Mode: Dmg</t>
+          <t>Region: Shikarpur | Mode: Dmg</t>
         </is>
       </c>
     </row>
@@ -15473,37 +15467,37 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>41186564.1</v>
+        <v>5510478.6</v>
       </c>
       <c r="C5" t="n">
-        <v>172035864</v>
+        <v>13157298</v>
       </c>
       <c r="D5" t="n">
-        <v>149873310.31</v>
+        <v>11462306.52</v>
       </c>
       <c r="E5" t="n">
-        <v>22276616.85</v>
+        <v>3877375.02</v>
       </c>
       <c r="F5" t="n">
-        <v>8333.4</v>
+        <v>5000.04</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1290738.24</v>
+        <v>113537.16</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>525212.1</v>
+        <v>124389.22</v>
       </c>
     </row>
     <row r="6">
@@ -15511,37 +15505,37 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>52261387.2</v>
+        <v>928857.6</v>
       </c>
       <c r="C6" t="n">
-        <v>116033148</v>
+        <v>2744280</v>
       </c>
       <c r="D6" t="n">
-        <v>94620998.66</v>
+        <v>2237864.94</v>
       </c>
       <c r="E6" t="n">
-        <v>7426069.56</v>
+        <v>476389.37</v>
       </c>
       <c r="F6" t="n">
-        <v>4166.7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>57553.5</v>
+        <v>1248.75</v>
       </c>
       <c r="H6" t="n">
-        <v>823144.41</v>
+        <v>33115</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>432259.31</v>
+        <v>34610.02</v>
       </c>
     </row>
     <row r="7">
@@ -15549,37 +15543,37 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>44473987.8</v>
+        <v>188476.2</v>
       </c>
       <c r="C7" t="n">
-        <v>77089320</v>
+        <v>526680</v>
       </c>
       <c r="D7" t="n">
-        <v>71195885.54000001</v>
+        <v>486415.61</v>
       </c>
       <c r="E7" t="n">
-        <v>3950135.08</v>
+        <v>105807.19</v>
       </c>
       <c r="F7" t="n">
-        <v>25000.2</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>110056.5</v>
+        <v>83.25</v>
       </c>
       <c r="H7" t="n">
-        <v>157524.51</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>392700.96</v>
+        <v>3560.76</v>
       </c>
     </row>
     <row r="8">
@@ -15587,37 +15581,37 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>18596160</v>
+        <v>13860</v>
       </c>
       <c r="C8" t="n">
-        <v>33485760</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>35676149.67</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1016866.62</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>130952.25</v>
+        <v>721.5</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>218102.2</v>
+        <v>1203.88</v>
       </c>
     </row>
     <row r="9">
@@ -15625,22 +15619,22 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>1519056</v>
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>4379760</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>5091032.4</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>88777.89</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>31135.5</v>
+        <v>471.75</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15655,7 +15649,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>64322.59</v>
+        <v>686.72</v>
       </c>
     </row>
     <row r="10">
@@ -15663,13 +15657,13 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>499950</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>887040</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1117126.77</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15678,7 +15672,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12210</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -15693,7 +15687,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>31187.74</v>
+        <v>1509.08</v>
       </c>
     </row>
     <row r="11">
@@ -15701,13 +15695,13 @@
         <v>350</v>
       </c>
       <c r="B11" t="n">
-        <v>459162</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>194040</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>252376.75</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15716,10 +15710,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2775</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -15731,4667 +15725,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>33346.8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>87120</v>
-      </c>
-      <c r="C12" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D12" t="n">
-        <v>223184.59</v>
-      </c>
-      <c r="E12" t="n">
-        <v>79260.05</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>14412.6</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>36036</v>
-      </c>
-      <c r="C13" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D13" t="n">
-        <v>114300.85</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2220</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>4239</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>36234</v>
-      </c>
-      <c r="C14" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D14" t="n">
-        <v>117009.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>94399.05</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1695.6</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>17424</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>1665</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2543.4</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>9504</v>
-      </c>
-      <c r="C16" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D16" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2775</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>1188</v>
-      </c>
-      <c r="C17" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D17" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3885</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>4239</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D18" t="n">
-        <v>280886.76</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>67710</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>3391.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D19" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>555</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D20" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D22" t="n">
-        <v>80253.36</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>27720</v>
-      </c>
-      <c r="D23" t="n">
-        <v>40126.68</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>166320</v>
-      </c>
-      <c r="D24" t="n">
-        <v>240760.08</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>5286.42</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1029672</v>
-      </c>
-      <c r="D4" t="n">
-        <v>809028</v>
-      </c>
-      <c r="E4" t="n">
-        <v>276300</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" t="n">
-        <v>13590</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3450</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>38070</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6745.14</v>
-      </c>
-      <c r="C5" t="n">
-        <v>762048</v>
-      </c>
-      <c r="D5" t="n">
-        <v>598752</v>
-      </c>
-      <c r="E5" t="n">
-        <v>155700</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>15420</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2010</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>32820</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>5796.81</v>
-      </c>
-      <c r="C6" t="n">
-        <v>402696</v>
-      </c>
-      <c r="D6" t="n">
-        <v>316404</v>
-      </c>
-      <c r="E6" t="n">
-        <v>73800</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8460</v>
-      </c>
-      <c r="H6" t="n">
-        <v>390</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>19500</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>4147.29</v>
-      </c>
-      <c r="C7" t="n">
-        <v>212184</v>
-      </c>
-      <c r="D7" t="n">
-        <v>166716</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4050</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>15600</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2729.61</v>
-      </c>
-      <c r="C8" t="n">
-        <v>71568</v>
-      </c>
-      <c r="D8" t="n">
-        <v>56232</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2340</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>6150</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1786.41</v>
-      </c>
-      <c r="C9" t="n">
-        <v>30744</v>
-      </c>
-      <c r="D9" t="n">
-        <v>24156</v>
-      </c>
-      <c r="E9" t="n">
-        <v>900</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>450</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>911.16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6552</v>
-      </c>
-      <c r="D10" t="n">
-        <v>5148</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>540.36</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2772</v>
-      </c>
-      <c r="E11" t="n">
-        <v>900</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>401.31</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>365.58</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1584</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.49</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>792</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>252.36</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1188</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27.63</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3035.31</v>
-      </c>
-      <c r="C5" t="n">
-        <v>419126.4</v>
-      </c>
-      <c r="D5" t="n">
-        <v>198186.91</v>
-      </c>
-      <c r="E5" t="n">
-        <v>17173.71</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>723.6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6892.2</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>4637.45</v>
-      </c>
-      <c r="C6" t="n">
-        <v>362426.4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>160416.83</v>
-      </c>
-      <c r="E6" t="n">
-        <v>12472.2</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>423</v>
-      </c>
-      <c r="H6" t="n">
-        <v>222.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>7215</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>3939.93</v>
-      </c>
-      <c r="C7" t="n">
-        <v>212184</v>
-      </c>
-      <c r="D7" t="n">
-        <v>106364.81</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6508.62</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G7" t="n">
-        <v>607.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>9360</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2729.61</v>
-      </c>
-      <c r="C8" t="n">
-        <v>71568</v>
-      </c>
-      <c r="D8" t="n">
-        <v>41386.75</v>
-      </c>
-      <c r="E8" t="n">
-        <v>441.54</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1521</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4366.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>1786.41</v>
-      </c>
-      <c r="C9" t="n">
-        <v>30744</v>
-      </c>
-      <c r="D9" t="n">
-        <v>19397.27</v>
-      </c>
-      <c r="E9" t="n">
-        <v>240.93</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>382.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1020.6</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>911.16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6552</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4478.76</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>240</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>186.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>540.36</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3528</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2490.64</v>
-      </c>
-      <c r="E11" t="n">
-        <v>368.82</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>401.31</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1101.28</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>365.58</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2016</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1504.01</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>491.49</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1008</v>
-      </c>
-      <c r="D14" t="n">
-        <v>769.8200000000001</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>252.36</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1512</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1171.37</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>42.66</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>27.63</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shaheed Benazirabad | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6677688.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>23051952</v>
-      </c>
-      <c r="D5" t="n">
-        <v>20082279.79</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3164084.33</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000.04</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>200183.94</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>64924.52</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>10202385.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>19933452</v>
-      </c>
-      <c r="D6" t="n">
-        <v>16255037.18</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2297878.13</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7825.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>61499.29</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>67965.3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>8667836.1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>11670120</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10777945.99</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1199148.15</v>
-      </c>
-      <c r="F7" t="n">
-        <v>25000.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>11238.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>88171.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6005142</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3936240</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4193719.58</v>
-      </c>
-      <c r="E8" t="n">
-        <v>81349.33</v>
-      </c>
-      <c r="F8" t="n">
-        <v>39583.65</v>
-      </c>
-      <c r="G8" t="n">
-        <v>28138.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>41132.43</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>3930102</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1690920</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1965525.17</v>
-      </c>
-      <c r="E9" t="n">
-        <v>44388.94</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7076.25</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>9614.049999999999</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2004552</v>
-      </c>
-      <c r="C10" t="n">
-        <v>360360</v>
-      </c>
-      <c r="D10" t="n">
-        <v>453832.75</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>4440</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1760.6</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>1188792</v>
-      </c>
-      <c r="C11" t="n">
-        <v>194040</v>
-      </c>
-      <c r="D11" t="n">
-        <v>252376.75</v>
-      </c>
-      <c r="E11" t="n">
-        <v>67951.39999999999</v>
-      </c>
-      <c r="F11" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>882882</v>
-      </c>
-      <c r="C12" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D12" t="n">
-        <v>111592.3</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>41667</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>804276</v>
-      </c>
-      <c r="C13" t="n">
-        <v>110880</v>
-      </c>
-      <c r="D13" t="n">
-        <v>152401.13</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>1081278</v>
-      </c>
-      <c r="C14" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D14" t="n">
-        <v>78006.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>555192</v>
-      </c>
-      <c r="C15" t="n">
-        <v>83160</v>
-      </c>
-      <c r="D15" t="n">
-        <v>118694.72</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>93852</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>60786</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Exp</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>22073.04</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2247840</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1766160</v>
-      </c>
-      <c r="E4" t="n">
-        <v>820800</v>
-      </c>
-      <c r="F4" t="n">
-        <v>27</v>
-      </c>
-      <c r="G4" t="n">
-        <v>61770</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4620</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>222870</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5566.14</v>
-      </c>
-      <c r="C5" t="n">
-        <v>434952</v>
-      </c>
-      <c r="D5" t="n">
-        <v>341748</v>
-      </c>
-      <c r="E5" t="n">
-        <v>190800</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13080</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1140</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>62880</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>527.76</v>
-      </c>
-      <c r="C6" t="n">
-        <v>55440</v>
-      </c>
-      <c r="D6" t="n">
-        <v>43560</v>
-      </c>
-      <c r="E6" t="n">
-        <v>15300</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1350</v>
-      </c>
-      <c r="H6" t="n">
-        <v>210</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>9930</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90.18000000000001</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9576</v>
-      </c>
-      <c r="D7" t="n">
-        <v>7524</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2700</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>60</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Vul</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2504.76</v>
-      </c>
-      <c r="C5" t="n">
-        <v>239223.6</v>
-      </c>
-      <c r="D5" t="n">
-        <v>113118.59</v>
-      </c>
-      <c r="E5" t="n">
-        <v>21045.24</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>410.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>13204.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>422.21</v>
-      </c>
-      <c r="C6" t="n">
-        <v>49896</v>
-      </c>
-      <c r="D6" t="n">
-        <v>22084.92</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2585.7</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="H6" t="n">
-        <v>119.7</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3674.1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>85.67</v>
-      </c>
-      <c r="C7" t="n">
-        <v>9576</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4800.31</v>
-      </c>
-      <c r="E7" t="n">
-        <v>574.29</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>39</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>127.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>72.90000000000001</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>160.2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>30</v>
+        <v>282.6</v>
       </c>
     </row>
     <row r="12">
@@ -21876,938 +17210,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Region: Shikarpur | Mode: Dmg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Inundation Depth (cm)</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Cropped Area (ha)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (56%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &lt;3m (44%) (sq.m)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Buildings &gt;=3m (sq.m)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Telecom Tower</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Electric lines</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Railways</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Hospitals</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>BHU</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Schools</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Roads</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>50</v>
-      </c>
-      <c r="B5" t="n">
-        <v>5510478.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>13157298</v>
-      </c>
-      <c r="D5" t="n">
-        <v>11462306.52</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3877375.02</v>
-      </c>
-      <c r="F5" t="n">
-        <v>5000.04</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>113537.16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>124389.22</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>100</v>
-      </c>
-      <c r="B6" t="n">
-        <v>928857.6</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2744280</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2237864.94</v>
-      </c>
-      <c r="E6" t="n">
-        <v>476389.37</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1248.75</v>
-      </c>
-      <c r="H6" t="n">
-        <v>33115</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>34610.02</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>150</v>
-      </c>
-      <c r="B7" t="n">
-        <v>188476.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>526680</v>
-      </c>
-      <c r="D7" t="n">
-        <v>486415.61</v>
-      </c>
-      <c r="E7" t="n">
-        <v>105807.19</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>83.25</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3560.76</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>200</v>
-      </c>
-      <c r="B8" t="n">
-        <v>13860</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>721.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1203.88</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>250</v>
-      </c>
-      <c r="B9" t="n">
-        <v>198</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>471.75</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>686.72</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>300</v>
-      </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1509.08</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>350</v>
-      </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>282.6</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>400</v>
-      </c>
-      <c r="B12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>450</v>
-      </c>
-      <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>500</v>
-      </c>
-      <c r="B14" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>550</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>600</v>
-      </c>
-      <c r="B16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>650</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>700</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>750</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>800</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>850</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>900</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>950</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="1">
-        <f>SUM(B4:B24)</f>
-        <v/>
-      </c>
-      <c r="C25" s="1">
-        <f>SUM(C4:C24)</f>
-        <v/>
-      </c>
-      <c r="D25" s="1">
-        <f>SUM(D4:D24)</f>
-        <v/>
-      </c>
-      <c r="E25" s="1">
-        <f>SUM(E4:E24)</f>
-        <v/>
-      </c>
-      <c r="F25" s="1">
-        <f>SUM(F4:F24)</f>
-        <v/>
-      </c>
-      <c r="G25" s="1">
-        <f>SUM(G4:G24)</f>
-        <v/>
-      </c>
-      <c r="H25" s="1">
-        <f>SUM(H4:H24)</f>
-        <v/>
-      </c>
-      <c r="I25" s="1">
-        <f>SUM(I4:I24)</f>
-        <v/>
-      </c>
-      <c r="J25" s="1">
-        <f>SUM(J4:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="1">
-        <f>SUM(K4:K24)</f>
-        <v/>
-      </c>
-      <c r="L25" s="1">
-        <f>SUM(L4:L24)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
@@ -538,7 +538,7 @@
         <v>75570</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
         <v>36</v>
@@ -576,7 +576,7 @@
         <v>65610</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
         <v>17</v>
@@ -614,7 +614,7 @@
         <v>19050</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
         <v>15</v>
@@ -690,7 +690,7 @@
         <v>5730</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>6</v>
@@ -804,7 +804,7 @@
         <v>810</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -1546,7 +1546,7 @@
         <v>5550</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -1622,7 +1622,7 @@
         <v>5400</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -1736,7 +1736,7 @@
         <v>750</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>3163.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
@@ -2554,7 +2554,7 @@
         <v>4590</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
@@ -2668,7 +2668,7 @@
         <v>750</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
         <v>875182.27</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>134165.5</v>
       </c>
       <c r="J6" t="n">
         <v>87499.5</v>
@@ -3486,7 +3486,7 @@
         <v>1269823.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>551995.2</v>
       </c>
       <c r="J8" t="n">
         <v>99166.10000000001</v>
@@ -3600,7 +3600,7 @@
         <v>207487.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -9858,7 +9858,7 @@
         <v>10110</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J4" t="n">
         <v>9</v>
@@ -9896,7 +9896,7 @@
         <v>12960</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>7</v>
@@ -9934,7 +9934,7 @@
         <v>5220</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>3</v>
@@ -10010,7 +10010,7 @@
         <v>60</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -10828,7 +10828,7 @@
         <v>23619.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
         <v>5.1</v>
@@ -10866,7 +10866,7 @@
         <v>10858.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
@@ -10942,7 +10942,7 @@
         <v>4870.5</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="J8" t="n">
         <v>5.1</v>
@@ -11056,7 +11056,7 @@
         <v>810</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
@@ -11760,7 +11760,7 @@
         <v>4665.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
@@ -11798,7 +11798,7 @@
         <v>2975.4</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
@@ -11874,7 +11874,7 @@
         <v>51</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
@@ -12692,7 +12692,7 @@
         <v>1290738.24</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>122499.3</v>
@@ -12730,7 +12730,7 @@
         <v>823144.41</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>402496.5</v>
       </c>
       <c r="J6" t="n">
         <v>87499.5</v>
@@ -12806,7 +12806,7 @@
         <v>14109.15</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>275997.6</v>
       </c>
       <c r="J8" t="n">
         <v>49583.05</v>
@@ -13586,7 +13586,7 @@
         <v>4620</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -16420,7 +16420,7 @@
         <v>6534362.34</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>114999</v>
       </c>
       <c r="J5" t="n">
         <v>297498.3</v>
@@ -16458,7 +16458,7 @@
         <v>3004004.02</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>536662</v>
       </c>
       <c r="J6" t="n">
         <v>437497.5</v>
@@ -16534,7 +16534,7 @@
         <v>1347423.82</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>827992.8</v>
       </c>
       <c r="J8" t="n">
         <v>297498.3</v>
@@ -16648,7 +16648,7 @@
         <v>224086.5</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>383330</v>
       </c>
       <c r="J11" t="n">
         <v>116666</v>
@@ -17314,7 +17314,7 @@
         <v>20790</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>7</v>
@@ -17352,7 +17352,7 @@
         <v>16710</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -18284,7 +18284,7 @@
         <v>6015.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="J5" t="n">
         <v>0.9</v>
@@ -19216,7 +19216,7 @@
         <v>1664215.74</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>57499.5</v>
       </c>
       <c r="J5" t="n">
         <v>52499.7</v>
@@ -20110,7 +20110,7 @@
         <v>27840</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
         <v>10</v>

--- a/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
@@ -544,7 +544,7 @@
         <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>888</v>
       </c>
       <c r="L4" t="n">
         <v>1290060</v>
@@ -582,7 +582,7 @@
         <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>714</v>
       </c>
       <c r="L5" t="n">
         <v>932970</v>
@@ -620,7 +620,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>411</v>
       </c>
       <c r="L6" t="n">
         <v>566070</v>
@@ -658,7 +658,7 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="L7" t="n">
         <v>335640</v>
@@ -696,7 +696,7 @@
         <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>187</v>
       </c>
       <c r="L8" t="n">
         <v>236520</v>
@@ -734,7 +734,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="L9" t="n">
         <v>189810</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L10" t="n">
         <v>98130</v>
@@ -810,7 +810,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
         <v>47460</v>
@@ -848,7 +848,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>17130</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>5400</v>
@@ -962,7 +962,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1470</v>
@@ -1476,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L4" t="n">
         <v>35820</v>
@@ -1514,7 +1514,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
         <v>52170</v>
@@ -1552,7 +1552,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
         <v>55620</v>
@@ -1590,7 +1590,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
         <v>49740</v>
@@ -1628,7 +1628,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>73170</v>
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L9" t="n">
         <v>93150</v>
@@ -1704,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
         <v>50670</v>
@@ -1742,7 +1742,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
         <v>23910</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>10830</v>
@@ -1818,7 +1818,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>3480</v>
@@ -2446,7 +2446,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>14.28</v>
       </c>
       <c r="L5" t="n">
         <v>10955.7</v>
@@ -2484,7 +2484,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>21.45</v>
       </c>
       <c r="L6" t="n">
         <v>20579.4</v>
@@ -2522,7 +2522,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>18.04</v>
       </c>
       <c r="L7" t="n">
         <v>29844</v>
@@ -2560,7 +2560,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="L8" t="n">
         <v>51950.7</v>
@@ -2598,7 +2598,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="L9" t="n">
         <v>75451.5</v>
@@ -2636,7 +2636,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L10" t="n">
         <v>45096.3</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
         <v>23910</v>
@@ -2712,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L12" t="n">
         <v>10830</v>
@@ -2750,7 +2750,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>3480</v>
@@ -3378,7 +3378,7 @@
         <v>17499.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>304649.52</v>
       </c>
       <c r="L5" t="n">
         <v>103202.69</v>
@@ -3416,7 +3416,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>457614.3</v>
       </c>
       <c r="L6" t="n">
         <v>193857.95</v>
@@ -3454,7 +3454,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>384865.36</v>
       </c>
       <c r="L7" t="n">
         <v>281130.48</v>
@@ -3492,7 +3492,7 @@
         <v>99166.10000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>595218.6</v>
       </c>
       <c r="L8" t="n">
         <v>489375.59</v>
@@ -3530,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1024032</v>
       </c>
       <c r="L9" t="n">
         <v>710753.13</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>576018</v>
       </c>
       <c r="L10" t="n">
         <v>424807.15</v>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>256008</v>
       </c>
       <c r="L11" t="n">
         <v>225232.2</v>
@@ -3644,7 +3644,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>149338</v>
       </c>
       <c r="L12" t="n">
         <v>102018.6</v>
@@ -3682,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L13" t="n">
         <v>32781.6</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L4" t="n">
         <v>103020</v>
@@ -4310,7 +4310,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L5" t="n">
         <v>35070</v>
@@ -4348,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>8190</v>
@@ -5242,7 +5242,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="L5" t="n">
         <v>7364.7</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>134404.2</v>
       </c>
       <c r="L5" t="n">
         <v>69375.47</v>
@@ -6212,7 +6212,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>27734.2</v>
       </c>
       <c r="L6" t="n">
         <v>28545.43</v>
@@ -7068,7 +7068,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="L4" t="n">
         <v>53850</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L5" t="n">
         <v>13770</v>
@@ -7144,7 +7144,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>2640</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>510</v>
@@ -8038,7 +8038,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="L5" t="n">
         <v>2891.7</v>
@@ -8076,7 +8076,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
@@ -8114,7 +8114,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
@@ -8970,7 +8970,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>80642.52</v>
       </c>
       <c r="L5" t="n">
         <v>27239.81</v>
@@ -9008,7 +9008,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>41601.3</v>
       </c>
       <c r="L6" t="n">
         <v>9201.459999999999</v>
@@ -9046,7 +9046,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>34987.76</v>
       </c>
       <c r="L7" t="n">
         <v>2882.52</v>
@@ -9864,7 +9864,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="L4" t="n">
         <v>230460</v>
@@ -9902,7 +9902,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
       <c r="L5" t="n">
         <v>265500</v>
@@ -9940,7 +9940,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="L6" t="n">
         <v>124020</v>
@@ -9978,7 +9978,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L7" t="n">
         <v>69480</v>
@@ -10016,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L8" t="n">
         <v>32610</v>
@@ -10054,7 +10054,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>8430</v>
@@ -10834,7 +10834,7 @@
         <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>299.88</v>
       </c>
       <c r="L5" t="n">
         <v>195923.7</v>
@@ -10872,7 +10872,7 @@
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>267.15</v>
       </c>
       <c r="L6" t="n">
         <v>209445.9</v>
@@ -10910,7 +10910,7 @@
         <v>5.6</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>251.74</v>
       </c>
       <c r="L7" t="n">
         <v>201384</v>
@@ -10948,7 +10948,7 @@
         <v>5.1</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>168.3</v>
       </c>
       <c r="L8" t="n">
         <v>167929.2</v>
@@ -10986,7 +10986,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="L9" t="n">
         <v>153746.1</v>
@@ -11024,7 +11024,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="L10" t="n">
         <v>87335.7</v>
@@ -11062,7 +11062,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="L11" t="n">
         <v>47460</v>
@@ -11100,7 +11100,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L12" t="n">
         <v>17130</v>
@@ -11138,7 +11138,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>5400</v>
@@ -11214,7 +11214,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>1470</v>
@@ -11766,7 +11766,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>112.98</v>
       </c>
       <c r="L5" t="n">
         <v>55755</v>
@@ -11804,7 +11804,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="L6" t="n">
         <v>45887.4</v>
@@ -11842,7 +11842,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L7" t="n">
         <v>41688</v>
@@ -11880,7 +11880,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="L8" t="n">
         <v>23153.1</v>
@@ -11918,7 +11918,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>6828.3</v>
@@ -12698,7 +12698,7 @@
         <v>122499.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2410315.32</v>
       </c>
       <c r="L5" t="n">
         <v>525212.1</v>
@@ -12736,7 +12736,7 @@
         <v>87499.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1539248.1</v>
       </c>
       <c r="L6" t="n">
         <v>432259.31</v>
@@ -12774,7 +12774,7 @@
         <v>81666.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1399510.4</v>
       </c>
       <c r="L7" t="n">
         <v>392700.96</v>
@@ -12812,7 +12812,7 @@
         <v>49583.05</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>576018</v>
       </c>
       <c r="L8" t="n">
         <v>218102.2</v>
@@ -12850,7 +12850,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>149338</v>
       </c>
       <c r="L9" t="n">
         <v>64322.59</v>
@@ -13592,7 +13592,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="L4" t="n">
         <v>222870</v>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
         <v>62880</v>
@@ -14562,7 +14562,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>7.98</v>
       </c>
       <c r="L5" t="n">
         <v>13204.8</v>
@@ -15494,7 +15494,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>170245.32</v>
       </c>
       <c r="L5" t="n">
         <v>124389.22</v>
@@ -16426,7 +16426,7 @@
         <v>297498.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>6397639.92</v>
       </c>
       <c r="L5" t="n">
         <v>1845601.25</v>
@@ -16464,7 +16464,7 @@
         <v>437497.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>5699378.1</v>
       </c>
       <c r="L6" t="n">
         <v>1972980.38</v>
@@ -16502,7 +16502,7 @@
         <v>326664.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>5370621.16</v>
       </c>
       <c r="L7" t="n">
         <v>1897037.28</v>
@@ -16540,7 +16540,7 @@
         <v>297498.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3590512.2</v>
       </c>
       <c r="L8" t="n">
         <v>1581893.06</v>
@@ -16578,7 +16578,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3093430</v>
       </c>
       <c r="L9" t="n">
         <v>1448288.26</v>
@@ -16616,7 +16616,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1749388</v>
       </c>
       <c r="L10" t="n">
         <v>822702.29</v>
@@ -16654,7 +16654,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>682688</v>
       </c>
       <c r="L11" t="n">
         <v>447073.2</v>
@@ -16692,7 +16692,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>213340</v>
       </c>
       <c r="L12" t="n">
         <v>161364.6</v>
@@ -16730,7 +16730,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>42668</v>
       </c>
       <c r="L13" t="n">
         <v>50868</v>
@@ -16806,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>13847.4</v>
@@ -17320,7 +17320,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="L4" t="n">
         <v>220350</v>
@@ -17358,7 +17358,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="L5" t="n">
         <v>276510</v>
@@ -17396,7 +17396,7 @@
         <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="L6" t="n">
         <v>258930</v>
@@ -17434,7 +17434,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="L7" t="n">
         <v>179460</v>
@@ -17472,7 +17472,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="L8" t="n">
         <v>117300</v>
@@ -17510,7 +17510,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L9" t="n">
         <v>84810</v>
@@ -17548,7 +17548,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L10" t="n">
         <v>42120</v>
@@ -17586,7 +17586,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
         <v>19380</v>
@@ -17624,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>4680</v>
@@ -17738,7 +17738,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
@@ -18290,7 +18290,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>58067.1</v>
@@ -18328,7 +18328,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>139.75</v>
       </c>
       <c r="L6" t="n">
         <v>95804.10000000001</v>
@@ -18366,7 +18366,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>162.36</v>
       </c>
       <c r="L7" t="n">
         <v>107676</v>
@@ -18404,7 +18404,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>112.5</v>
       </c>
       <c r="L8" t="n">
         <v>83283</v>
@@ -18442,7 +18442,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L9" t="n">
         <v>68696.10000000001</v>
@@ -18480,7 +18480,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="L10" t="n">
         <v>37486.8</v>
@@ -18518,7 +18518,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
         <v>19380</v>
@@ -18556,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
         <v>4680</v>
@@ -18670,7 +18670,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
@@ -19222,7 +19222,7 @@
         <v>52499.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>2051904.12</v>
       </c>
       <c r="L5" t="n">
         <v>546992.08</v>
@@ -19260,7 +19260,7 @@
         <v>233332</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2981426.5</v>
       </c>
       <c r="L6" t="n">
         <v>902474.62</v>
@@ -19298,7 +19298,7 @@
         <v>163332.4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3463788.24</v>
       </c>
       <c r="L7" t="n">
         <v>1014307.92</v>
@@ -19336,7 +19336,7 @@
         <v>148749.15</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2400075</v>
       </c>
       <c r="L8" t="n">
         <v>784525.86</v>
@@ -19374,7 +19374,7 @@
         <v>166249.05</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1877392</v>
       </c>
       <c r="L9" t="n">
         <v>647117.26</v>
@@ -19412,7 +19412,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1173370</v>
       </c>
       <c r="L10" t="n">
         <v>353125.66</v>
@@ -19450,7 +19450,7 @@
         <v>116666</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>426680</v>
       </c>
       <c r="L11" t="n">
         <v>182559.6</v>
@@ -19488,7 +19488,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>64002</v>
       </c>
       <c r="L12" t="n">
         <v>44085.6</v>
@@ -19602,7 +19602,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>21334</v>
       </c>
       <c r="L15" t="n">
         <v>2826</v>
@@ -20116,7 +20116,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="L4" t="n">
         <v>359460</v>
@@ -20154,7 +20154,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="L5" t="n">
         <v>165570</v>
@@ -20192,7 +20192,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="L6" t="n">
         <v>61770</v>
@@ -20230,7 +20230,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>8640</v>
@@ -21086,7 +21086,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>57.12</v>
       </c>
       <c r="L5" t="n">
         <v>34769.7</v>
@@ -21124,7 +21124,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>29.9</v>
       </c>
       <c r="L6" t="n">
         <v>22854.9</v>
@@ -21162,7 +21162,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="L7" t="n">
         <v>5184</v>
@@ -22018,7 +22018,7 @@
         <v>104999.4</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1218598.08</v>
       </c>
       <c r="L5" t="n">
         <v>327530.57</v>
@@ -22056,7 +22056,7 @@
         <v>29166.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>637886.6</v>
       </c>
       <c r="L6" t="n">
         <v>215293.16</v>
@@ -22094,7 +22094,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>69975.52</v>
       </c>
       <c r="L7" t="n">
         <v>48833.28</v>

--- a/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,13 +511,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>155475.09</v>
+        <v>155326.05</v>
       </c>
       <c r="C4" t="n">
         <v>30190608</v>
@@ -532,7 +537,7 @@
         <v>162</v>
       </c>
       <c r="G4" t="n">
-        <v>477060</v>
+        <v>474660</v>
       </c>
       <c r="H4" t="n">
         <v>75570</v>
@@ -544,10 +549,13 @@
         <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="L4" t="n">
-        <v>1290060</v>
+        <v>1287210</v>
+      </c>
+      <c r="M4" t="n">
+        <v>72930</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +563,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>115810.92</v>
+        <v>115685.46</v>
       </c>
       <c r="C5" t="n">
         <v>19053216</v>
@@ -570,7 +578,7 @@
         <v>75</v>
       </c>
       <c r="G5" t="n">
-        <v>356490</v>
+        <v>354990</v>
       </c>
       <c r="H5" t="n">
         <v>65610</v>
@@ -582,10 +590,13 @@
         <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>714</v>
+        <v>705</v>
       </c>
       <c r="L5" t="n">
-        <v>932970</v>
+        <v>930960</v>
+      </c>
+      <c r="M5" t="n">
+        <v>45720</v>
       </c>
     </row>
     <row r="6">
@@ -593,7 +604,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>84995.10000000001</v>
+        <v>84871.53</v>
       </c>
       <c r="C6" t="n">
         <v>10161144</v>
@@ -608,7 +619,7 @@
         <v>29</v>
       </c>
       <c r="G6" t="n">
-        <v>244440</v>
+        <v>243690</v>
       </c>
       <c r="H6" t="n">
         <v>19050</v>
@@ -620,10 +631,13 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L6" t="n">
-        <v>566070</v>
+        <v>564330</v>
+      </c>
+      <c r="M6" t="n">
+        <v>22110</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +645,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>65121.48</v>
+        <v>65076.39</v>
       </c>
       <c r="C7" t="n">
         <v>6274296</v>
@@ -646,7 +660,7 @@
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>145080</v>
+        <v>144630</v>
       </c>
       <c r="H7" t="n">
         <v>5820</v>
@@ -661,7 +675,10 @@
         <v>307</v>
       </c>
       <c r="L7" t="n">
-        <v>335640</v>
+        <v>334620</v>
+      </c>
+      <c r="M7" t="n">
+        <v>14250</v>
       </c>
     </row>
     <row r="8">
@@ -669,7 +686,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>42680.43</v>
+        <v>42680.16</v>
       </c>
       <c r="C8" t="n">
         <v>3645936</v>
@@ -684,7 +701,7 @@
         <v>28</v>
       </c>
       <c r="G8" t="n">
-        <v>113190</v>
+        <v>112740</v>
       </c>
       <c r="H8" t="n">
         <v>5730</v>
@@ -699,7 +716,10 @@
         <v>187</v>
       </c>
       <c r="L8" t="n">
-        <v>236520</v>
+        <v>235830</v>
+      </c>
+      <c r="M8" t="n">
+        <v>9510</v>
       </c>
     </row>
     <row r="9">
@@ -707,7 +727,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>27402.03</v>
+        <v>27401.94</v>
       </c>
       <c r="C9" t="n">
         <v>2064384</v>
@@ -722,7 +742,7 @@
         <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>72570</v>
+        <v>72240</v>
       </c>
       <c r="H9" t="n">
         <v>3330</v>
@@ -737,7 +757,10 @@
         <v>145</v>
       </c>
       <c r="L9" t="n">
-        <v>189810</v>
+        <v>189450</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4920</v>
       </c>
     </row>
     <row r="10">
@@ -745,7 +768,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17281.53</v>
+        <v>17281.26</v>
       </c>
       <c r="C10" t="n">
         <v>1101240</v>
@@ -775,7 +798,10 @@
         <v>82</v>
       </c>
       <c r="L10" t="n">
-        <v>98130</v>
+        <v>98040</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2790</v>
       </c>
     </row>
     <row r="11">
@@ -813,7 +839,10 @@
         <v>32</v>
       </c>
       <c r="L11" t="n">
-        <v>47460</v>
+        <v>47190</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2850</v>
       </c>
     </row>
     <row r="12">
@@ -851,7 +880,10 @@
         <v>10</v>
       </c>
       <c r="L12" t="n">
-        <v>17130</v>
+        <v>16920</v>
+      </c>
+      <c r="M12" t="n">
+        <v>660</v>
       </c>
     </row>
     <row r="13">
@@ -891,6 +923,9 @@
       <c r="L13" t="n">
         <v>5400</v>
       </c>
+      <c r="M13" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -929,6 +964,9 @@
       <c r="L14" t="n">
         <v>2520</v>
       </c>
+      <c r="M14" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -967,6 +1005,9 @@
       <c r="L15" t="n">
         <v>1470</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1005,6 +1046,9 @@
       <c r="L16" t="n">
         <v>1470</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1043,6 +1087,9 @@
       <c r="L17" t="n">
         <v>570</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1081,6 +1128,9 @@
       <c r="L18" t="n">
         <v>360</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1119,6 +1169,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1157,6 +1210,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1195,6 +1251,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1233,6 +1292,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1271,6 +1333,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1309,6 +1374,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -1358,6 +1426,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -1372,7 +1444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1443,6 +1515,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1464,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>10320</v>
+        <v>10560</v>
       </c>
       <c r="H4" t="n">
         <v>3240</v>
@@ -1479,7 +1556,10 @@
         <v>24</v>
       </c>
       <c r="L4" t="n">
-        <v>35820</v>
+        <v>36030</v>
+      </c>
+      <c r="M4" t="n">
+        <v>12270</v>
       </c>
     </row>
     <row r="5">
@@ -1487,7 +1567,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3140.1</v>
+        <v>3140.01</v>
       </c>
       <c r="C5" t="n">
         <v>827064</v>
@@ -1502,7 +1582,7 @@
         <v>11</v>
       </c>
       <c r="G5" t="n">
-        <v>18720</v>
+        <v>18780</v>
       </c>
       <c r="H5" t="n">
         <v>2940</v>
@@ -1517,7 +1597,10 @@
         <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>52170</v>
+        <v>52440</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14910</v>
       </c>
     </row>
     <row r="6">
@@ -1540,7 +1623,7 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>23340</v>
+        <v>23310</v>
       </c>
       <c r="H6" t="n">
         <v>5550</v>
@@ -1555,7 +1638,10 @@
         <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>55620</v>
+        <v>55650</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7170</v>
       </c>
     </row>
     <row r="7">
@@ -1578,7 +1664,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>16620</v>
+        <v>16650</v>
       </c>
       <c r="H7" t="n">
         <v>3720</v>
@@ -1594,6 +1680,9 @@
       </c>
       <c r="L7" t="n">
         <v>49740</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4440</v>
       </c>
     </row>
     <row r="8">
@@ -1616,7 +1705,7 @@
         <v>14</v>
       </c>
       <c r="G8" t="n">
-        <v>28260</v>
+        <v>28290</v>
       </c>
       <c r="H8" t="n">
         <v>5400</v>
@@ -1631,7 +1720,10 @@
         <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>73170</v>
+        <v>73500</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2220</v>
       </c>
     </row>
     <row r="9">
@@ -1669,7 +1761,10 @@
         <v>48</v>
       </c>
       <c r="L9" t="n">
-        <v>93150</v>
+        <v>93120</v>
+      </c>
+      <c r="M9" t="n">
+        <v>630</v>
       </c>
     </row>
     <row r="10">
@@ -1707,7 +1802,10 @@
         <v>27</v>
       </c>
       <c r="L10" t="n">
-        <v>50670</v>
+        <v>50790</v>
+      </c>
+      <c r="M10" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="11">
@@ -1730,7 +1828,7 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>9900</v>
+        <v>9930</v>
       </c>
       <c r="H11" t="n">
         <v>750</v>
@@ -1745,7 +1843,10 @@
         <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>23910</v>
+        <v>23970</v>
+      </c>
+      <c r="M11" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -1783,7 +1884,10 @@
         <v>7</v>
       </c>
       <c r="L12" t="n">
-        <v>10830</v>
+        <v>10860</v>
+      </c>
+      <c r="M12" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="13">
@@ -1823,6 +1927,9 @@
       <c r="L13" t="n">
         <v>3480</v>
       </c>
+      <c r="M13" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1861,6 +1968,9 @@
       <c r="L14" t="n">
         <v>1290</v>
       </c>
+      <c r="M14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1899,6 +2009,9 @@
       <c r="L15" t="n">
         <v>900</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1937,6 +2050,9 @@
       <c r="L16" t="n">
         <v>1050</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1975,6 +2091,9 @@
       <c r="L17" t="n">
         <v>30</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2013,6 +2132,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2051,6 +2173,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2089,6 +2214,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2127,6 +2255,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2165,6 +2296,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2203,6 +2337,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2241,6 +2378,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2290,6 +2430,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -2304,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2375,6 +2519,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2411,6 +2560,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2419,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>1413.04</v>
+        <v>1413</v>
       </c>
       <c r="C5" t="n">
         <v>454885.2</v>
@@ -2446,10 +2598,13 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>14.28</v>
+        <v>11.25</v>
       </c>
       <c r="L5" t="n">
-        <v>10955.7</v>
+        <v>11012.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>298.2</v>
       </c>
     </row>
     <row r="6">
@@ -2472,22 +2627,25 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1167</v>
+        <v>1165.5</v>
       </c>
       <c r="H6" t="n">
         <v>3163.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.35</v>
+        <v>0.51</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>21.45</v>
+        <v>16.73</v>
       </c>
       <c r="L6" t="n">
-        <v>20579.4</v>
+        <v>20590.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>573.6</v>
       </c>
     </row>
     <row r="7">
@@ -2510,7 +2668,7 @@
         <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>2493</v>
+        <v>2497.5</v>
       </c>
       <c r="H7" t="n">
         <v>2715.6</v>
@@ -2522,10 +2680,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>18.04</v>
+        <v>14.04</v>
       </c>
       <c r="L7" t="n">
         <v>29844</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1554</v>
       </c>
     </row>
     <row r="8">
@@ -2548,22 +2709,25 @@
         <v>13.3</v>
       </c>
       <c r="G8" t="n">
-        <v>18369</v>
+        <v>18388.5</v>
       </c>
       <c r="H8" t="n">
         <v>4590</v>
       </c>
       <c r="I8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="J8" t="n">
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>27.9</v>
+        <v>22.82</v>
       </c>
       <c r="L8" t="n">
-        <v>51950.7</v>
+        <v>52185</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1332</v>
       </c>
     </row>
     <row r="9">
@@ -2598,10 +2762,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>48</v>
+        <v>38.54</v>
       </c>
       <c r="L9" t="n">
-        <v>75451.5</v>
+        <v>75427.2</v>
+      </c>
+      <c r="M9" t="n">
+        <v>630</v>
       </c>
     </row>
     <row r="10">
@@ -2636,10 +2803,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>23.49</v>
       </c>
       <c r="L10" t="n">
-        <v>45096.3</v>
+        <v>45203.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="11">
@@ -2662,22 +2832,25 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>9900</v>
+        <v>9930</v>
       </c>
       <c r="H11" t="n">
         <v>750</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>10.78</v>
       </c>
       <c r="L11" t="n">
-        <v>23910</v>
+        <v>23970</v>
+      </c>
+      <c r="M11" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="12">
@@ -2712,10 +2885,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>6.49</v>
       </c>
       <c r="L12" t="n">
-        <v>10830</v>
+        <v>10860</v>
+      </c>
+      <c r="M12" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="13">
@@ -2750,10 +2926,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="L13" t="n">
         <v>3480</v>
+      </c>
+      <c r="M13" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2793,6 +2972,9 @@
       <c r="L14" t="n">
         <v>1290</v>
       </c>
+      <c r="M14" t="n">
+        <v>180</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2831,6 +3013,9 @@
       <c r="L15" t="n">
         <v>900</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2869,6 +3054,9 @@
       <c r="L16" t="n">
         <v>1050</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2907,6 +3095,9 @@
       <c r="L17" t="n">
         <v>30</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2945,6 +3136,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2983,6 +3177,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3021,6 +3218,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3059,6 +3259,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3097,6 +3300,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3135,6 +3341,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3382,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3222,6 +3434,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -3236,7 +3452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3307,6 +3523,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3343,6 +3564,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3351,16 +3575,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>3108699</v>
+        <v>3108609.9</v>
       </c>
       <c r="C5" t="n">
-        <v>25018686</v>
+        <v>19105178.4</v>
       </c>
       <c r="D5" t="n">
-        <v>21795648.9</v>
+        <v>41298377.47</v>
       </c>
       <c r="E5" t="n">
-        <v>10242122.69</v>
+        <v>19178964</v>
       </c>
       <c r="F5" t="n">
         <v>9166.74</v>
@@ -3369,19 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>292806.36</v>
+        <v>6032880</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>17499.9</v>
+        <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>304649.52</v>
+        <v>546449.22</v>
       </c>
       <c r="L5" t="n">
-        <v>103202.69</v>
+        <v>1982232</v>
+      </c>
+      <c r="M5" t="n">
+        <v>89460</v>
       </c>
     </row>
     <row r="6">
@@ -3392,34 +3619,37 @@
         <v>10048104</v>
       </c>
       <c r="C6" t="n">
-        <v>44083116</v>
+        <v>33663470.4</v>
       </c>
       <c r="D6" t="n">
-        <v>35948248.68</v>
+        <v>68114711.81</v>
       </c>
       <c r="E6" t="n">
-        <v>14067497.81</v>
+        <v>26342199</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>21589.5</v>
+        <v>62937</v>
       </c>
       <c r="H6" t="n">
-        <v>875182.27</v>
+        <v>18031950</v>
       </c>
       <c r="I6" t="n">
-        <v>134165.5</v>
+        <v>98471.57000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>457614.3</v>
+        <v>812390.4399999999</v>
       </c>
       <c r="L6" t="n">
-        <v>193857.95</v>
+        <v>3706290</v>
+      </c>
+      <c r="M6" t="n">
+        <v>172080</v>
       </c>
     </row>
     <row r="7">
@@ -3430,34 +3660,37 @@
         <v>13236973.2</v>
       </c>
       <c r="C7" t="n">
-        <v>37616040</v>
+        <v>28724976</v>
       </c>
       <c r="D7" t="n">
-        <v>34740315.24</v>
+        <v>65825920.51</v>
       </c>
       <c r="E7" t="n">
-        <v>9452108.939999999</v>
+        <v>17699617.8</v>
       </c>
       <c r="F7" t="n">
         <v>50000.4</v>
       </c>
       <c r="G7" t="n">
-        <v>46120.5</v>
+        <v>134865</v>
       </c>
       <c r="H7" t="n">
-        <v>751270.74</v>
+        <v>15478920</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>384865.36</v>
+        <v>681532.02</v>
       </c>
       <c r="L7" t="n">
-        <v>281130.48</v>
+        <v>5371920</v>
+      </c>
+      <c r="M7" t="n">
+        <v>466200</v>
       </c>
     </row>
     <row r="8">
@@ -3468,34 +3701,37 @@
         <v>13419450</v>
       </c>
       <c r="C8" t="n">
-        <v>36812160</v>
+        <v>28111104</v>
       </c>
       <c r="D8" t="n">
-        <v>39220138.05</v>
+        <v>74314285.06</v>
       </c>
       <c r="E8" t="n">
-        <v>9599220.890000001</v>
+        <v>17975093.4</v>
       </c>
       <c r="F8" t="n">
         <v>554171.1</v>
       </c>
       <c r="G8" t="n">
-        <v>339826.5</v>
+        <v>992979</v>
       </c>
       <c r="H8" t="n">
-        <v>1269823.5</v>
+        <v>26163000</v>
       </c>
       <c r="I8" t="n">
-        <v>551995.2</v>
+        <v>285897.73</v>
       </c>
       <c r="J8" t="n">
-        <v>99166.10000000001</v>
+        <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>595218.6</v>
+        <v>1107853.7</v>
       </c>
       <c r="L8" t="n">
-        <v>489375.59</v>
+        <v>9393300</v>
+      </c>
+      <c r="M8" t="n">
+        <v>399600</v>
       </c>
     </row>
     <row r="9">
@@ -3506,22 +3742,22 @@
         <v>15843564</v>
       </c>
       <c r="C9" t="n">
-        <v>32210640</v>
+        <v>24597216</v>
       </c>
       <c r="D9" t="n">
-        <v>37441643.33</v>
+        <v>70944394.75</v>
       </c>
       <c r="E9" t="n">
-        <v>6436396.76</v>
+        <v>12052523.25</v>
       </c>
       <c r="F9" t="n">
         <v>291669</v>
       </c>
       <c r="G9" t="n">
-        <v>546286.5</v>
+        <v>1594566</v>
       </c>
       <c r="H9" t="n">
-        <v>904645.5</v>
+        <v>18639000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3530,10 +3766,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1024032</v>
+        <v>1871542.46</v>
       </c>
       <c r="L9" t="n">
-        <v>710753.13</v>
+        <v>13576896</v>
+      </c>
+      <c r="M9" t="n">
+        <v>189000</v>
       </c>
     </row>
     <row r="10">
@@ -3544,22 +3783,22 @@
         <v>11534094</v>
       </c>
       <c r="C10" t="n">
-        <v>21483000</v>
+        <v>16405200</v>
       </c>
       <c r="D10" t="n">
-        <v>27055413.99</v>
+        <v>51264576</v>
       </c>
       <c r="E10" t="n">
-        <v>6010830</v>
+        <v>11255625</v>
       </c>
       <c r="F10" t="n">
         <v>208335</v>
       </c>
       <c r="G10" t="n">
-        <v>447885</v>
+        <v>1307340</v>
       </c>
       <c r="H10" t="n">
-        <v>248985</v>
+        <v>5130000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3568,10 +3807,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>576018</v>
+        <v>1140580.44</v>
       </c>
       <c r="L10" t="n">
-        <v>424807.15</v>
+        <v>8136558</v>
+      </c>
+      <c r="M10" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="11">
@@ -3582,34 +3824,37 @@
         <v>4898718</v>
       </c>
       <c r="C11" t="n">
-        <v>13083840</v>
+        <v>9991296</v>
       </c>
       <c r="D11" t="n">
-        <v>17017403.97</v>
+        <v>32244562.94</v>
       </c>
       <c r="E11" t="n">
-        <v>3125764.25</v>
+        <v>5853173.4</v>
       </c>
       <c r="F11" t="n">
         <v>83334</v>
       </c>
       <c r="G11" t="n">
-        <v>183150</v>
+        <v>536220</v>
       </c>
       <c r="H11" t="n">
-        <v>207487.5</v>
+        <v>4275000</v>
       </c>
       <c r="I11" t="n">
-        <v>383330</v>
+        <v>174510.26</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>256008</v>
+        <v>523530.79</v>
       </c>
       <c r="L11" t="n">
-        <v>225232.2</v>
+        <v>4314600</v>
+      </c>
+      <c r="M11" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="12">
@@ -3620,22 +3865,22 @@
         <v>2987820</v>
       </c>
       <c r="C12" t="n">
-        <v>5959800</v>
+        <v>4551120</v>
       </c>
       <c r="D12" t="n">
-        <v>7997447.96</v>
+        <v>15153557.76</v>
       </c>
       <c r="E12" t="n">
-        <v>2060761.25</v>
+        <v>3858894</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>77145</v>
+        <v>225180</v>
       </c>
       <c r="H12" t="n">
-        <v>41497.5</v>
+        <v>855000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3644,10 +3889,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>149338</v>
+        <v>315079.88</v>
       </c>
       <c r="L12" t="n">
-        <v>102018.6</v>
+        <v>1954800</v>
+      </c>
+      <c r="M12" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="13">
@@ -3658,22 +3906,22 @@
         <v>1269774</v>
       </c>
       <c r="C13" t="n">
-        <v>1496880</v>
+        <v>1143072</v>
       </c>
       <c r="D13" t="n">
-        <v>2057415.26</v>
+        <v>3898388.74</v>
       </c>
       <c r="E13" t="n">
-        <v>350999.31</v>
+        <v>657266.4</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>19980</v>
+        <v>58320</v>
       </c>
       <c r="H13" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3682,10 +3930,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>42668</v>
+        <v>92207.84</v>
       </c>
       <c r="L13" t="n">
-        <v>32781.6</v>
+        <v>626400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="14">
@@ -3696,10 +3947,10 @@
         <v>1120878</v>
       </c>
       <c r="C14" t="n">
-        <v>471240</v>
+        <v>359856</v>
       </c>
       <c r="D14" t="n">
-        <v>663053.26</v>
+        <v>1256352.77</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -3708,10 +3959,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>5550</v>
+        <v>16200</v>
       </c>
       <c r="H14" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3723,7 +3974,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>12151.8</v>
+        <v>232200</v>
+      </c>
+      <c r="M14" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="15">
@@ -3734,10 +3988,10 @@
         <v>401148</v>
       </c>
       <c r="C15" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D15" t="n">
-        <v>237389.44</v>
+        <v>449805.31</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -3746,10 +4000,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H15" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3761,7 +4015,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>8478</v>
+        <v>162000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3772,10 +4029,10 @@
         <v>269280</v>
       </c>
       <c r="C16" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D16" t="n">
-        <v>160506.72</v>
+        <v>304128</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -3799,7 +4056,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>9891</v>
+        <v>189000</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3825,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3837,7 +4097,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3877,6 +4140,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3915,6 +4181,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3953,6 +4222,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3991,6 +4263,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4029,6 +4304,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4067,6 +4345,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -4105,6 +4386,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -4154,6 +4438,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -4168,7 +4456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4239,6 +4527,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -4260,7 +4553,7 @@
         <v>18</v>
       </c>
       <c r="G4" t="n">
-        <v>30630</v>
+        <v>30690</v>
       </c>
       <c r="H4" t="n">
         <v>1710</v>
@@ -4275,7 +4568,10 @@
         <v>44</v>
       </c>
       <c r="L4" t="n">
-        <v>103020</v>
+        <v>103230</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -4298,7 +4594,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>9810</v>
+        <v>9840</v>
       </c>
       <c r="H5" t="n">
         <v>480</v>
@@ -4313,7 +4609,10 @@
         <v>15</v>
       </c>
       <c r="L5" t="n">
-        <v>35070</v>
+        <v>35310</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4353,6 +4652,9 @@
       <c r="L6" t="n">
         <v>8190</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4391,6 +4693,9 @@
       <c r="L7" t="n">
         <v>1560</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4429,6 +4734,9 @@
       <c r="L8" t="n">
         <v>360</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4467,6 +4775,9 @@
       <c r="L9" t="n">
         <v>150</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4505,6 +4816,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4543,6 +4857,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4581,6 +4898,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4619,6 +4939,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4657,6 +4980,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4695,6 +5021,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4733,6 +5062,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4771,6 +5103,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4809,6 +5144,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4847,6 +5185,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4885,6 +5226,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4923,6 +5267,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -4961,6 +5308,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -4999,6 +5349,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5037,6 +5390,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -5086,6 +5442,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -5100,7 +5460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5171,6 +5531,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -5207,6 +5572,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5242,10 +5610,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.3</v>
+        <v>4.96</v>
       </c>
       <c r="L5" t="n">
-        <v>7364.7</v>
+        <v>7415.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5280,10 +5651,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -5323,6 +5697,9 @@
       <c r="L7" t="n">
         <v>936</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5361,6 +5738,9 @@
       <c r="L8" t="n">
         <v>255.6</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5399,6 +5779,9 @@
       <c r="L9" t="n">
         <v>121.5</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -5437,6 +5820,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -5475,6 +5861,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -5513,6 +5902,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -5551,6 +5943,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -5589,6 +5984,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -5627,6 +6025,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -5665,6 +6066,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -5703,6 +6107,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -5741,6 +6148,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -5779,6 +6189,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5817,6 +6230,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5855,6 +6271,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -5893,6 +6312,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -5931,6 +6353,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -5969,6 +6394,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6018,6 +6446,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6032,7 +6464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6103,6 +6535,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -6139,6 +6576,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6150,13 +6590,13 @@
         <v>2901541.5</v>
       </c>
       <c r="C5" t="n">
-        <v>12440736</v>
+        <v>9500198.4</v>
       </c>
       <c r="D5" t="n">
-        <v>10838055.76</v>
+        <v>20535939.07</v>
       </c>
       <c r="E5" t="n">
-        <v>2395925.13</v>
+        <v>4486507.65</v>
       </c>
       <c r="F5" t="n">
         <v>2500.02</v>
@@ -6165,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>47805.12</v>
+        <v>984960</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -6174,10 +6614,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>134404.2</v>
+        <v>241080.54</v>
       </c>
       <c r="L5" t="n">
-        <v>69375.47</v>
+        <v>1334718</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -6188,22 +6631,22 @@
         <v>315849.6</v>
       </c>
       <c r="C6" t="n">
-        <v>4191264</v>
+        <v>3200601.6</v>
       </c>
       <c r="D6" t="n">
-        <v>3417830.1</v>
+        <v>6476101.63</v>
       </c>
       <c r="E6" t="n">
-        <v>1345099.39</v>
+        <v>2518776</v>
       </c>
       <c r="F6" t="n">
         <v>16666.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1526.25</v>
+        <v>4455</v>
       </c>
       <c r="H6" t="n">
-        <v>23653.57</v>
+        <v>487350</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -6212,10 +6655,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>27734.2</v>
+        <v>49235.78</v>
       </c>
       <c r="L6" t="n">
-        <v>28545.43</v>
+        <v>545454</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -6226,19 +6672,19 @@
         <v>68280.3</v>
       </c>
       <c r="C7" t="n">
-        <v>748440</v>
+        <v>571536</v>
       </c>
       <c r="D7" t="n">
-        <v>691222.1899999999</v>
+        <v>1309727.23</v>
       </c>
       <c r="E7" t="n">
-        <v>70538.13</v>
+        <v>132086.7</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>666</v>
+        <v>1944</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -6253,7 +6699,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8817.120000000001</v>
+        <v>168480</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -6264,10 +6713,10 @@
         <v>38412</v>
       </c>
       <c r="C8" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D8" t="n">
-        <v>88599.71000000001</v>
+        <v>167878.66</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -6276,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2525.25</v>
+        <v>7371</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -6291,7 +6740,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2407.75</v>
+        <v>46008</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -6302,13 +6754,13 @@
         <v>24750</v>
       </c>
       <c r="C9" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D9" t="n">
-        <v>96665.17</v>
+        <v>183161.09</v>
       </c>
       <c r="E9" t="n">
-        <v>44388.94</v>
+        <v>83120.85000000001</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -6329,7 +6781,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1144.53</v>
+        <v>21870</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -6369,6 +6824,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6407,6 +6865,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -6445,6 +6906,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -6483,6 +6947,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -6521,6 +6988,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -6559,6 +7029,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -6597,6 +7070,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -6635,6 +7111,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -6673,6 +7152,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -6711,6 +7193,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -6749,6 +7234,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -6787,6 +7275,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -6825,6 +7316,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -6863,6 +7357,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -6901,6 +7398,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -6950,6 +7450,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -6964,7 +7468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7035,6 +7539,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -7056,7 +7565,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>42390</v>
+        <v>42450</v>
       </c>
       <c r="H4" t="n">
         <v>3390</v>
@@ -7071,7 +7580,10 @@
         <v>64</v>
       </c>
       <c r="L4" t="n">
-        <v>53850</v>
+        <v>53880</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7111,6 +7623,9 @@
       <c r="L5" t="n">
         <v>13770</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -7149,6 +7664,9 @@
       <c r="L6" t="n">
         <v>2640</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -7187,6 +7705,9 @@
       <c r="L7" t="n">
         <v>510</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -7225,6 +7746,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -7263,6 +7787,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -7301,6 +7828,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -7339,6 +7869,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7377,6 +7910,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7415,6 +7951,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7453,6 +7992,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -7491,6 +8033,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -7529,6 +8074,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -7567,6 +8115,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -7605,6 +8156,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -7643,6 +8197,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -7681,6 +8238,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -7719,6 +8279,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -7757,6 +8320,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -7795,6 +8361,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -7833,6 +8402,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -7882,6 +8454,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -7896,7 +8472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,6 +8543,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8003,6 +8584,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8038,10 +8622,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>3.78</v>
+        <v>2.98</v>
       </c>
       <c r="L5" t="n">
         <v>2891.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8076,10 +8663,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -8114,10 +8704,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.64</v>
+        <v>1.28</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -8157,6 +8750,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -8195,6 +8791,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -8233,6 +8832,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -8271,6 +8873,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -8309,6 +8914,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -8347,6 +8955,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8385,6 +8996,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8423,6 +9037,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8461,6 +9078,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -8499,6 +9119,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -8537,6 +9160,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -8575,6 +9201,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -8613,6 +9242,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -8651,6 +9283,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -8689,6 +9324,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -8727,6 +9365,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -8765,6 +9406,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -8814,6 +9458,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -8828,7 +9476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8899,6 +9547,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -8935,6 +9588,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8946,13 +9602,13 @@
         <v>2269733.4</v>
       </c>
       <c r="C5" t="n">
-        <v>7912674</v>
+        <v>6042405.6</v>
       </c>
       <c r="D5" t="n">
-        <v>6893322.23</v>
+        <v>13061461.25</v>
       </c>
       <c r="E5" t="n">
-        <v>658422.17</v>
+        <v>1232933.4</v>
       </c>
       <c r="F5" t="n">
         <v>1666.68</v>
@@ -8961,7 +9617,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>250976.88</v>
+        <v>5171040</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8970,10 +9626,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>80642.52</v>
+        <v>144648.32</v>
       </c>
       <c r="L5" t="n">
-        <v>27239.81</v>
+        <v>520506</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -8984,22 +9643,22 @@
         <v>646113.6</v>
       </c>
       <c r="C6" t="n">
-        <v>2370060</v>
+        <v>1809864</v>
       </c>
       <c r="D6" t="n">
-        <v>1932701.54</v>
+        <v>3662081.28</v>
       </c>
       <c r="E6" t="n">
-        <v>280229.04</v>
+        <v>524745</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>2608.5</v>
+        <v>7614</v>
       </c>
       <c r="H6" t="n">
-        <v>66230.00999999999</v>
+        <v>1364580</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9008,10 +9667,13 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>41601.3</v>
+        <v>73853.67999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>9201.459999999999</v>
+        <v>175824</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9022,10 +9684,10 @@
         <v>146718</v>
       </c>
       <c r="C7" t="n">
-        <v>332640</v>
+        <v>254016</v>
       </c>
       <c r="D7" t="n">
-        <v>307209.86</v>
+        <v>582100.99</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -9034,7 +9696,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2081.25</v>
+        <v>6075</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -9046,10 +9708,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>34987.76</v>
+        <v>61957.46</v>
       </c>
       <c r="L7" t="n">
-        <v>2882.52</v>
+        <v>55080</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9060,10 +9725,10 @@
         <v>25740</v>
       </c>
       <c r="C8" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D8" t="n">
-        <v>29533.24</v>
+        <v>55959.55</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -9087,6 +9752,9 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9127,6 +9795,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -9165,6 +9836,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -9203,6 +9877,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -9241,6 +9918,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -9279,6 +9959,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -9317,6 +10000,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -9355,6 +10041,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -9393,6 +10082,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9431,6 +10123,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -9469,6 +10164,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -9507,6 +10205,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -9545,6 +10246,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -9583,6 +10287,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -9621,6 +10328,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -9659,6 +10369,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -9697,6 +10410,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -9746,6 +10462,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -9760,7 +10480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9831,6 +10551,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -9852,10 +10577,10 @@
         <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>100230</v>
+        <v>100320</v>
       </c>
       <c r="H4" t="n">
-        <v>10110</v>
+        <v>10080</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -9867,7 +10592,10 @@
         <v>228</v>
       </c>
       <c r="L4" t="n">
-        <v>230460</v>
+        <v>230880</v>
+      </c>
+      <c r="M4" t="n">
+        <v>19110</v>
       </c>
     </row>
     <row r="5">
@@ -9890,10 +10618,10 @@
         <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>99990</v>
+        <v>100080</v>
       </c>
       <c r="H5" t="n">
-        <v>12960</v>
+        <v>12930</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -9905,7 +10633,10 @@
         <v>269</v>
       </c>
       <c r="L5" t="n">
-        <v>265500</v>
+        <v>265440</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14970</v>
       </c>
     </row>
     <row r="6">
@@ -9928,10 +10659,10 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>62220</v>
+        <v>62160</v>
       </c>
       <c r="H6" t="n">
-        <v>5220</v>
+        <v>5250</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
@@ -9943,7 +10674,10 @@
         <v>111</v>
       </c>
       <c r="L6" t="n">
-        <v>124020</v>
+        <v>124110</v>
+      </c>
+      <c r="M6" t="n">
+        <v>6900</v>
       </c>
     </row>
     <row r="7">
@@ -9966,7 +10700,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>39660</v>
+        <v>39810</v>
       </c>
       <c r="H7" t="n">
         <v>780</v>
@@ -9978,10 +10712,13 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L7" t="n">
-        <v>69480</v>
+        <v>69540</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3750</v>
       </c>
     </row>
     <row r="8">
@@ -10021,6 +10758,9 @@
       <c r="L8" t="n">
         <v>32610</v>
       </c>
+      <c r="M8" t="n">
+        <v>2130</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -10059,6 +10799,9 @@
       <c r="L9" t="n">
         <v>8430</v>
       </c>
+      <c r="M9" t="n">
+        <v>1020</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -10097,6 +10840,9 @@
       <c r="L10" t="n">
         <v>3720</v>
       </c>
+      <c r="M10" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -10135,6 +10881,9 @@
       <c r="L11" t="n">
         <v>3540</v>
       </c>
+      <c r="M11" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -10173,6 +10922,9 @@
       <c r="L12" t="n">
         <v>1530</v>
       </c>
+      <c r="M12" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -10211,6 +10963,9 @@
       <c r="L13" t="n">
         <v>450</v>
       </c>
+      <c r="M13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -10249,6 +11004,9 @@
       <c r="L14" t="n">
         <v>180</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -10287,6 +11045,9 @@
       <c r="L15" t="n">
         <v>270</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -10325,6 +11086,9 @@
       <c r="L16" t="n">
         <v>360</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -10363,6 +11127,9 @@
       <c r="L17" t="n">
         <v>450</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10401,6 +11168,9 @@
       <c r="L18" t="n">
         <v>360</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10439,6 +11209,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10477,6 +11250,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -10515,6 +11291,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -10553,6 +11332,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -10591,6 +11373,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -10629,6 +11414,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -10678,6 +11466,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -10692,7 +11484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10763,6 +11555,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -10799,6 +11596,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10807,7 +11607,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>52114.91</v>
+        <v>52058.46</v>
       </c>
       <c r="C5" t="n">
         <v>10479268.8</v>
@@ -10828,16 +11628,19 @@
         <v>23619.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>0.66</v>
       </c>
       <c r="J5" t="n">
         <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>299.88</v>
+        <v>233.36</v>
       </c>
       <c r="L5" t="n">
-        <v>195923.7</v>
+        <v>195501.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>914.4</v>
       </c>
     </row>
     <row r="6">
@@ -10845,7 +11648,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>67996.08</v>
+        <v>67897.22</v>
       </c>
       <c r="C6" t="n">
         <v>9145029.6</v>
@@ -10860,22 +11663,25 @@
         <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>12222</v>
+        <v>12184.5</v>
       </c>
       <c r="H6" t="n">
         <v>10858.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>2.03</v>
       </c>
       <c r="J6" t="n">
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>267.15</v>
+        <v>207.87</v>
       </c>
       <c r="L6" t="n">
-        <v>209445.9</v>
+        <v>208802.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1768.8</v>
       </c>
     </row>
     <row r="7">
@@ -10883,7 +11689,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>61865.41</v>
+        <v>61822.57</v>
       </c>
       <c r="C7" t="n">
         <v>6274296</v>
@@ -10898,7 +11704,7 @@
         <v>9.6</v>
       </c>
       <c r="G7" t="n">
-        <v>21762</v>
+        <v>21694.5</v>
       </c>
       <c r="H7" t="n">
         <v>4248.6</v>
@@ -10910,10 +11716,13 @@
         <v>5.6</v>
       </c>
       <c r="K7" t="n">
-        <v>251.74</v>
+        <v>195.87</v>
       </c>
       <c r="L7" t="n">
-        <v>201384</v>
+        <v>200772</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4987.5</v>
       </c>
     </row>
     <row r="8">
@@ -10921,7 +11730,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>42680.43</v>
+        <v>42680.16</v>
       </c>
       <c r="C8" t="n">
         <v>3645936</v>
@@ -10936,22 +11745,25 @@
         <v>26.6</v>
       </c>
       <c r="G8" t="n">
-        <v>73573.5</v>
+        <v>73281</v>
       </c>
       <c r="H8" t="n">
         <v>4870.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="J8" t="n">
         <v>5.1</v>
       </c>
       <c r="K8" t="n">
-        <v>168.3</v>
+        <v>137.63</v>
       </c>
       <c r="L8" t="n">
-        <v>167929.2</v>
+        <v>167439.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5706</v>
       </c>
     </row>
     <row r="9">
@@ -10959,7 +11771,7 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>27402.03</v>
+        <v>27401.94</v>
       </c>
       <c r="C9" t="n">
         <v>2064384</v>
@@ -10974,7 +11786,7 @@
         <v>26</v>
       </c>
       <c r="G9" t="n">
-        <v>61684.5</v>
+        <v>61404</v>
       </c>
       <c r="H9" t="n">
         <v>3330</v>
@@ -10986,10 +11798,13 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>145</v>
+        <v>116.44</v>
       </c>
       <c r="L9" t="n">
-        <v>153746.1</v>
+        <v>153454.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>4920</v>
       </c>
     </row>
     <row r="10">
@@ -10997,7 +11812,7 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>17281.53</v>
+        <v>17281.26</v>
       </c>
       <c r="C10" t="n">
         <v>1101240</v>
@@ -11024,10 +11839,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>82</v>
+        <v>71.34</v>
       </c>
       <c r="L10" t="n">
-        <v>87335.7</v>
+        <v>87255.60000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2790</v>
       </c>
     </row>
     <row r="11">
@@ -11056,16 +11874,19 @@
         <v>810</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>28.75</v>
       </c>
       <c r="L11" t="n">
-        <v>47460</v>
+        <v>47190</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2850</v>
       </c>
     </row>
     <row r="12">
@@ -11100,10 +11921,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>9.27</v>
       </c>
       <c r="L12" t="n">
-        <v>17130</v>
+        <v>16920</v>
+      </c>
+      <c r="M12" t="n">
+        <v>660</v>
       </c>
     </row>
     <row r="13">
@@ -11138,10 +11962,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="L13" t="n">
         <v>5400</v>
+      </c>
+      <c r="M13" t="n">
+        <v>180</v>
       </c>
     </row>
     <row r="14">
@@ -11181,6 +12008,9 @@
       <c r="L14" t="n">
         <v>2520</v>
       </c>
+      <c r="M14" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -11214,10 +12044,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>1470</v>
+      </c>
+      <c r="M15" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -11257,6 +12090,9 @@
       <c r="L16" t="n">
         <v>1470</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -11295,6 +12131,9 @@
       <c r="L17" t="n">
         <v>570</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -11333,6 +12172,9 @@
       <c r="L18" t="n">
         <v>360</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -11371,6 +12213,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11409,6 +12254,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11447,6 +12295,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11485,6 +12336,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -11523,6 +12377,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -11561,6 +12418,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -11610,6 +12470,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -11624,7 +12488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11695,6 +12559,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -11731,6 +12600,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11757,19 +12629,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4665.6</v>
+        <v>4654.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>112.98</v>
+        <v>89.04000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>55755</v>
+        <v>55742.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>299.4</v>
       </c>
     </row>
     <row r="6">
@@ -11792,22 +12667,25 @@
         <v>0.1</v>
       </c>
       <c r="G6" t="n">
-        <v>3111</v>
+        <v>3108</v>
       </c>
       <c r="H6" t="n">
-        <v>2975.4</v>
+        <v>2992.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="J6" t="n">
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>72.15000000000001</v>
+        <v>56.28</v>
       </c>
       <c r="L6" t="n">
-        <v>45887.4</v>
+        <v>45920.7</v>
+      </c>
+      <c r="M6" t="n">
+        <v>552</v>
       </c>
     </row>
     <row r="7">
@@ -11830,7 +12708,7 @@
         <v>0.6</v>
       </c>
       <c r="G7" t="n">
-        <v>5949</v>
+        <v>5971.5</v>
       </c>
       <c r="H7" t="n">
         <v>569.4</v>
@@ -11842,10 +12720,13 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>65.59999999999999</v>
+        <v>51.68</v>
       </c>
       <c r="L7" t="n">
-        <v>41688</v>
+        <v>41724</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1312.5</v>
       </c>
     </row>
     <row r="8">
@@ -11874,16 +12755,19 @@
         <v>51</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="J8" t="n">
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>27</v>
+        <v>22.08</v>
       </c>
       <c r="L8" t="n">
         <v>23153.1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1278</v>
       </c>
     </row>
     <row r="9">
@@ -11918,10 +12802,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>5.62</v>
       </c>
       <c r="L9" t="n">
         <v>6828.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1020</v>
       </c>
     </row>
     <row r="10">
@@ -11961,6 +12848,9 @@
       <c r="L10" t="n">
         <v>3310.8</v>
       </c>
+      <c r="M10" t="n">
+        <v>240</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -11999,6 +12889,9 @@
       <c r="L11" t="n">
         <v>3540</v>
       </c>
+      <c r="M11" t="n">
+        <v>360</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -12037,6 +12930,9 @@
       <c r="L12" t="n">
         <v>1530</v>
       </c>
+      <c r="M12" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -12075,6 +12971,9 @@
       <c r="L13" t="n">
         <v>450</v>
       </c>
+      <c r="M13" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -12113,6 +13012,9 @@
       <c r="L14" t="n">
         <v>180</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -12151,6 +13053,9 @@
       <c r="L15" t="n">
         <v>270</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -12189,6 +13094,9 @@
       <c r="L16" t="n">
         <v>360</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -12227,6 +13135,9 @@
       <c r="L17" t="n">
         <v>450</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -12265,6 +13176,9 @@
       <c r="L18" t="n">
         <v>360</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -12303,6 +13217,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -12341,6 +13258,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -12379,6 +13299,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12417,6 +13340,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12455,6 +13381,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12493,6 +13422,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -12542,6 +13474,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -12556,7 +13492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12627,6 +13563,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -12663,6 +13604,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12674,13 +13618,13 @@
         <v>41186564.1</v>
       </c>
       <c r="C5" t="n">
-        <v>172035864</v>
+        <v>131372841.6</v>
       </c>
       <c r="D5" t="n">
-        <v>149873310.31</v>
+        <v>283979824.13</v>
       </c>
       <c r="E5" t="n">
-        <v>22276616.85</v>
+        <v>41714246.7</v>
       </c>
       <c r="F5" t="n">
         <v>8333.4</v>
@@ -12689,19 +13633,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1290738.24</v>
+        <v>26532360</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
-        <v>122499.3</v>
+        <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2410315.32</v>
+        <v>4323377.68</v>
       </c>
       <c r="L5" t="n">
-        <v>525212.1</v>
+        <v>10033632</v>
+      </c>
+      <c r="M5" t="n">
+        <v>89820</v>
       </c>
     </row>
     <row r="6">
@@ -12712,34 +13659,37 @@
         <v>52261387.2</v>
       </c>
       <c r="C6" t="n">
-        <v>116033148</v>
+        <v>88607131.2</v>
       </c>
       <c r="D6" t="n">
-        <v>94620998.66</v>
+        <v>179287789.82</v>
       </c>
       <c r="E6" t="n">
-        <v>7426069.56</v>
+        <v>13905742.5</v>
       </c>
       <c r="F6" t="n">
         <v>4166.7</v>
       </c>
       <c r="G6" t="n">
-        <v>57553.5</v>
+        <v>167832</v>
       </c>
       <c r="H6" t="n">
-        <v>823144.41</v>
+        <v>17057250</v>
       </c>
       <c r="I6" t="n">
-        <v>402496.5</v>
+        <v>295414.7</v>
       </c>
       <c r="J6" t="n">
-        <v>87499.5</v>
+        <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>1539248.1</v>
+        <v>2732586.01</v>
       </c>
       <c r="L6" t="n">
-        <v>432259.31</v>
+        <v>8265726</v>
+      </c>
+      <c r="M6" t="n">
+        <v>165600</v>
       </c>
     </row>
     <row r="7">
@@ -12750,34 +13700,37 @@
         <v>44473987.8</v>
       </c>
       <c r="C7" t="n">
-        <v>77089320</v>
+        <v>58868208</v>
       </c>
       <c r="D7" t="n">
-        <v>71195885.54000001</v>
+        <v>134901904.9</v>
       </c>
       <c r="E7" t="n">
-        <v>3950135.08</v>
+        <v>7396855.2</v>
       </c>
       <c r="F7" t="n">
         <v>25000.2</v>
       </c>
       <c r="G7" t="n">
-        <v>110056.5</v>
+        <v>322461</v>
       </c>
       <c r="H7" t="n">
-        <v>157524.51</v>
+        <v>3245580</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>81666.2</v>
+        <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>1399510.4</v>
+        <v>2509276.97</v>
       </c>
       <c r="L7" t="n">
-        <v>392700.96</v>
+        <v>7510320</v>
+      </c>
+      <c r="M7" t="n">
+        <v>393750</v>
       </c>
     </row>
     <row r="8">
@@ -12788,34 +13741,37 @@
         <v>18596160</v>
       </c>
       <c r="C8" t="n">
-        <v>33485760</v>
+        <v>25570944</v>
       </c>
       <c r="D8" t="n">
-        <v>35676149.67</v>
+        <v>67599138.81999999</v>
       </c>
       <c r="E8" t="n">
-        <v>1016866.62</v>
+        <v>1904141.25</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>130952.25</v>
+        <v>382239</v>
       </c>
       <c r="H8" t="n">
-        <v>14109.15</v>
+        <v>290700</v>
       </c>
       <c r="I8" t="n">
-        <v>275997.6</v>
+        <v>142948.86</v>
       </c>
       <c r="J8" t="n">
-        <v>49583.05</v>
+        <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>576018</v>
+        <v>1072116.48</v>
       </c>
       <c r="L8" t="n">
-        <v>218102.2</v>
+        <v>4167558</v>
+      </c>
+      <c r="M8" t="n">
+        <v>383400</v>
       </c>
     </row>
     <row r="9">
@@ -12826,19 +13782,19 @@
         <v>1519056</v>
       </c>
       <c r="C9" t="n">
-        <v>4379760</v>
+        <v>3344544</v>
       </c>
       <c r="D9" t="n">
-        <v>5091032.4</v>
+        <v>9646483.970000001</v>
       </c>
       <c r="E9" t="n">
-        <v>88777.89</v>
+        <v>166241.7</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>31135.5</v>
+        <v>90882</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -12850,10 +13806,13 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>149338</v>
+        <v>272933.28</v>
       </c>
       <c r="L9" t="n">
-        <v>64322.59</v>
+        <v>1229094</v>
+      </c>
+      <c r="M9" t="n">
+        <v>306000</v>
       </c>
     </row>
     <row r="10">
@@ -12864,10 +13823,10 @@
         <v>499950</v>
       </c>
       <c r="C10" t="n">
-        <v>887040</v>
+        <v>677376</v>
       </c>
       <c r="D10" t="n">
-        <v>1117126.77</v>
+        <v>2116730.88</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -12876,7 +13835,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>12210</v>
+        <v>35640</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -12891,7 +13850,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>31187.74</v>
+        <v>595944</v>
+      </c>
+      <c r="M10" t="n">
+        <v>72000</v>
       </c>
     </row>
     <row r="11">
@@ -12902,10 +13864,10 @@
         <v>459162</v>
       </c>
       <c r="C11" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D11" t="n">
-        <v>252376.75</v>
+        <v>478203.26</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -12914,10 +13876,10 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -12929,7 +13891,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>33346.8</v>
+        <v>637200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="12">
@@ -12940,19 +13905,19 @@
         <v>87120</v>
       </c>
       <c r="C12" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D12" t="n">
-        <v>223184.59</v>
+        <v>422889.98</v>
       </c>
       <c r="E12" t="n">
-        <v>79260.05</v>
+        <v>148419</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>4440</v>
+        <v>12960</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -12967,7 +13932,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>14412.6</v>
+        <v>275400</v>
+      </c>
+      <c r="M12" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="13">
@@ -12978,10 +13946,10 @@
         <v>36036</v>
       </c>
       <c r="C13" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D13" t="n">
-        <v>114300.85</v>
+        <v>216577.15</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -12990,7 +13958,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -13005,7 +13973,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>4239</v>
+        <v>81000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="14">
@@ -13016,19 +13987,19 @@
         <v>36234</v>
       </c>
       <c r="C14" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D14" t="n">
-        <v>117009.4</v>
+        <v>221709.31</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -13043,7 +14014,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1695.6</v>
+        <v>32400</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -13054,10 +14028,10 @@
         <v>17424</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -13066,7 +14040,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1665</v>
+        <v>4860</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -13081,7 +14055,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2543.4</v>
+        <v>48600</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -13092,10 +14069,10 @@
         <v>9504</v>
       </c>
       <c r="C16" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D16" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -13104,7 +14081,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -13119,7 +14096,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>3391.2</v>
+        <v>64800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -13130,10 +14110,10 @@
         <v>1188</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -13142,7 +14122,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3885</v>
+        <v>11340</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -13157,7 +14137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>4239</v>
+        <v>81000</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -13168,10 +14151,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D18" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -13180,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>67710</v>
+        <v>197640</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -13195,7 +14178,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3391.2</v>
+        <v>64800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -13206,10 +14192,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D19" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -13218,7 +14204,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -13233,6 +14219,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13244,10 +14233,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -13271,6 +14260,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13311,6 +14303,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -13320,10 +14315,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -13347,6 +14342,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13358,10 +14356,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -13385,6 +14383,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13396,10 +14397,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D24" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -13423,6 +14424,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13474,6 +14478,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -13488,7 +14496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13559,6 +14567,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -13580,7 +14593,7 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>61770</v>
+        <v>61800</v>
       </c>
       <c r="H4" t="n">
         <v>4620</v>
@@ -13595,7 +14608,10 @@
         <v>78</v>
       </c>
       <c r="L4" t="n">
-        <v>222870</v>
+        <v>225150</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -13618,7 +14634,7 @@
         <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>13080</v>
+        <v>13050</v>
       </c>
       <c r="H5" t="n">
         <v>1140</v>
@@ -13633,7 +14649,10 @@
         <v>19</v>
       </c>
       <c r="L5" t="n">
-        <v>62880</v>
+        <v>62640</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -13656,7 +14675,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="H6" t="n">
         <v>210</v>
@@ -13671,7 +14690,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9930</v>
+        <v>10290</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -13711,6 +14733,9 @@
       <c r="L7" t="n">
         <v>630</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -13749,6 +14774,9 @@
       <c r="L8" t="n">
         <v>180</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -13787,6 +14815,9 @@
       <c r="L9" t="n">
         <v>90</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -13825,6 +14856,9 @@
       <c r="L10" t="n">
         <v>180</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -13863,6 +14897,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -13901,6 +14938,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -13939,6 +14979,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -13977,6 +15020,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14015,6 +15061,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14053,6 +15102,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -14091,6 +15143,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -14129,6 +15184,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -14167,6 +15225,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -14205,6 +15266,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -14243,6 +15307,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -14281,6 +15348,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -14319,6 +15389,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -14357,6 +15430,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -14406,6 +15482,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -14420,7 +15500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14491,6 +15571,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -14527,6 +15612,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14562,10 +15650,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7.98</v>
+        <v>6.29</v>
       </c>
       <c r="L5" t="n">
-        <v>13204.8</v>
+        <v>13154.4</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -14588,7 +15679,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>67.5</v>
+        <v>75</v>
       </c>
       <c r="H6" t="n">
         <v>119.7</v>
@@ -14603,7 +15694,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3674.1</v>
+        <v>3807.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -14643,6 +15737,9 @@
       <c r="L7" t="n">
         <v>378</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -14681,6 +15778,9 @@
       <c r="L8" t="n">
         <v>127.8</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -14719,6 +15819,9 @@
       <c r="L9" t="n">
         <v>72.90000000000001</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -14757,6 +15860,9 @@
       <c r="L10" t="n">
         <v>160.2</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -14795,6 +15901,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -14833,6 +15942,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -14871,6 +15983,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -14909,6 +16024,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -14947,6 +16065,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -14985,6 +16106,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15023,6 +16147,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15061,6 +16188,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -15099,6 +16229,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -15137,6 +16270,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15175,6 +16311,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -15213,6 +16352,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -15251,6 +16393,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -15289,6 +16434,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -15338,6 +16486,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -15352,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15423,6 +16575,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -15459,6 +16616,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -15470,13 +16630,13 @@
         <v>5510478.6</v>
       </c>
       <c r="C5" t="n">
-        <v>13157298</v>
+        <v>10047391.2</v>
       </c>
       <c r="D5" t="n">
-        <v>11462306.52</v>
+        <v>21718768.9</v>
       </c>
       <c r="E5" t="n">
-        <v>3877375.02</v>
+        <v>7260607.8</v>
       </c>
       <c r="F5" t="n">
         <v>5000.04</v>
@@ -15485,7 +16645,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>113537.16</v>
+        <v>2339280</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -15494,10 +16654,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>170245.32</v>
+        <v>305368.68</v>
       </c>
       <c r="L5" t="n">
-        <v>124389.22</v>
+        <v>2367792</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -15508,22 +16671,22 @@
         <v>928857.6</v>
       </c>
       <c r="C6" t="n">
-        <v>2744280</v>
+        <v>2095632</v>
       </c>
       <c r="D6" t="n">
-        <v>2237864.94</v>
+        <v>4240304.64</v>
       </c>
       <c r="E6" t="n">
-        <v>476389.37</v>
+        <v>892066.5</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1248.75</v>
+        <v>4050</v>
       </c>
       <c r="H6" t="n">
-        <v>33115</v>
+        <v>682290</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -15535,7 +16698,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>34610.02</v>
+        <v>685314</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -15546,19 +16712,19 @@
         <v>188476.2</v>
       </c>
       <c r="C7" t="n">
-        <v>526680</v>
+        <v>402192</v>
       </c>
       <c r="D7" t="n">
-        <v>486415.61</v>
+        <v>921659.9</v>
       </c>
       <c r="E7" t="n">
-        <v>105807.19</v>
+        <v>198130.05</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>83.25</v>
+        <v>243</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -15573,7 +16739,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3560.76</v>
+        <v>68040</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -15596,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>721.5</v>
+        <v>2106</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -15611,7 +16780,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1203.88</v>
+        <v>23004</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15634,7 +16806,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>1377</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -15649,7 +16821,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>686.72</v>
+        <v>13122</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -15687,7 +16862,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1509.08</v>
+        <v>28836</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15725,7 +16903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15765,6 +16946,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -15803,6 +16987,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15841,6 +17028,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -15879,6 +17069,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -15917,6 +17110,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -15955,6 +17151,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -15993,6 +17192,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -16031,6 +17233,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -16069,6 +17274,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -16107,6 +17315,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -16145,6 +17356,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -16183,6 +17397,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -16221,6 +17438,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -16270,6 +17490,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -16284,7 +17508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16355,6 +17579,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -16391,6 +17620,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16399,16 +17631,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>114652810.8</v>
+        <v>114528605.4</v>
       </c>
       <c r="C5" t="n">
-        <v>576359784</v>
+        <v>440129289.6</v>
       </c>
       <c r="D5" t="n">
-        <v>502110122.55</v>
+        <v>951397843.97</v>
       </c>
       <c r="E5" t="n">
-        <v>94264107.73999999</v>
+        <v>176514965.1</v>
       </c>
       <c r="F5" t="n">
         <v>62500.5</v>
@@ -16417,19 +17649,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6534362.34</v>
+        <v>134631720</v>
       </c>
       <c r="I5" t="n">
-        <v>114999</v>
+        <v>128576.29</v>
       </c>
       <c r="J5" t="n">
-        <v>297498.3</v>
+        <v>123817.8</v>
       </c>
       <c r="K5" t="n">
-        <v>6397639.92</v>
+        <v>11330785.38</v>
       </c>
       <c r="L5" t="n">
-        <v>1845601.25</v>
+        <v>35190288</v>
+      </c>
+      <c r="M5" t="n">
+        <v>274320</v>
       </c>
     </row>
     <row r="6">
@@ -16437,37 +17672,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>149591376</v>
+        <v>149373892.8</v>
       </c>
       <c r="C6" t="n">
-        <v>502976628</v>
+        <v>384091243.2</v>
       </c>
       <c r="D6" t="n">
-        <v>410159955.71</v>
+        <v>777170744.0599999</v>
       </c>
       <c r="E6" t="n">
-        <v>72439206.84</v>
+        <v>135646582.5</v>
       </c>
       <c r="F6" t="n">
         <v>120834.3</v>
       </c>
       <c r="G6" t="n">
-        <v>226107</v>
+        <v>657963</v>
       </c>
       <c r="H6" t="n">
-        <v>3004004.02</v>
+        <v>61893450</v>
       </c>
       <c r="I6" t="n">
-        <v>536662</v>
+        <v>393886.27</v>
       </c>
       <c r="J6" t="n">
-        <v>437497.5</v>
+        <v>182085</v>
       </c>
       <c r="K6" t="n">
-        <v>5699378.1</v>
+        <v>10093335.72</v>
       </c>
       <c r="L6" t="n">
-        <v>1972980.38</v>
+        <v>37584378</v>
+      </c>
+      <c r="M6" t="n">
+        <v>530640</v>
       </c>
     </row>
     <row r="7">
@@ -16475,37 +17713,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>136103893.2</v>
+        <v>136009655.1</v>
       </c>
       <c r="C7" t="n">
-        <v>345086280</v>
+        <v>263520432</v>
       </c>
       <c r="D7" t="n">
-        <v>318704631.09</v>
+        <v>603881270.78</v>
       </c>
       <c r="E7" t="n">
-        <v>52868325.74</v>
+        <v>98998981.65000001</v>
       </c>
       <c r="F7" t="n">
         <v>400003.2</v>
       </c>
       <c r="G7" t="n">
-        <v>402597</v>
+        <v>1171503</v>
       </c>
       <c r="H7" t="n">
-        <v>1175375.19</v>
+        <v>24217020</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>326664.8</v>
+        <v>135956.8</v>
       </c>
       <c r="K7" t="n">
-        <v>5370621.16</v>
+        <v>9510469.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1897037.28</v>
+        <v>36138960</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1496250</v>
       </c>
     </row>
     <row r="8">
@@ -16513,37 +17754,40 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>93896946</v>
+        <v>93896352</v>
       </c>
       <c r="C8" t="n">
-        <v>200526480</v>
+        <v>153129312</v>
       </c>
       <c r="D8" t="n">
-        <v>213643432.7</v>
+        <v>404811399.17</v>
       </c>
       <c r="E8" t="n">
-        <v>35712355.69</v>
+        <v>66873440.7</v>
       </c>
       <c r="F8" t="n">
         <v>1108342.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1361109.75</v>
+        <v>3957174</v>
       </c>
       <c r="H8" t="n">
-        <v>1347423.82</v>
+        <v>27761850</v>
       </c>
       <c r="I8" t="n">
-        <v>827992.8</v>
+        <v>428846.59</v>
       </c>
       <c r="J8" t="n">
-        <v>297498.3</v>
+        <v>123817.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3590512.2</v>
+        <v>6682859.39</v>
       </c>
       <c r="L8" t="n">
-        <v>1581893.06</v>
+        <v>30139074</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1711800</v>
       </c>
     </row>
     <row r="9">
@@ -16551,37 +17795,40 @@
         <v>250</v>
       </c>
       <c r="B9" t="n">
-        <v>60284466</v>
+        <v>60284268</v>
       </c>
       <c r="C9" t="n">
-        <v>113541120</v>
+        <v>86704128</v>
       </c>
       <c r="D9" t="n">
-        <v>131980181.67</v>
+        <v>250075938.82</v>
       </c>
       <c r="E9" t="n">
-        <v>26455810.15</v>
+        <v>49540026.6</v>
       </c>
       <c r="F9" t="n">
         <v>1083342</v>
       </c>
       <c r="G9" t="n">
-        <v>1141163.25</v>
+        <v>3315816</v>
       </c>
       <c r="H9" t="n">
-        <v>921244.5</v>
+        <v>18981000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>166249.05</v>
+        <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3093430</v>
+        <v>5653617.86</v>
       </c>
       <c r="L9" t="n">
-        <v>1448288.26</v>
+        <v>27621810</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1476000</v>
       </c>
     </row>
     <row r="10">
@@ -16589,25 +17836,25 @@
         <v>300</v>
       </c>
       <c r="B10" t="n">
-        <v>38019366</v>
+        <v>38018772</v>
       </c>
       <c r="C10" t="n">
-        <v>60568200</v>
+        <v>46252080</v>
       </c>
       <c r="D10" t="n">
-        <v>76278812.34999999</v>
+        <v>144533030.4</v>
       </c>
       <c r="E10" t="n">
-        <v>14329818.72</v>
+        <v>26833410</v>
       </c>
       <c r="F10" t="n">
         <v>333336</v>
       </c>
       <c r="G10" t="n">
-        <v>753690</v>
+        <v>2199960</v>
       </c>
       <c r="H10" t="n">
-        <v>257284.5</v>
+        <v>5301000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -16616,10 +17863,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1749388</v>
+        <v>3463985.04</v>
       </c>
       <c r="L10" t="n">
-        <v>822702.29</v>
+        <v>15706008</v>
+      </c>
+      <c r="M10" t="n">
+        <v>837000</v>
       </c>
     </row>
     <row r="11">
@@ -16630,34 +17880,37 @@
         <v>22003542</v>
       </c>
       <c r="C11" t="n">
-        <v>28939680</v>
+        <v>22099392</v>
       </c>
       <c r="D11" t="n">
-        <v>37640190.15</v>
+        <v>71320601.09</v>
       </c>
       <c r="E11" t="n">
-        <v>5504063.14</v>
+        <v>10306674.9</v>
       </c>
       <c r="F11" t="n">
         <v>166668</v>
       </c>
       <c r="G11" t="n">
-        <v>485625</v>
+        <v>1417500</v>
       </c>
       <c r="H11" t="n">
-        <v>224086.5</v>
+        <v>4617000</v>
       </c>
       <c r="I11" t="n">
-        <v>383330</v>
+        <v>174510.26</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>682688</v>
+        <v>1396082.11</v>
       </c>
       <c r="L11" t="n">
-        <v>447073.2</v>
+        <v>8494200</v>
+      </c>
+      <c r="M11" t="n">
+        <v>855000</v>
       </c>
     </row>
     <row r="12">
@@ -16668,22 +17921,22 @@
         <v>10812384</v>
       </c>
       <c r="C12" t="n">
-        <v>8399160</v>
+        <v>6413904</v>
       </c>
       <c r="D12" t="n">
-        <v>11270822.01</v>
+        <v>21355944.19</v>
       </c>
       <c r="E12" t="n">
-        <v>2377801.44</v>
+        <v>4452570</v>
       </c>
       <c r="F12" t="n">
         <v>125001</v>
       </c>
       <c r="G12" t="n">
-        <v>167610</v>
+        <v>489240</v>
       </c>
       <c r="H12" t="n">
-        <v>41497.5</v>
+        <v>855000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16692,10 +17945,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>213340</v>
+        <v>450114.12</v>
       </c>
       <c r="L12" t="n">
-        <v>161364.6</v>
+        <v>3045600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>198000</v>
       </c>
     </row>
     <row r="13">
@@ -16706,22 +17962,22 @@
         <v>4342932</v>
       </c>
       <c r="C13" t="n">
-        <v>2605680</v>
+        <v>1989792</v>
       </c>
       <c r="D13" t="n">
-        <v>3581426.57</v>
+        <v>6786084.1</v>
       </c>
       <c r="E13" t="n">
-        <v>614248.79</v>
+        <v>1150216.2</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>43290</v>
+        <v>126360</v>
       </c>
       <c r="H13" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -16730,10 +17986,13 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>42668</v>
+        <v>92207.84</v>
       </c>
       <c r="L13" t="n">
-        <v>50868</v>
+        <v>972000</v>
+      </c>
+      <c r="M13" t="n">
+        <v>54000</v>
       </c>
     </row>
     <row r="14">
@@ -16744,22 +18003,22 @@
         <v>3123252</v>
       </c>
       <c r="C14" t="n">
-        <v>887040</v>
+        <v>677376</v>
       </c>
       <c r="D14" t="n">
-        <v>1248100.25</v>
+        <v>2364899.33</v>
       </c>
       <c r="E14" t="n">
-        <v>188798.1</v>
+        <v>353535.3</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>29970</v>
+        <v>87480</v>
       </c>
       <c r="H14" t="n">
-        <v>24898.5</v>
+        <v>513000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -16771,7 +18030,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>23738.4</v>
+        <v>453600</v>
+      </c>
+      <c r="M14" t="n">
+        <v>90000</v>
       </c>
     </row>
     <row r="15">
@@ -16782,10 +18044,10 @@
         <v>1305810</v>
       </c>
       <c r="C15" t="n">
-        <v>415800</v>
+        <v>317520</v>
       </c>
       <c r="D15" t="n">
-        <v>593473.6</v>
+        <v>1124513.28</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16794,10 +18056,10 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>5550</v>
+        <v>16200</v>
       </c>
       <c r="H15" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -16806,10 +18068,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>13847.4</v>
+        <v>264600</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="16">
@@ -16820,10 +18085,10 @@
         <v>623502</v>
       </c>
       <c r="C16" t="n">
-        <v>166320</v>
+        <v>127008</v>
       </c>
       <c r="D16" t="n">
-        <v>240760.08</v>
+        <v>456192</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16832,7 +18097,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -16847,7 +18112,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>13847.4</v>
+        <v>264600</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="17">
@@ -16858,10 +18126,10 @@
         <v>352440</v>
       </c>
       <c r="C17" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D17" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -16870,10 +18138,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>6660</v>
+        <v>19440</v>
       </c>
       <c r="H17" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -16885,7 +18153,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5369.4</v>
+        <v>102600</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="18">
@@ -16896,10 +18167,10 @@
         <v>38214</v>
       </c>
       <c r="C18" t="n">
-        <v>194040</v>
+        <v>148176</v>
       </c>
       <c r="D18" t="n">
-        <v>280886.76</v>
+        <v>532224</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16908,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>67710</v>
+        <v>197640</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -16923,7 +18194,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3391.2</v>
+        <v>64800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -16934,10 +18208,10 @@
         <v>12474</v>
       </c>
       <c r="C19" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D19" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16946,7 +18220,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>555</v>
+        <v>1620</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -16961,6 +18235,9 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -16972,10 +18249,10 @@
         <v>198</v>
       </c>
       <c r="C20" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D20" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16999,6 +18276,9 @@
         <v>0</v>
       </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17010,10 +18290,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D21" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -17037,6 +18317,9 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17048,10 +18331,10 @@
         <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D22" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -17075,6 +18358,9 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17086,10 +18372,10 @@
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D23" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -17113,6 +18399,9 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17124,10 +18413,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>221760</v>
+        <v>169344</v>
       </c>
       <c r="D24" t="n">
-        <v>321013.44</v>
+        <v>608256</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -17151,6 +18440,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -17202,6 +18494,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -17216,7 +18512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17287,13 +18583,18 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>18627.75</v>
+        <v>18544.05</v>
       </c>
       <c r="C4" t="n">
         <v>4026456</v>
@@ -17308,10 +18609,10 @@
         <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>72390</v>
+        <v>70140</v>
       </c>
       <c r="H4" t="n">
-        <v>20790</v>
+        <v>20820</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -17320,10 +18621,13 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="L4" t="n">
-        <v>220350</v>
+        <v>217650</v>
+      </c>
+      <c r="M4" t="n">
+        <v>32790</v>
       </c>
     </row>
     <row r="5">
@@ -17331,7 +18635,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>30545.64</v>
+        <v>30516.48</v>
       </c>
       <c r="C5" t="n">
         <v>4641336</v>
@@ -17346,7 +18650,7 @@
         <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>98220</v>
+        <v>97380</v>
       </c>
       <c r="H5" t="n">
         <v>16710</v>
@@ -17358,10 +18662,13 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="L5" t="n">
-        <v>276510</v>
+        <v>275010</v>
+      </c>
+      <c r="M5" t="n">
+        <v>11100</v>
       </c>
     </row>
     <row r="6">
@@ -17369,7 +18676,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>31622.22</v>
+        <v>31618.08</v>
       </c>
       <c r="C6" t="n">
         <v>4332384</v>
@@ -17384,7 +18691,7 @@
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>105030</v>
+        <v>104370</v>
       </c>
       <c r="H6" t="n">
         <v>2190</v>
@@ -17396,10 +18703,13 @@
         <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L6" t="n">
-        <v>258930</v>
+        <v>258240</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5460</v>
       </c>
     </row>
     <row r="7">
@@ -17407,7 +18717,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>30237.03</v>
+        <v>30236.58</v>
       </c>
       <c r="C7" t="n">
         <v>3555720</v>
@@ -17422,7 +18732,7 @@
         <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>77370</v>
+        <v>76980</v>
       </c>
       <c r="H7" t="n">
         <v>720</v>
@@ -17437,7 +18747,10 @@
         <v>198</v>
       </c>
       <c r="L7" t="n">
-        <v>179460</v>
+        <v>178560</v>
+      </c>
+      <c r="M7" t="n">
+        <v>4440</v>
       </c>
     </row>
     <row r="8">
@@ -17445,7 +18758,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23998.23</v>
+        <v>23998.14</v>
       </c>
       <c r="C8" t="n">
         <v>2210544</v>
@@ -17460,7 +18773,7 @@
         <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>69120</v>
+        <v>68670</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -17475,7 +18788,10 @@
         <v>125</v>
       </c>
       <c r="L8" t="n">
-        <v>117300</v>
+        <v>116610</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3990</v>
       </c>
     </row>
     <row r="9">
@@ -17498,7 +18814,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>34440</v>
+        <v>34140</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -17510,10 +18826,13 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L9" t="n">
-        <v>84810</v>
+        <v>84540</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3060</v>
       </c>
     </row>
     <row r="10">
@@ -17551,7 +18870,10 @@
         <v>55</v>
       </c>
       <c r="L10" t="n">
-        <v>42120</v>
+        <v>42030</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1890</v>
       </c>
     </row>
     <row r="11">
@@ -17589,7 +18911,10 @@
         <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>19380</v>
+        <v>19110</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2310</v>
       </c>
     </row>
     <row r="12">
@@ -17627,7 +18952,10 @@
         <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>4680</v>
+        <v>4470</v>
+      </c>
+      <c r="M12" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="13">
@@ -17667,6 +18995,9 @@
       <c r="L13" t="n">
         <v>1320</v>
       </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -17705,6 +19036,9 @@
       <c r="L14" t="n">
         <v>510</v>
       </c>
+      <c r="M14" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -17743,6 +19077,9 @@
       <c r="L15" t="n">
         <v>300</v>
       </c>
+      <c r="M15" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -17781,6 +19118,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -17819,6 +19159,9 @@
       <c r="L17" t="n">
         <v>90</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -17857,6 +19200,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -17895,6 +19241,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -17933,6 +19282,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -17971,6 +19323,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18009,6 +19364,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18047,6 +19405,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -18085,6 +19446,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -18134,6 +19498,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -18148,7 +19516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18219,6 +19587,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -18255,6 +19628,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -18263,7 +19639,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>13745.54</v>
+        <v>13732.42</v>
       </c>
       <c r="C5" t="n">
         <v>2552734.8</v>
@@ -18284,16 +19660,19 @@
         <v>6015.6</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15</v>
+        <v>0.33</v>
       </c>
       <c r="J5" t="n">
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>96.18000000000001</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>58067.1</v>
+        <v>57752.1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>222</v>
       </c>
     </row>
     <row r="6">
@@ -18301,7 +19680,7 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>25297.78</v>
+        <v>25294.46</v>
       </c>
       <c r="C6" t="n">
         <v>3899145.6</v>
@@ -18316,7 +19695,7 @@
         <v>0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5251.5</v>
+        <v>5218.5</v>
       </c>
       <c r="H6" t="n">
         <v>1248.3</v>
@@ -18328,10 +19707,13 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>139.75</v>
+        <v>108.5</v>
       </c>
       <c r="L6" t="n">
-        <v>95804.10000000001</v>
+        <v>95548.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>436.8</v>
       </c>
     </row>
     <row r="7">
@@ -18339,7 +19721,7 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>28725.18</v>
+        <v>28724.75</v>
       </c>
       <c r="C7" t="n">
         <v>3555720</v>
@@ -18354,7 +19736,7 @@
         <v>6</v>
       </c>
       <c r="G7" t="n">
-        <v>11605.5</v>
+        <v>11547</v>
       </c>
       <c r="H7" t="n">
         <v>525.6</v>
@@ -18366,10 +19748,13 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>162.36</v>
+        <v>126.32</v>
       </c>
       <c r="L7" t="n">
-        <v>107676</v>
+        <v>107136</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1554</v>
       </c>
     </row>
     <row r="8">
@@ -18377,7 +19762,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>23998.23</v>
+        <v>23998.14</v>
       </c>
       <c r="C8" t="n">
         <v>2210544</v>
@@ -18392,7 +19777,7 @@
         <v>12.35</v>
       </c>
       <c r="G8" t="n">
-        <v>44928</v>
+        <v>44635.5</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -18404,10 +19789,13 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>112.5</v>
+        <v>92</v>
       </c>
       <c r="L8" t="n">
-        <v>83283</v>
+        <v>82793.10000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2394</v>
       </c>
     </row>
     <row r="9">
@@ -18430,7 +19818,7 @@
         <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>29274</v>
+        <v>29019</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -18442,10 +19830,13 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>88</v>
+        <v>71.47</v>
       </c>
       <c r="L9" t="n">
-        <v>68696.10000000001</v>
+        <v>68477.39999999999</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3060</v>
       </c>
     </row>
     <row r="10">
@@ -18480,10 +19871,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>55</v>
+        <v>47.85</v>
       </c>
       <c r="L10" t="n">
-        <v>37486.8</v>
+        <v>37406.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1890</v>
       </c>
     </row>
     <row r="11">
@@ -18518,10 +19912,13 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>17.97</v>
       </c>
       <c r="L11" t="n">
-        <v>19380</v>
+        <v>19110</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2310</v>
       </c>
     </row>
     <row r="12">
@@ -18556,10 +19953,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="L12" t="n">
-        <v>4680</v>
+        <v>4470</v>
+      </c>
+      <c r="M12" t="n">
+        <v>390</v>
       </c>
     </row>
     <row r="13">
@@ -18599,6 +19999,9 @@
       <c r="L13" t="n">
         <v>1320</v>
       </c>
+      <c r="M13" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -18637,6 +20040,9 @@
       <c r="L14" t="n">
         <v>510</v>
       </c>
+      <c r="M14" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -18670,10 +20076,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
+      </c>
+      <c r="M15" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -18713,6 +20122,9 @@
       <c r="L16" t="n">
         <v>60</v>
       </c>
+      <c r="M16" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -18751,6 +20163,9 @@
       <c r="L17" t="n">
         <v>90</v>
       </c>
+      <c r="M17" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -18789,6 +20204,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -18827,6 +20245,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -18865,6 +20286,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -18903,6 +20327,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -18941,6 +20368,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -18979,6 +20409,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19017,6 +20450,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -19066,6 +20502,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -19080,7 +20520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19151,6 +20591,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -19187,6 +20632,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19195,16 +20643,16 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>30240183.6</v>
+        <v>30211315.2</v>
       </c>
       <c r="C5" t="n">
-        <v>140400414</v>
+        <v>107214861.6</v>
       </c>
       <c r="D5" t="n">
-        <v>122313303.32</v>
+        <v>231759145.73</v>
       </c>
       <c r="E5" t="n">
-        <v>37274010.78</v>
+        <v>69797729.7</v>
       </c>
       <c r="F5" t="n">
         <v>18333.48</v>
@@ -19213,19 +20661,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1664215.74</v>
+        <v>34288920</v>
       </c>
       <c r="I5" t="n">
-        <v>57499.5</v>
+        <v>64288.14</v>
       </c>
       <c r="J5" t="n">
-        <v>52499.7</v>
+        <v>21850.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2051904.12</v>
+        <v>3535847.92</v>
       </c>
       <c r="L5" t="n">
-        <v>546992.08</v>
+        <v>10395378</v>
+      </c>
+      <c r="M5" t="n">
+        <v>66600</v>
       </c>
     </row>
     <row r="6">
@@ -19233,37 +20684,40 @@
         <v>100</v>
       </c>
       <c r="B6" t="n">
-        <v>55655107.2</v>
+        <v>55647820.8</v>
       </c>
       <c r="C6" t="n">
-        <v>214453008</v>
+        <v>163764115.2</v>
       </c>
       <c r="D6" t="n">
-        <v>174878973.23</v>
+        <v>331360533.5</v>
       </c>
       <c r="E6" t="n">
-        <v>39820546.58</v>
+        <v>74566264.5</v>
       </c>
       <c r="F6" t="n">
         <v>29166.9</v>
       </c>
       <c r="G6" t="n">
-        <v>97152.75</v>
+        <v>281799</v>
       </c>
       <c r="H6" t="n">
-        <v>345342.19</v>
+        <v>7115310</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>233332</v>
+        <v>97112</v>
       </c>
       <c r="K6" t="n">
-        <v>2981426.5</v>
+        <v>5268228.89</v>
       </c>
       <c r="L6" t="n">
-        <v>902474.62</v>
+        <v>17198784</v>
+      </c>
+      <c r="M6" t="n">
+        <v>131040</v>
       </c>
     </row>
     <row r="7">
@@ -19271,37 +20725,40 @@
         <v>150</v>
       </c>
       <c r="B7" t="n">
-        <v>63195392.7</v>
+        <v>63194452.2</v>
       </c>
       <c r="C7" t="n">
-        <v>195564600</v>
+        <v>149340240</v>
       </c>
       <c r="D7" t="n">
-        <v>180613798.08</v>
+        <v>342226874.88</v>
       </c>
       <c r="E7" t="n">
-        <v>36115520.72</v>
+        <v>67628390.40000001</v>
       </c>
       <c r="F7" t="n">
         <v>250002</v>
       </c>
       <c r="G7" t="n">
-        <v>214701.75</v>
+        <v>623538</v>
       </c>
       <c r="H7" t="n">
-        <v>145407.24</v>
+        <v>2995920</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>163332.4</v>
+        <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>3463788.24</v>
+        <v>6133788.14</v>
       </c>
       <c r="L7" t="n">
-        <v>1014307.92</v>
+        <v>19284480</v>
+      </c>
+      <c r="M7" t="n">
+        <v>466200</v>
       </c>
     </row>
     <row r="8">
@@ -19309,22 +20766,22 @@
         <v>200</v>
       </c>
       <c r="B8" t="n">
-        <v>52796106</v>
+        <v>52795908</v>
       </c>
       <c r="C8" t="n">
-        <v>121579920</v>
+        <v>92842848</v>
       </c>
       <c r="D8" t="n">
-        <v>129532775.2</v>
+        <v>245438595.07</v>
       </c>
       <c r="E8" t="n">
-        <v>24689521.53</v>
+        <v>46232549.55</v>
       </c>
       <c r="F8" t="n">
         <v>514587.45</v>
       </c>
       <c r="G8" t="n">
-        <v>831168</v>
+        <v>2410317</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -19333,13 +20790,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>148749.15</v>
+        <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2400075</v>
+        <v>4467152</v>
       </c>
       <c r="L8" t="n">
-        <v>784525.86</v>
+        <v>14902758</v>
+      </c>
+      <c r="M8" t="n">
+        <v>718200</v>
       </c>
     </row>
     <row r="9">
@@ -19350,19 +20810,19 @@
         <v>37519416</v>
       </c>
       <c r="C9" t="n">
-        <v>73901520</v>
+        <v>56433888</v>
       </c>
       <c r="D9" t="n">
-        <v>85903116.29000001</v>
+        <v>162769153.54</v>
       </c>
       <c r="E9" t="n">
-        <v>19442357.12</v>
+        <v>36406932.3</v>
       </c>
       <c r="F9" t="n">
         <v>750006</v>
       </c>
       <c r="G9" t="n">
-        <v>541569</v>
+        <v>1567026</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -19371,13 +20831,16 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>166249.05</v>
+        <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>1877392</v>
+        <v>3470151.65</v>
       </c>
       <c r="L9" t="n">
-        <v>647117.26</v>
+        <v>12325932</v>
+      </c>
+      <c r="M9" t="n">
+        <v>918000</v>
       </c>
     </row>
     <row r="10">
@@ -19388,22 +20851,22 @@
         <v>23115906</v>
       </c>
       <c r="C10" t="n">
-        <v>37699200</v>
+        <v>28788480</v>
       </c>
       <c r="D10" t="n">
-        <v>47477887.78</v>
+        <v>89961062.40000001</v>
       </c>
       <c r="E10" t="n">
-        <v>8318988.72</v>
+        <v>15577785</v>
       </c>
       <c r="F10" t="n">
         <v>125001</v>
       </c>
       <c r="G10" t="n">
-        <v>281940</v>
+        <v>822960</v>
       </c>
       <c r="H10" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -19412,10 +20875,13 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1173370</v>
+        <v>2323404.6</v>
       </c>
       <c r="L10" t="n">
-        <v>353125.66</v>
+        <v>6733206</v>
+      </c>
+      <c r="M10" t="n">
+        <v>567000</v>
       </c>
     </row>
     <row r="11">
@@ -19426,19 +20892,19 @@
         <v>14979096</v>
       </c>
       <c r="C11" t="n">
-        <v>15246000</v>
+        <v>11642400</v>
       </c>
       <c r="D11" t="n">
-        <v>19829602.09</v>
+        <v>37573113.6</v>
       </c>
       <c r="E11" t="n">
-        <v>2310347.49</v>
+        <v>4326258.6</v>
       </c>
       <c r="F11" t="n">
         <v>41667</v>
       </c>
       <c r="G11" t="n">
-        <v>297480</v>
+        <v>868320</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -19447,13 +20913,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>116666</v>
+        <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>426680</v>
+        <v>872551.3199999999</v>
       </c>
       <c r="L11" t="n">
-        <v>182559.6</v>
+        <v>3439800</v>
+      </c>
+      <c r="M11" t="n">
+        <v>693000</v>
       </c>
     </row>
     <row r="12">
@@ -19464,19 +20933,19 @@
         <v>6508458</v>
       </c>
       <c r="C12" t="n">
-        <v>2134440</v>
+        <v>1629936</v>
       </c>
       <c r="D12" t="n">
-        <v>2864202.29</v>
+        <v>5427088.13</v>
       </c>
       <c r="E12" t="n">
-        <v>237780.14</v>
+        <v>445257</v>
       </c>
       <c r="F12" t="n">
         <v>83334</v>
       </c>
       <c r="G12" t="n">
-        <v>83805</v>
+        <v>244620</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -19488,10 +20957,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>64002</v>
+        <v>135034.24</v>
       </c>
       <c r="L12" t="n">
-        <v>44085.6</v>
+        <v>804600</v>
+      </c>
+      <c r="M12" t="n">
+        <v>117000</v>
       </c>
     </row>
     <row r="13">
@@ -19502,19 +20974,19 @@
         <v>1860408</v>
       </c>
       <c r="C13" t="n">
-        <v>914760</v>
+        <v>698544</v>
       </c>
       <c r="D13" t="n">
-        <v>1257309.33</v>
+        <v>2382348.67</v>
       </c>
       <c r="E13" t="n">
-        <v>263249.48</v>
+        <v>492949.8</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>18870</v>
+        <v>55080</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -19529,7 +21001,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>12434.4</v>
+        <v>237600</v>
+      </c>
+      <c r="M13" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="14">
@@ -19540,19 +21015,19 @@
         <v>790416</v>
       </c>
       <c r="C14" t="n">
-        <v>249480</v>
+        <v>190512</v>
       </c>
       <c r="D14" t="n">
-        <v>351028.2</v>
+        <v>665127.9399999999</v>
       </c>
       <c r="E14" t="n">
-        <v>94399.05</v>
+        <v>176767.65</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>13320</v>
+        <v>38880</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -19567,7 +21042,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4804.2</v>
+        <v>91800</v>
+      </c>
+      <c r="M14" t="n">
+        <v>36000</v>
       </c>
     </row>
     <row r="15">
@@ -19578,10 +21056,10 @@
         <v>322542</v>
       </c>
       <c r="C15" t="n">
-        <v>83160</v>
+        <v>63504</v>
       </c>
       <c r="D15" t="n">
-        <v>118694.72</v>
+        <v>224902.66</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -19590,7 +21068,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2220</v>
+        <v>6480</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -19602,10 +21080,13 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>21334</v>
+        <v>47876.22</v>
       </c>
       <c r="L15" t="n">
-        <v>2826</v>
+        <v>54000</v>
+      </c>
+      <c r="M15" t="n">
+        <v>9000</v>
       </c>
     </row>
     <row r="16">
@@ -19643,7 +21124,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>565.2</v>
+        <v>10800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18000</v>
       </c>
     </row>
     <row r="17">
@@ -19654,10 +21138,10 @@
         <v>235224</v>
       </c>
       <c r="C17" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D17" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -19666,7 +21150,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>2775</v>
+        <v>8100</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -19681,7 +21165,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>847.8</v>
+        <v>16200</v>
+      </c>
+      <c r="M17" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="18">
@@ -19721,6 +21208,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -19759,6 +21249,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -19797,6 +21290,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -19806,10 +21302,10 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>27720</v>
+        <v>21168</v>
       </c>
       <c r="D21" t="n">
-        <v>40126.68</v>
+        <v>76032</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -19833,6 +21329,9 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19873,6 +21372,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -19911,6 +21413,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -19920,10 +21425,10 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>55440</v>
+        <v>42336</v>
       </c>
       <c r="D24" t="n">
-        <v>80253.36</v>
+        <v>152064</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -19947,6 +21452,9 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -19998,6 +21506,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20012,7 +21524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20083,6 +21595,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -20104,10 +21621,10 @@
         <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>130290</v>
+        <v>130320</v>
       </c>
       <c r="H4" t="n">
-        <v>27840</v>
+        <v>27900</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -20119,7 +21636,10 @@
         <v>256</v>
       </c>
       <c r="L4" t="n">
-        <v>359460</v>
+        <v>357900</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -20142,7 +21662,7 @@
         <v>8</v>
       </c>
       <c r="G5" t="n">
-        <v>75090</v>
+        <v>75300</v>
       </c>
       <c r="H5" t="n">
         <v>25680</v>
@@ -20157,7 +21677,10 @@
         <v>136</v>
       </c>
       <c r="L5" t="n">
-        <v>165570</v>
+        <v>166560</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -20180,10 +21703,10 @@
         <v>5</v>
       </c>
       <c r="G6" t="n">
-        <v>28050</v>
+        <v>28200</v>
       </c>
       <c r="H6" t="n">
-        <v>4320</v>
+        <v>4380</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20195,7 +21718,10 @@
         <v>46</v>
       </c>
       <c r="L6" t="n">
-        <v>61770</v>
+        <v>61590</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -20235,6 +21761,9 @@
       <c r="L7" t="n">
         <v>8640</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -20271,7 +21800,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2880</v>
+        <v>2850</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -20294,7 +21826,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H9" t="n">
         <v>60</v>
@@ -20310,6 +21842,9 @@
       </c>
       <c r="L9" t="n">
         <v>630</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -20349,6 +21884,9 @@
       <c r="L10" t="n">
         <v>270</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -20387,6 +21925,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -20425,6 +21966,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -20463,6 +22007,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -20501,6 +22048,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -20539,6 +22089,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -20577,6 +22130,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -20615,6 +22171,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -20653,6 +22212,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -20691,6 +22253,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -20729,6 +22294,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -20767,6 +22335,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -20805,6 +22376,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -20843,6 +22417,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -20881,6 +22458,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -20930,6 +22510,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -20944,7 +22528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21015,6 +22599,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21051,6 +22640,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21086,10 +22678,13 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>57.12</v>
+        <v>45.02</v>
       </c>
       <c r="L5" t="n">
-        <v>34769.7</v>
+        <v>34977.6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21112,10 +22707,10 @@
         <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1402.5</v>
+        <v>1410</v>
       </c>
       <c r="H6" t="n">
-        <v>2462.4</v>
+        <v>2496.6</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21124,10 +22719,13 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>29.9</v>
+        <v>23.32</v>
       </c>
       <c r="L6" t="n">
-        <v>22854.9</v>
+        <v>22788.3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21162,10 +22760,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>3.28</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
         <v>5184</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21203,7 +22804,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2044.8</v>
+        <v>2023.5</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21226,7 +22830,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>25.5</v>
+        <v>51</v>
       </c>
       <c r="H9" t="n">
         <v>60</v>
@@ -21242,6 +22846,9 @@
       </c>
       <c r="L9" t="n">
         <v>510.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -21281,6 +22888,9 @@
       <c r="L10" t="n">
         <v>240.3</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -21319,6 +22929,9 @@
       <c r="L11" t="n">
         <v>30</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -21357,6 +22970,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -21395,6 +23011,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -21433,6 +23052,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -21471,6 +23093,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -21509,6 +23134,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -21547,6 +23175,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -21585,6 +23216,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -21623,6 +23257,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -21661,6 +23298,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -21699,6 +23339,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -21737,6 +23380,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -21775,6 +23421,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -21813,6 +23462,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -21862,6 +23514,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>
@@ -21876,7 +23532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21947,6 +23603,11 @@
           <t>Roads</t>
         </is>
       </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Hydraulic Structures</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -21983,6 +23644,9 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21994,13 +23658,13 @@
         <v>18977141.7</v>
       </c>
       <c r="C5" t="n">
-        <v>68271588</v>
+        <v>52134667.2</v>
       </c>
       <c r="D5" t="n">
-        <v>59476487.38</v>
+        <v>112695998.98</v>
       </c>
       <c r="E5" t="n">
-        <v>4810139.76</v>
+        <v>9007263.449999999</v>
       </c>
       <c r="F5" t="n">
         <v>6666.72</v>
@@ -22009,19 +23673,22 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2557573.92</v>
+        <v>52695360</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>104999.4</v>
+        <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1218598.08</v>
+        <v>2185796.9</v>
       </c>
       <c r="L5" t="n">
-        <v>327530.57</v>
+        <v>6295968</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -22032,34 +23699,37 @@
         <v>12792859.2</v>
       </c>
       <c r="C6" t="n">
-        <v>36299340</v>
+        <v>27719496</v>
       </c>
       <c r="D6" t="n">
-        <v>29600849.94</v>
+        <v>56087665.92</v>
       </c>
       <c r="E6" t="n">
-        <v>2129740.7</v>
+        <v>3988062</v>
       </c>
       <c r="F6" t="n">
         <v>20833.5</v>
       </c>
       <c r="G6" t="n">
-        <v>25946.25</v>
+        <v>76140</v>
       </c>
       <c r="H6" t="n">
-        <v>681222.96</v>
+        <v>14230620</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>29166.5</v>
+        <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>637886.6</v>
+        <v>1132423.03</v>
       </c>
       <c r="L6" t="n">
-        <v>215293.16</v>
+        <v>4101894</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -22070,22 +23740,22 @@
         <v>919620.9</v>
       </c>
       <c r="C7" t="n">
-        <v>6292440</v>
+        <v>4805136</v>
       </c>
       <c r="D7" t="n">
-        <v>5811386.56</v>
+        <v>11011410.43</v>
       </c>
       <c r="E7" t="n">
-        <v>317421.57</v>
+        <v>594390.15</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2497.5</v>
+        <v>7290</v>
       </c>
       <c r="H7" t="n">
-        <v>121172.7</v>
+        <v>2496600</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22094,10 +23764,13 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>69975.52</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
-        <v>48833.28</v>
+        <v>933120</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -22108,10 +23781,10 @@
         <v>169092</v>
       </c>
       <c r="C8" t="n">
-        <v>693000</v>
+        <v>529200</v>
       </c>
       <c r="D8" t="n">
-        <v>738330.91</v>
+        <v>1398988.8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -22120,10 +23793,10 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3607.5</v>
+        <v>10530</v>
       </c>
       <c r="H8" t="n">
-        <v>63491.18</v>
+        <v>1308150</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -22135,7 +23808,10 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>19262.02</v>
+        <v>364230</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22146,10 +23822,10 @@
         <v>60984</v>
       </c>
       <c r="C9" t="n">
-        <v>110880</v>
+        <v>84672</v>
       </c>
       <c r="D9" t="n">
-        <v>128886.9</v>
+        <v>244214.78</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -22158,10 +23834,10 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>471.75</v>
+        <v>2754</v>
       </c>
       <c r="H9" t="n">
-        <v>16599</v>
+        <v>342000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22173,7 +23849,10 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>4807.03</v>
+        <v>91854</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -22211,7 +23890,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2263.63</v>
+        <v>43254</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22237,7 +23919,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>8299.5</v>
+        <v>171000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -22249,7 +23931,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>282.6</v>
+        <v>5400</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -22289,6 +23974,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -22327,6 +24015,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -22365,6 +24056,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -22403,6 +24097,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -22441,6 +24138,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -22479,6 +24179,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -22517,6 +24220,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -22555,6 +24261,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -22593,6 +24302,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -22631,6 +24343,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -22669,6 +24384,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -22707,6 +24425,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -22745,6 +24466,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -22794,6 +24518,10 @@
       </c>
       <c r="L25" s="1">
         <f>SUM(L4:L24)</f>
+        <v/>
+      </c>
+      <c r="M25" s="1">
+        <f>SUM(M4:M24)</f>
         <v/>
       </c>
     </row>

--- a/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
@@ -549,7 +549,7 @@
         <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>881</v>
+        <v>349</v>
       </c>
       <c r="L4" t="n">
         <v>1287210</v>
@@ -590,7 +590,7 @@
         <v>17</v>
       </c>
       <c r="K5" t="n">
-        <v>705</v>
+        <v>253</v>
       </c>
       <c r="L5" t="n">
         <v>930960</v>
@@ -631,7 +631,7 @@
         <v>15</v>
       </c>
       <c r="K6" t="n">
-        <v>410</v>
+        <v>104</v>
       </c>
       <c r="L6" t="n">
         <v>564330</v>
@@ -672,7 +672,7 @@
         <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>307</v>
+        <v>88</v>
       </c>
       <c r="L7" t="n">
         <v>334620</v>
@@ -713,7 +713,7 @@
         <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="L8" t="n">
         <v>235830</v>
@@ -754,7 +754,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="L9" t="n">
         <v>189450</v>
@@ -795,7 +795,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="L10" t="n">
         <v>98040</v>
@@ -836,7 +836,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>47190</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>16920</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>5400</v>
@@ -1000,7 +1000,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1470</v>
@@ -1553,7 +1553,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
         <v>36030</v>
@@ -1594,7 +1594,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="L5" t="n">
         <v>52440</v>
@@ -1635,7 +1635,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
         <v>55650</v>
@@ -1676,7 +1676,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>49740</v>
@@ -1717,7 +1717,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L8" t="n">
         <v>73500</v>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
         <v>93120</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
         <v>50790</v>
@@ -1840,7 +1840,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>23970</v>
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>10860</v>
@@ -1922,7 +1922,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>3480</v>
@@ -2598,7 +2598,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>11.25</v>
+        <v>6.95</v>
       </c>
       <c r="L5" t="n">
         <v>11012.4</v>
@@ -2639,7 +2639,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>16.73</v>
+        <v>4.06</v>
       </c>
       <c r="L6" t="n">
         <v>20590.5</v>
@@ -2680,7 +2680,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>14.04</v>
+        <v>2.55</v>
       </c>
       <c r="L7" t="n">
         <v>29844</v>
@@ -2721,7 +2721,7 @@
         <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>22.82</v>
+        <v>2.21</v>
       </c>
       <c r="L8" t="n">
         <v>52185</v>
@@ -2762,7 +2762,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>38.54</v>
+        <v>5.62</v>
       </c>
       <c r="L9" t="n">
         <v>75427.2</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>23.49</v>
+        <v>2.61</v>
       </c>
       <c r="L10" t="n">
         <v>45203.1</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>10.78</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>23970</v>
@@ -2885,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>6.49</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>10860</v>
@@ -2926,7 +2926,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>3480</v>
@@ -3602,7 +3602,7 @@
         <v>7283.4</v>
       </c>
       <c r="K5" t="n">
-        <v>546449.22</v>
+        <v>337512.76</v>
       </c>
       <c r="L5" t="n">
         <v>1982232</v>
@@ -3643,7 +3643,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>812390.4399999999</v>
+        <v>196943.14</v>
       </c>
       <c r="L6" t="n">
         <v>3706290</v>
@@ -3684,7 +3684,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>681532.02</v>
+        <v>123914.91</v>
       </c>
       <c r="L7" t="n">
         <v>5371920</v>
@@ -3725,7 +3725,7 @@
         <v>41272.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1107853.7</v>
+        <v>107211.65</v>
       </c>
       <c r="L8" t="n">
         <v>9393300</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>1871542.46</v>
+        <v>272933.28</v>
       </c>
       <c r="L9" t="n">
         <v>13576896</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>1140580.44</v>
+        <v>126731.16</v>
       </c>
       <c r="L10" t="n">
         <v>8136558</v>
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>523530.79</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>4314600</v>
@@ -3889,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>315079.88</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>1954800</v>
@@ -3930,7 +3930,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>92207.84</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>626400</v>
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="L4" t="n">
         <v>103230</v>
@@ -4606,7 +4606,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
         <v>35310</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>8190</v>
@@ -5610,7 +5610,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4.96</v>
+        <v>2.32</v>
       </c>
       <c r="L5" t="n">
         <v>7415.1</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.01</v>
+        <v>0.51</v>
       </c>
       <c r="L6" t="n">
         <v>3030.3</v>
@@ -6614,7 +6614,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>241080.54</v>
+        <v>112504.25</v>
       </c>
       <c r="L5" t="n">
         <v>1334718</v>
@@ -6655,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>49235.78</v>
+        <v>24617.89</v>
       </c>
       <c r="L6" t="n">
         <v>545454</v>
@@ -7577,7 +7577,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>53880</v>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>13770</v>
@@ -7659,7 +7659,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>2640</v>
@@ -7700,7 +7700,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>510</v>
@@ -8622,7 +8622,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>2891.7</v>
@@ -8663,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>976.8</v>
@@ -8704,7 +8704,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>306</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>144648.32</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>520506</v>
@@ -9667,7 +9667,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>73853.67999999999</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>175824</v>
@@ -9708,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>61957.46</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>55080</v>
@@ -10589,7 +10589,7 @@
         <v>9</v>
       </c>
       <c r="K4" t="n">
-        <v>228</v>
+        <v>125</v>
       </c>
       <c r="L4" t="n">
         <v>230880</v>
@@ -10630,7 +10630,7 @@
         <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>269</v>
+        <v>102</v>
       </c>
       <c r="L5" t="n">
         <v>265440</v>
@@ -10671,7 +10671,7 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="L6" t="n">
         <v>124110</v>
@@ -10712,7 +10712,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
         <v>69540</v>
@@ -10753,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
         <v>32610</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>8430</v>
@@ -11634,7 +11634,7 @@
         <v>5.1</v>
       </c>
       <c r="K5" t="n">
-        <v>233.36</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="L5" t="n">
         <v>195501.6</v>
@@ -11675,7 +11675,7 @@
         <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>207.87</v>
+        <v>52.73</v>
       </c>
       <c r="L6" t="n">
         <v>208802.1</v>
@@ -11716,7 +11716,7 @@
         <v>5.6</v>
       </c>
       <c r="K7" t="n">
-        <v>195.87</v>
+        <v>56.14</v>
       </c>
       <c r="L7" t="n">
         <v>200772</v>
@@ -11757,7 +11757,7 @@
         <v>5.1</v>
       </c>
       <c r="K8" t="n">
-        <v>137.63</v>
+        <v>27.97</v>
       </c>
       <c r="L8" t="n">
         <v>167439.3</v>
@@ -11798,7 +11798,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>116.44</v>
+        <v>26.5</v>
       </c>
       <c r="L9" t="n">
         <v>153454.5</v>
@@ -11839,7 +11839,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>71.34</v>
+        <v>6.96</v>
       </c>
       <c r="L10" t="n">
         <v>87255.60000000001</v>
@@ -11880,7 +11880,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>28.75</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>47190</v>
@@ -11921,7 +11921,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>9.27</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>16920</v>
@@ -11962,7 +11962,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>5400</v>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>1470</v>
@@ -12638,7 +12638,7 @@
         <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>89.04000000000001</v>
+        <v>33.76</v>
       </c>
       <c r="L5" t="n">
         <v>55742.4</v>
@@ -12679,7 +12679,7 @@
         <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>56.28</v>
+        <v>15.21</v>
       </c>
       <c r="L6" t="n">
         <v>45920.7</v>
@@ -12720,7 +12720,7 @@
         <v>1.4</v>
       </c>
       <c r="K7" t="n">
-        <v>51.68</v>
+        <v>19.78</v>
       </c>
       <c r="L7" t="n">
         <v>41724</v>
@@ -12761,7 +12761,7 @@
         <v>0.85</v>
       </c>
       <c r="K8" t="n">
-        <v>22.08</v>
+        <v>2.94</v>
       </c>
       <c r="L8" t="n">
         <v>23153.1</v>
@@ -12802,7 +12802,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>5.62</v>
+        <v>3.21</v>
       </c>
       <c r="L9" t="n">
         <v>6828.3</v>
@@ -13642,7 +13642,7 @@
         <v>50983.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4323377.68</v>
+        <v>1639347.67</v>
       </c>
       <c r="L5" t="n">
         <v>10033632</v>
@@ -13683,7 +13683,7 @@
         <v>36417</v>
       </c>
       <c r="K6" t="n">
-        <v>2732586.01</v>
+        <v>738536.76</v>
       </c>
       <c r="L6" t="n">
         <v>8265726</v>
@@ -13724,7 +13724,7 @@
         <v>33989.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2509276.97</v>
+        <v>960340.5699999999</v>
       </c>
       <c r="L7" t="n">
         <v>7510320</v>
@@ -13765,7 +13765,7 @@
         <v>20636.3</v>
       </c>
       <c r="K8" t="n">
-        <v>1072116.48</v>
+        <v>142948.86</v>
       </c>
       <c r="L8" t="n">
         <v>4167558</v>
@@ -13806,7 +13806,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>272933.28</v>
+        <v>155961.87</v>
       </c>
       <c r="L9" t="n">
         <v>1229094</v>
@@ -14605,7 +14605,7 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
         <v>225150</v>
@@ -14646,7 +14646,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L5" t="n">
         <v>62640</v>
@@ -15650,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6.29</v>
+        <v>3.64</v>
       </c>
       <c r="L5" t="n">
         <v>13154.4</v>
@@ -16654,7 +16654,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>305368.68</v>
+        <v>176792.4</v>
       </c>
       <c r="L5" t="n">
         <v>2367792</v>
@@ -17658,7 +17658,7 @@
         <v>123817.8</v>
       </c>
       <c r="K5" t="n">
-        <v>11330785.38</v>
+        <v>4066225.11</v>
       </c>
       <c r="L5" t="n">
         <v>35190288</v>
@@ -17699,7 +17699,7 @@
         <v>182085</v>
       </c>
       <c r="K6" t="n">
-        <v>10093335.72</v>
+        <v>2560260.77</v>
       </c>
       <c r="L6" t="n">
         <v>37584378</v>
@@ -17740,7 +17740,7 @@
         <v>135956.8</v>
       </c>
       <c r="K7" t="n">
-        <v>9510469.5</v>
+        <v>2726128.06</v>
       </c>
       <c r="L7" t="n">
         <v>36138960</v>
@@ -17781,7 +17781,7 @@
         <v>123817.8</v>
       </c>
       <c r="K8" t="n">
-        <v>6682859.39</v>
+        <v>1358014.21</v>
       </c>
       <c r="L8" t="n">
         <v>30139074</v>
@@ -17822,7 +17822,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5653617.86</v>
+        <v>1286685.44</v>
       </c>
       <c r="L9" t="n">
         <v>27621810</v>
@@ -17863,7 +17863,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3463985.04</v>
+        <v>337949.76</v>
       </c>
       <c r="L10" t="n">
         <v>15706008</v>
@@ -17904,7 +17904,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>1396082.11</v>
+        <v>43627.57</v>
       </c>
       <c r="L11" t="n">
         <v>8494200</v>
@@ -17945,7 +17945,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>450114.12</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>3045600</v>
@@ -17986,7 +17986,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>92207.84</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>972000</v>
@@ -18068,7 +18068,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>264600</v>
@@ -18621,7 +18621,7 @@
         <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="L4" t="n">
         <v>217650</v>
@@ -18662,7 +18662,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>220</v>
+        <v>74</v>
       </c>
       <c r="L5" t="n">
         <v>275010</v>
@@ -18703,7 +18703,7 @@
         <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>214</v>
+        <v>58</v>
       </c>
       <c r="L6" t="n">
         <v>258240</v>
@@ -18744,7 +18744,7 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>198</v>
+        <v>53</v>
       </c>
       <c r="L7" t="n">
         <v>178560</v>
@@ -18785,7 +18785,7 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="L8" t="n">
         <v>116610</v>
@@ -18826,7 +18826,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="L9" t="n">
         <v>84540</v>
@@ -18867,7 +18867,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>42030</v>
@@ -18908,7 +18908,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
         <v>19110</v>
@@ -18949,7 +18949,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>4470</v>
@@ -19072,7 +19072,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
@@ -19666,7 +19666,7 @@
         <v>0.9</v>
       </c>
       <c r="K5" t="n">
-        <v>72.81999999999999</v>
+        <v>24.49</v>
       </c>
       <c r="L5" t="n">
         <v>57752.1</v>
@@ -19707,7 +19707,7 @@
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>108.5</v>
+        <v>29.41</v>
       </c>
       <c r="L6" t="n">
         <v>95548.8</v>
@@ -19748,7 +19748,7 @@
         <v>2.8</v>
       </c>
       <c r="K7" t="n">
-        <v>126.32</v>
+        <v>33.81</v>
       </c>
       <c r="L7" t="n">
         <v>107136</v>
@@ -19789,7 +19789,7 @@
         <v>2.55</v>
       </c>
       <c r="K8" t="n">
-        <v>92</v>
+        <v>22.82</v>
       </c>
       <c r="L8" t="n">
         <v>82793.10000000001</v>
@@ -19830,7 +19830,7 @@
         <v>2.85</v>
       </c>
       <c r="K9" t="n">
-        <v>71.47</v>
+        <v>16.86</v>
       </c>
       <c r="L9" t="n">
         <v>68477.39999999999</v>
@@ -19871,7 +19871,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>47.85</v>
+        <v>4.35</v>
       </c>
       <c r="L10" t="n">
         <v>37406.7</v>
@@ -19912,7 +19912,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>17.97</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
         <v>19110</v>
@@ -19953,7 +19953,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>4470</v>
@@ -20076,7 +20076,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>300</v>
@@ -20670,7 +20670,7 @@
         <v>21850.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3535847.92</v>
+        <v>1189330.66</v>
       </c>
       <c r="L5" t="n">
         <v>10395378</v>
@@ -20711,7 +20711,7 @@
         <v>97112</v>
       </c>
       <c r="K6" t="n">
-        <v>5268228.89</v>
+        <v>1427837.74</v>
       </c>
       <c r="L6" t="n">
         <v>17198784</v>
@@ -20752,7 +20752,7 @@
         <v>67978.39999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>6133788.14</v>
+        <v>1641872.58</v>
       </c>
       <c r="L7" t="n">
         <v>19284480</v>
@@ -20793,7 +20793,7 @@
         <v>61908.9</v>
       </c>
       <c r="K8" t="n">
-        <v>4467152</v>
+        <v>1107853.7</v>
       </c>
       <c r="L8" t="n">
         <v>14902758</v>
@@ -20834,7 +20834,7 @@
         <v>69192.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3470151.65</v>
+        <v>818799.83</v>
       </c>
       <c r="L9" t="n">
         <v>12325932</v>
@@ -20875,7 +20875,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>2323404.6</v>
+        <v>211218.6</v>
       </c>
       <c r="L10" t="n">
         <v>6733206</v>
@@ -20916,7 +20916,7 @@
         <v>48556</v>
       </c>
       <c r="K11" t="n">
-        <v>872551.3199999999</v>
+        <v>43627.57</v>
       </c>
       <c r="L11" t="n">
         <v>3439800</v>
@@ -20957,7 +20957,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>135034.24</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>804600</v>
@@ -21080,7 +21080,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>47876.22</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
         <v>54000</v>
@@ -21633,7 +21633,7 @@
         <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>256</v>
+        <v>71</v>
       </c>
       <c r="L4" t="n">
         <v>357900</v>
@@ -21674,7 +21674,7 @@
         <v>6</v>
       </c>
       <c r="K5" t="n">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
         <v>166560</v>
@@ -21715,7 +21715,7 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="L6" t="n">
         <v>61590</v>
@@ -21756,7 +21756,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>8640</v>
@@ -22678,7 +22678,7 @@
         <v>1.8</v>
       </c>
       <c r="K5" t="n">
-        <v>45.02</v>
+        <v>12.58</v>
       </c>
       <c r="L5" t="n">
         <v>34977.6</v>
@@ -22719,7 +22719,7 @@
         <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>23.32</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>22788.3</v>
@@ -22760,7 +22760,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>5184</v>
@@ -23682,7 +23682,7 @@
         <v>43700.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2185796.9</v>
+        <v>610737.37</v>
       </c>
       <c r="L5" t="n">
         <v>6295968</v>
@@ -23723,7 +23723,7 @@
         <v>12139</v>
       </c>
       <c r="K6" t="n">
-        <v>1132423.03</v>
+        <v>172325.24</v>
       </c>
       <c r="L6" t="n">
         <v>4101894</v>
@@ -23764,7 +23764,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>123914.91</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>933120</v>

--- a/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
+++ b/risk/Risk_Analysis_T3_25yrs_Present_RedCapacity.xlsx
@@ -560,7 +560,7 @@
         <v>474660</v>
       </c>
       <c r="H4" t="n">
-        <v>75570</v>
+        <v>82230</v>
       </c>
       <c r="I4" t="n">
         <v>9</v>
@@ -572,22 +572,22 @@
         <v>349</v>
       </c>
       <c r="L4" t="n">
-        <v>1287210</v>
+        <v>1375290</v>
       </c>
       <c r="M4" t="n">
-        <v>72930</v>
+        <v>49350</v>
       </c>
       <c r="N4" t="n">
-        <v>56190</v>
+        <v>64380</v>
       </c>
       <c r="O4" t="n">
-        <v>228840</v>
+        <v>241770</v>
       </c>
       <c r="P4" t="n">
-        <v>57390</v>
+        <v>19890</v>
       </c>
       <c r="Q4" t="n">
-        <v>192604.3</v>
+        <v>1995939.74</v>
       </c>
     </row>
     <row r="5">
@@ -613,7 +613,7 @@
         <v>354990</v>
       </c>
       <c r="H5" t="n">
-        <v>65610</v>
+        <v>70380</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -625,22 +625,22 @@
         <v>253</v>
       </c>
       <c r="L5" t="n">
-        <v>930960</v>
+        <v>966750</v>
       </c>
       <c r="M5" t="n">
-        <v>45720</v>
+        <v>37680</v>
       </c>
       <c r="N5" t="n">
-        <v>21030</v>
+        <v>30510</v>
       </c>
       <c r="O5" t="n">
-        <v>176130</v>
+        <v>199410</v>
       </c>
       <c r="P5" t="n">
-        <v>71880</v>
+        <v>49260</v>
       </c>
       <c r="Q5" t="n">
-        <v>143449.97</v>
+        <v>1486558.16</v>
       </c>
     </row>
     <row r="6">
@@ -666,7 +666,7 @@
         <v>243690</v>
       </c>
       <c r="H6" t="n">
-        <v>19050</v>
+        <v>21870</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
@@ -678,22 +678,22 @@
         <v>104</v>
       </c>
       <c r="L6" t="n">
-        <v>564330</v>
+        <v>597060</v>
       </c>
       <c r="M6" t="n">
-        <v>22110</v>
+        <v>30900</v>
       </c>
       <c r="N6" t="n">
-        <v>4980</v>
+        <v>9330</v>
       </c>
       <c r="O6" t="n">
-        <v>99780</v>
+        <v>115890</v>
       </c>
       <c r="P6" t="n">
-        <v>69210</v>
+        <v>54120</v>
       </c>
       <c r="Q6" t="n">
-        <v>105240.7</v>
+        <v>1090599.16</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>144630</v>
       </c>
       <c r="H7" t="n">
-        <v>5820</v>
+        <v>6960</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -731,22 +731,22 @@
         <v>88</v>
       </c>
       <c r="L7" t="n">
-        <v>334620</v>
+        <v>370290</v>
       </c>
       <c r="M7" t="n">
-        <v>14250</v>
+        <v>31860</v>
       </c>
       <c r="N7" t="n">
-        <v>720</v>
+        <v>2850</v>
       </c>
       <c r="O7" t="n">
-        <v>70530</v>
+        <v>78030</v>
       </c>
       <c r="P7" t="n">
-        <v>74070</v>
+        <v>62250</v>
       </c>
       <c r="Q7" t="n">
-        <v>80694.72</v>
+        <v>836231.61</v>
       </c>
     </row>
     <row r="8">
@@ -772,7 +772,7 @@
         <v>112740</v>
       </c>
       <c r="H8" t="n">
-        <v>5730</v>
+        <v>5580</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -784,22 +784,22 @@
         <v>38</v>
       </c>
       <c r="L8" t="n">
-        <v>235830</v>
+        <v>265950</v>
       </c>
       <c r="M8" t="n">
-        <v>9510</v>
+        <v>34950</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8" t="n">
-        <v>30180</v>
+        <v>49770</v>
       </c>
       <c r="P8" t="n">
-        <v>81270</v>
+        <v>78270</v>
       </c>
       <c r="Q8" t="n">
-        <v>52923.4</v>
+        <v>548440.0600000001</v>
       </c>
     </row>
     <row r="9">
@@ -825,7 +825,7 @@
         <v>72240</v>
       </c>
       <c r="H9" t="n">
-        <v>3330</v>
+        <v>4290</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -837,22 +837,22 @@
         <v>33</v>
       </c>
       <c r="L9" t="n">
-        <v>189450</v>
+        <v>226530</v>
       </c>
       <c r="M9" t="n">
-        <v>4920</v>
+        <v>28860</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8700</v>
+        <v>20190</v>
       </c>
       <c r="P9" t="n">
-        <v>81240</v>
+        <v>95310</v>
       </c>
       <c r="Q9" t="n">
-        <v>33978.41</v>
+        <v>352114.93</v>
       </c>
     </row>
     <row r="10">
@@ -878,7 +878,7 @@
         <v>40740</v>
       </c>
       <c r="H10" t="n">
-        <v>930</v>
+        <v>1470</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -890,22 +890,22 @@
         <v>8</v>
       </c>
       <c r="L10" t="n">
-        <v>98040</v>
+        <v>146460</v>
       </c>
       <c r="M10" t="n">
-        <v>2790</v>
+        <v>27630</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3750</v>
+        <v>11460</v>
       </c>
       <c r="P10" t="n">
-        <v>72660</v>
+        <v>113310</v>
       </c>
       <c r="Q10" t="n">
-        <v>21428.76</v>
+        <v>222064.19</v>
       </c>
     </row>
     <row r="11">
@@ -931,7 +931,7 @@
         <v>26250</v>
       </c>
       <c r="H11" t="n">
-        <v>810</v>
+        <v>1080</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -943,22 +943,22 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>47190</v>
+        <v>87750</v>
       </c>
       <c r="M11" t="n">
-        <v>2850</v>
+        <v>16140</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3540</v>
+        <v>4650</v>
       </c>
       <c r="P11" t="n">
-        <v>48180</v>
+        <v>81480</v>
       </c>
       <c r="Q11" t="n">
-        <v>12402</v>
+        <v>128520.69</v>
       </c>
     </row>
     <row r="12">
@@ -984,7 +984,7 @@
         <v>9060</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -996,22 +996,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16920</v>
+        <v>43530</v>
       </c>
       <c r="M12" t="n">
-        <v>660</v>
+        <v>18630</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>390</v>
+        <v>720</v>
       </c>
       <c r="P12" t="n">
-        <v>38820</v>
+        <v>62790</v>
       </c>
       <c r="Q12" t="n">
-        <v>6094.25</v>
+        <v>63154.15</v>
       </c>
     </row>
     <row r="13">
@@ -1037,7 +1037,7 @@
         <v>2340</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1049,22 +1049,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5400</v>
+        <v>18660</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>5130</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P13" t="n">
-        <v>28050</v>
+        <v>32280</v>
       </c>
       <c r="Q13" t="n">
-        <v>2447.83</v>
+        <v>25366.67</v>
       </c>
     </row>
     <row r="14">
@@ -1090,7 +1090,7 @@
         <v>1620</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1102,10 +1102,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2520</v>
+        <v>12690</v>
       </c>
       <c r="M14" t="n">
-        <v>300</v>
+        <v>1710</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>41610</v>
+        <v>61620</v>
       </c>
       <c r="Q14" t="n">
-        <v>1760.38</v>
+        <v>18242.63</v>
       </c>
     </row>
     <row r="15">
@@ -1143,7 +1143,7 @@
         <v>300</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1155,10 +1155,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1470</v>
+        <v>6210</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>1050</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -1167,10 +1167,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>17910</v>
+        <v>31740</v>
       </c>
       <c r="Q15" t="n">
-        <v>736</v>
+        <v>7627.12</v>
       </c>
     </row>
     <row r="16">
@@ -1208,10 +1208,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1470</v>
+        <v>5910</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>1980</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -1220,10 +1220,10 @@
         <v>30</v>
       </c>
       <c r="P16" t="n">
-        <v>17250</v>
+        <v>21030</v>
       </c>
       <c r="Q16" t="n">
-        <v>351.43</v>
+        <v>3641.82</v>
       </c>
     </row>
     <row r="17">
@@ -1249,7 +1249,7 @@
         <v>360</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1261,22 +1261,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>3000</v>
       </c>
       <c r="M17" t="n">
+        <v>450</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>90</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>30</v>
-      </c>
       <c r="P17" t="n">
-        <v>19620</v>
+        <v>35520</v>
       </c>
       <c r="Q17" t="n">
-        <v>198.65</v>
+        <v>2058.57</v>
       </c>
     </row>
     <row r="18">
@@ -1314,10 +1314,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>930</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>330</v>
+        <v>1680</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.54</v>
+        <v>223.2</v>
       </c>
     </row>
     <row r="19">
@@ -1382,7 +1382,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.03</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="20">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.11</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="21">
@@ -1852,7 +1852,7 @@
         <v>10560</v>
       </c>
       <c r="H4" t="n">
-        <v>3240</v>
+        <v>3900</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1864,22 +1864,22 @@
         <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>36030</v>
+        <v>26640</v>
       </c>
       <c r="M4" t="n">
-        <v>12270</v>
+        <v>2640</v>
       </c>
       <c r="N4" t="n">
-        <v>870</v>
+        <v>540</v>
       </c>
       <c r="O4" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>493.4</v>
+        <v>55918.44</v>
       </c>
     </row>
     <row r="5">
@@ -1905,7 +1905,7 @@
         <v>18780</v>
       </c>
       <c r="H5" t="n">
-        <v>2940</v>
+        <v>2610</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1917,22 +1917,22 @@
         <v>21</v>
       </c>
       <c r="L5" t="n">
-        <v>52440</v>
+        <v>41880</v>
       </c>
       <c r="M5" t="n">
-        <v>14910</v>
+        <v>8460</v>
       </c>
       <c r="N5" t="n">
-        <v>150</v>
+        <v>570</v>
       </c>
       <c r="O5" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>942</v>
+        <v>106760.34</v>
       </c>
     </row>
     <row r="6">
@@ -1958,7 +1958,7 @@
         <v>23310</v>
       </c>
       <c r="H6" t="n">
-        <v>5550</v>
+        <v>5700</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1970,22 +1970,22 @@
         <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>55650</v>
+        <v>56130</v>
       </c>
       <c r="M6" t="n">
-        <v>7170</v>
+        <v>5760</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="O6" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1712.74</v>
+        <v>194111.1</v>
       </c>
     </row>
     <row r="7">
@@ -2011,7 +2011,7 @@
         <v>16650</v>
       </c>
       <c r="H7" t="n">
-        <v>3720</v>
+        <v>4140</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>49740</v>
+        <v>51240</v>
       </c>
       <c r="M7" t="n">
-        <v>4440</v>
+        <v>4050</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1900.04</v>
+        <v>215338.32</v>
       </c>
     </row>
     <row r="8">
@@ -2064,7 +2064,7 @@
         <v>28290</v>
       </c>
       <c r="H8" t="n">
-        <v>5400</v>
+        <v>4740</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -2076,22 +2076,22 @@
         <v>3</v>
       </c>
       <c r="L8" t="n">
-        <v>73500</v>
+        <v>72690</v>
       </c>
       <c r="M8" t="n">
-        <v>2220</v>
+        <v>4980</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1829.92</v>
+        <v>207391.5</v>
       </c>
     </row>
     <row r="9">
@@ -2117,7 +2117,7 @@
         <v>34740</v>
       </c>
       <c r="H9" t="n">
-        <v>3270</v>
+        <v>4140</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -2129,22 +2129,22 @@
         <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>93120</v>
+        <v>98550</v>
       </c>
       <c r="M9" t="n">
-        <v>630</v>
+        <v>4590</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2160.49</v>
+        <v>244855.08</v>
       </c>
     </row>
     <row r="10">
@@ -2170,7 +2170,7 @@
         <v>24210</v>
       </c>
       <c r="H10" t="n">
-        <v>900</v>
+        <v>1080</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -2182,10 +2182,10 @@
         <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>50790</v>
+        <v>60630</v>
       </c>
       <c r="M10" t="n">
-        <v>300</v>
+        <v>4080</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1572.83</v>
+        <v>178254.18</v>
       </c>
     </row>
     <row r="11">
@@ -2223,7 +2223,7 @@
         <v>9930</v>
       </c>
       <c r="H11" t="n">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -2235,10 +2235,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>23970</v>
+        <v>30960</v>
       </c>
       <c r="M11" t="n">
-        <v>180</v>
+        <v>3450</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>668.01</v>
+        <v>75707.46000000001</v>
       </c>
     </row>
     <row r="12">
@@ -2276,7 +2276,7 @@
         <v>4170</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10860</v>
+        <v>16260</v>
       </c>
       <c r="M12" t="n">
-        <v>120</v>
+        <v>3120</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>407.43</v>
+        <v>46175.4</v>
       </c>
     </row>
     <row r="13">
@@ -2329,7 +2329,7 @@
         <v>1080</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -2341,10 +2341,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3480</v>
+        <v>7920</v>
       </c>
       <c r="M13" t="n">
-        <v>60</v>
+        <v>1470</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -2356,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>173.15</v>
+        <v>19623.78</v>
       </c>
     </row>
     <row r="14">
@@ -2382,7 +2382,7 @@
         <v>300</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -2394,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>3120</v>
       </c>
       <c r="M14" t="n">
-        <v>180</v>
+        <v>840</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>152.85</v>
+        <v>17322.66</v>
       </c>
     </row>
     <row r="15">
@@ -2435,7 +2435,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2447,10 +2447,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>900</v>
+        <v>2340</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>54.7</v>
+        <v>6199.56</v>
       </c>
     </row>
     <row r="16">
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1050</v>
+        <v>2370</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1860</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36.72</v>
+        <v>4161.6</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2553,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>30</v>
+        <v>870</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.16</v>
+        <v>810.9</v>
       </c>
     </row>
     <row r="18">
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.67</v>
+        <v>189.72</v>
       </c>
     </row>
     <row r="19">
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.08</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="20">
@@ -3197,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1058.4</v>
+        <v>939.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -3209,22 +3209,22 @@
         <v>6.95</v>
       </c>
       <c r="L5" t="n">
-        <v>11012.4</v>
+        <v>8794.799999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>298.2</v>
+        <v>169.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>5.7</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>47.1</v>
+        <v>5338.02</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3250,7 @@
         <v>1165.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3163.5</v>
+        <v>3249</v>
       </c>
       <c r="I6" t="n">
         <v>0.51</v>
@@ -3262,22 +3262,22 @@
         <v>4.06</v>
       </c>
       <c r="L6" t="n">
-        <v>20590.5</v>
+        <v>20768.1</v>
       </c>
       <c r="M6" t="n">
-        <v>573.6</v>
+        <v>460.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O6" t="n">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1284.56</v>
+        <v>145583.32</v>
       </c>
     </row>
     <row r="7">
@@ -3303,7 +3303,7 @@
         <v>2497.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2715.6</v>
+        <v>3022.2</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -3315,22 +3315,22 @@
         <v>2.55</v>
       </c>
       <c r="L7" t="n">
-        <v>29844</v>
+        <v>30744</v>
       </c>
       <c r="M7" t="n">
-        <v>1554</v>
+        <v>1417.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>10.5</v>
+        <v>42</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1520.04</v>
+        <v>172270.66</v>
       </c>
     </row>
     <row r="8">
@@ -3356,7 +3356,7 @@
         <v>18388.5</v>
       </c>
       <c r="H8" t="n">
-        <v>4590</v>
+        <v>4029</v>
       </c>
       <c r="I8" t="n">
         <v>1.47</v>
@@ -3368,22 +3368,22 @@
         <v>2.21</v>
       </c>
       <c r="L8" t="n">
-        <v>52185</v>
+        <v>51609.9</v>
       </c>
       <c r="M8" t="n">
-        <v>1221</v>
+        <v>2739</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1738.43</v>
+        <v>197021.92</v>
       </c>
     </row>
     <row r="9">
@@ -3409,7 +3409,7 @@
         <v>29529</v>
       </c>
       <c r="H9" t="n">
-        <v>3270</v>
+        <v>4140</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -3421,22 +3421,22 @@
         <v>5.62</v>
       </c>
       <c r="L9" t="n">
-        <v>75427.2</v>
+        <v>79825.5</v>
       </c>
       <c r="M9" t="n">
-        <v>441</v>
+        <v>3213</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>49.5</v>
+        <v>99</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2095.67</v>
+        <v>237509.43</v>
       </c>
     </row>
     <row r="10">
@@ -3462,7 +3462,7 @@
         <v>24210</v>
       </c>
       <c r="H10" t="n">
-        <v>900</v>
+        <v>1080</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -3474,10 +3474,10 @@
         <v>2.61</v>
       </c>
       <c r="L10" t="n">
-        <v>45203.1</v>
+        <v>53960.7</v>
       </c>
       <c r="M10" t="n">
-        <v>255</v>
+        <v>3468</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>1572.83</v>
+        <v>178254.18</v>
       </c>
     </row>
     <row r="11">
@@ -3515,7 +3515,7 @@
         <v>9930</v>
       </c>
       <c r="H11" t="n">
-        <v>750</v>
+        <v>900</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>23970</v>
+        <v>30960</v>
       </c>
       <c r="M11" t="n">
-        <v>162</v>
+        <v>3105</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>668.01</v>
+        <v>75707.46000000001</v>
       </c>
     </row>
     <row r="12">
@@ -3568,7 +3568,7 @@
         <v>4170</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -3580,10 +3580,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10860</v>
+        <v>16260</v>
       </c>
       <c r="M12" t="n">
-        <v>114</v>
+        <v>2964</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>407.43</v>
+        <v>46175.4</v>
       </c>
     </row>
     <row r="13">
@@ -3621,7 +3621,7 @@
         <v>1080</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -3633,10 +3633,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>3480</v>
+        <v>7920</v>
       </c>
       <c r="M13" t="n">
-        <v>60</v>
+        <v>1470</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>173.15</v>
+        <v>19623.78</v>
       </c>
     </row>
     <row r="14">
@@ -3674,7 +3674,7 @@
         <v>300</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -3686,10 +3686,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1290</v>
+        <v>3120</v>
       </c>
       <c r="M14" t="n">
-        <v>180</v>
+        <v>840</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>152.85</v>
+        <v>17322.66</v>
       </c>
     </row>
     <row r="15">
@@ -3727,7 +3727,7 @@
         <v>90</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -3739,10 +3739,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>900</v>
+        <v>2340</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>54.7</v>
+        <v>6199.56</v>
       </c>
     </row>
     <row r="16">
@@ -3792,10 +3792,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1050</v>
+        <v>2370</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1860</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>36.72</v>
+        <v>4161.6</v>
       </c>
     </row>
     <row r="17">
@@ -3833,7 +3833,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -3845,10 +3845,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>30</v>
+        <v>870</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>7.16</v>
+        <v>810.9</v>
       </c>
     </row>
     <row r="18">
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.67</v>
+        <v>189.72</v>
       </c>
     </row>
     <row r="19">
@@ -3966,7 +3966,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.08</v>
+        <v>9.18</v>
       </c>
     </row>
     <row r="20">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6032880</v>
+        <v>5355720</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -4501,22 +4501,22 @@
         <v>337512.76</v>
       </c>
       <c r="L5" t="n">
-        <v>1982232</v>
+        <v>1583064</v>
       </c>
       <c r="M5" t="n">
-        <v>104370</v>
+        <v>59220</v>
       </c>
       <c r="N5" t="n">
-        <v>255</v>
+        <v>969</v>
       </c>
       <c r="O5" t="n">
-        <v>3060</v>
+        <v>3570</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>28260.09</v>
+        <v>3202810.2</v>
       </c>
     </row>
     <row r="6">
@@ -4542,7 +4542,7 @@
         <v>62937</v>
       </c>
       <c r="H6" t="n">
-        <v>18031950</v>
+        <v>18519300</v>
       </c>
       <c r="I6" t="n">
         <v>98471.57000000001</v>
@@ -4554,22 +4554,22 @@
         <v>196943.14</v>
       </c>
       <c r="L6" t="n">
-        <v>3706290</v>
+        <v>3738258</v>
       </c>
       <c r="M6" t="n">
-        <v>200760</v>
+        <v>161280</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1275</v>
       </c>
       <c r="O6" t="n">
-        <v>7650</v>
+        <v>6375</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>770735.25</v>
+        <v>87349995</v>
       </c>
     </row>
     <row r="7">
@@ -4595,7 +4595,7 @@
         <v>134865</v>
       </c>
       <c r="H7" t="n">
-        <v>15478920</v>
+        <v>17226540</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -4607,22 +4607,22 @@
         <v>123914.91</v>
       </c>
       <c r="L7" t="n">
-        <v>5371920</v>
+        <v>5533920</v>
       </c>
       <c r="M7" t="n">
-        <v>543900</v>
+        <v>496125</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1785</v>
+        <v>7140</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>912021.12</v>
+        <v>103362393.6</v>
       </c>
     </row>
     <row r="8">
@@ -4648,7 +4648,7 @@
         <v>992979</v>
       </c>
       <c r="H8" t="n">
-        <v>26163000</v>
+        <v>22965300</v>
       </c>
       <c r="I8" t="n">
         <v>285897.73</v>
@@ -4660,22 +4660,22 @@
         <v>107211.65</v>
       </c>
       <c r="L8" t="n">
-        <v>9393300</v>
+        <v>9289782</v>
       </c>
       <c r="M8" t="n">
-        <v>427350</v>
+        <v>958650</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>13770</v>
+        <v>9180</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1043057.25</v>
+        <v>118213155</v>
       </c>
     </row>
     <row r="9">
@@ -4701,7 +4701,7 @@
         <v>1594566</v>
       </c>
       <c r="H9" t="n">
-        <v>18639000</v>
+        <v>23598000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4713,22 +4713,22 @@
         <v>272933.28</v>
       </c>
       <c r="L9" t="n">
-        <v>13576896</v>
+        <v>14368590</v>
       </c>
       <c r="M9" t="n">
-        <v>154350</v>
+        <v>1124550</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8415</v>
+        <v>16830</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1257402.85</v>
+        <v>142505656.56</v>
       </c>
     </row>
     <row r="10">
@@ -4754,7 +4754,7 @@
         <v>1307340</v>
       </c>
       <c r="H10" t="n">
-        <v>5130000</v>
+        <v>6156000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -4766,10 +4766,10 @@
         <v>126731.16</v>
       </c>
       <c r="L10" t="n">
-        <v>8136558</v>
+        <v>9712926</v>
       </c>
       <c r="M10" t="n">
-        <v>89250</v>
+        <v>1213800</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>943698.6</v>
+        <v>106952508</v>
       </c>
     </row>
     <row r="11">
@@ -4807,7 +4807,7 @@
         <v>536220</v>
       </c>
       <c r="H11" t="n">
-        <v>4275000</v>
+        <v>5130000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -4819,10 +4819,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4314600</v>
+        <v>5572800</v>
       </c>
       <c r="M11" t="n">
-        <v>56700</v>
+        <v>1086750</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>400804.2</v>
+        <v>45424476</v>
       </c>
     </row>
     <row r="12">
@@ -4860,7 +4860,7 @@
         <v>225180</v>
       </c>
       <c r="H12" t="n">
-        <v>855000</v>
+        <v>1026000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1954800</v>
+        <v>2926800</v>
       </c>
       <c r="M12" t="n">
-        <v>39900</v>
+        <v>1037400</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -4887,7 +4887,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>244458</v>
+        <v>27705240</v>
       </c>
     </row>
     <row r="13">
@@ -4913,7 +4913,7 @@
         <v>58320</v>
       </c>
       <c r="H13" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -4925,10 +4925,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>626400</v>
+        <v>1425600</v>
       </c>
       <c r="M13" t="n">
-        <v>21000</v>
+        <v>514500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>103890.6</v>
+        <v>11774268</v>
       </c>
     </row>
     <row r="14">
@@ -4966,7 +4966,7 @@
         <v>16200</v>
       </c>
       <c r="H14" t="n">
-        <v>513000</v>
+        <v>342000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -4978,10 +4978,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>232200</v>
+        <v>561600</v>
       </c>
       <c r="M14" t="n">
-        <v>63000</v>
+        <v>294000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>91708.2</v>
+        <v>10393596</v>
       </c>
     </row>
     <row r="15">
@@ -5019,7 +5019,7 @@
         <v>4860</v>
       </c>
       <c r="H15" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -5031,10 +5031,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>162000</v>
+        <v>421200</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>336000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -5046,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>32821.2</v>
+        <v>3719736</v>
       </c>
     </row>
     <row r="16">
@@ -5084,10 +5084,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>189000</v>
+        <v>426600</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>651000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5099,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>22032</v>
+        <v>2496960</v>
       </c>
     </row>
     <row r="17">
@@ -5125,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -5137,10 +5137,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>5400</v>
+        <v>156600</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>136500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -5152,7 +5152,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4293</v>
+        <v>486540</v>
       </c>
     </row>
     <row r="18">
@@ -5190,7 +5190,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1004.4</v>
+        <v>113832</v>
       </c>
     </row>
     <row r="19">
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>48.6</v>
+        <v>5508</v>
       </c>
     </row>
     <row r="20">
@@ -5728,7 +5728,7 @@
         <v>30690</v>
       </c>
       <c r="H4" t="n">
-        <v>1710</v>
+        <v>3030</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -5740,22 +5740,22 @@
         <v>29</v>
       </c>
       <c r="L4" t="n">
-        <v>103230</v>
+        <v>119460</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>3150</v>
+        <v>3690</v>
       </c>
       <c r="O4" t="n">
-        <v>18780</v>
+        <v>20790</v>
       </c>
       <c r="P4" t="n">
-        <v>10530</v>
+        <v>9180</v>
       </c>
       <c r="Q4" t="n">
-        <v>17902.47</v>
+        <v>94223.52</v>
       </c>
     </row>
     <row r="5">
@@ -5781,7 +5781,7 @@
         <v>9840</v>
       </c>
       <c r="H5" t="n">
-        <v>480</v>
+        <v>810</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
         <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>35310</v>
+        <v>50190</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1350</v>
+        <v>1920</v>
       </c>
       <c r="O5" t="n">
-        <v>4440</v>
+        <v>8370</v>
       </c>
       <c r="P5" t="n">
-        <v>8310</v>
+        <v>12510</v>
       </c>
       <c r="Q5" t="n">
-        <v>6682.34</v>
+        <v>35170.2</v>
       </c>
     </row>
     <row r="6">
@@ -5834,7 +5834,7 @@
         <v>1650</v>
       </c>
       <c r="H6" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -5846,7 +5846,7 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>8190</v>
+        <v>11700</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -5855,13 +5855,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>210</v>
+        <v>810</v>
       </c>
       <c r="P6" t="n">
-        <v>5970</v>
+        <v>8250</v>
       </c>
       <c r="Q6" t="n">
-        <v>409.17</v>
+        <v>2153.52</v>
       </c>
     </row>
     <row r="7">
@@ -5887,7 +5887,7 @@
         <v>240</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -5899,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1560</v>
+        <v>3270</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -5911,10 +5911,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>5790</v>
+        <v>8880</v>
       </c>
       <c r="Q7" t="n">
-        <v>74.48999999999999</v>
+        <v>392.04</v>
       </c>
     </row>
     <row r="8">
@@ -5952,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>360</v>
+        <v>1530</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -5964,10 +5964,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>4860</v>
+        <v>9840</v>
       </c>
       <c r="Q8" t="n">
-        <v>39.81</v>
+        <v>209.52</v>
       </c>
     </row>
     <row r="9">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>150</v>
+        <v>870</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>4350</v>
+        <v>11850</v>
       </c>
       <c r="Q9" t="n">
-        <v>25.65</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -6070,10 +6070,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>510</v>
+        <v>1440</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.82</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
@@ -7073,7 +7073,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>172.8</v>
+        <v>291.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -7085,22 +7085,22 @@
         <v>2.32</v>
       </c>
       <c r="L5" t="n">
-        <v>7415.1</v>
+        <v>10539.9</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>13.5</v>
+        <v>19.2</v>
       </c>
       <c r="O5" t="n">
-        <v>222</v>
+        <v>418.5</v>
       </c>
       <c r="P5" t="n">
-        <v>166.2</v>
+        <v>250.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>334.12</v>
+        <v>1758.51</v>
       </c>
     </row>
     <row r="6">
@@ -7126,7 +7126,7 @@
         <v>82.5</v>
       </c>
       <c r="H6" t="n">
-        <v>85.5</v>
+        <v>171</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -7138,7 +7138,7 @@
         <v>0.51</v>
       </c>
       <c r="L6" t="n">
-        <v>3030.3</v>
+        <v>4329</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -7147,13 +7147,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>52.5</v>
+        <v>202.5</v>
       </c>
       <c r="P6" t="n">
-        <v>895.5</v>
+        <v>1237.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>306.88</v>
+        <v>1615.14</v>
       </c>
     </row>
     <row r="7">
@@ -7179,7 +7179,7 @@
         <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -7191,7 +7191,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>936</v>
+        <v>1962</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1447.5</v>
+        <v>2220</v>
       </c>
       <c r="Q7" t="n">
-        <v>59.59</v>
+        <v>313.63</v>
       </c>
     </row>
     <row r="8">
@@ -7244,7 +7244,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>255.6</v>
+        <v>1086.3</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -7256,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1846.8</v>
+        <v>3739.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.82</v>
+        <v>199.04</v>
       </c>
     </row>
     <row r="9">
@@ -7297,7 +7297,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>121.5</v>
+        <v>704.7</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -7309,10 +7309,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2175</v>
+        <v>5925</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.88</v>
+        <v>130.95</v>
       </c>
     </row>
     <row r="10">
@@ -7350,7 +7350,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -7362,10 +7362,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>433.5</v>
+        <v>1224</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.82</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="11">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>984960</v>
+        <v>1662120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -8377,22 +8377,22 @@
         <v>112504.25</v>
       </c>
       <c r="L5" t="n">
-        <v>1334718</v>
+        <v>1897182</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2295</v>
+        <v>3264</v>
       </c>
       <c r="O5" t="n">
-        <v>37740</v>
+        <v>71145</v>
       </c>
       <c r="P5" t="n">
-        <v>10803</v>
+        <v>16263</v>
       </c>
       <c r="Q5" t="n">
-        <v>200470.14</v>
+        <v>1055106</v>
       </c>
     </row>
     <row r="6">
@@ -8418,7 +8418,7 @@
         <v>4455</v>
       </c>
       <c r="H6" t="n">
-        <v>487350</v>
+        <v>974700</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -8430,7 +8430,7 @@
         <v>24617.89</v>
       </c>
       <c r="L6" t="n">
-        <v>545454</v>
+        <v>779220</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -8439,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>8925</v>
+        <v>34425</v>
       </c>
       <c r="P6" t="n">
-        <v>58207.5</v>
+        <v>80437.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>184125.96</v>
+        <v>969084</v>
       </c>
     </row>
     <row r="7">
@@ -8471,7 +8471,7 @@
         <v>1944</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>249660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -8483,7 +8483,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>168480</v>
+        <v>353160</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -8495,10 +8495,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>94087.5</v>
+        <v>144300</v>
       </c>
       <c r="Q7" t="n">
-        <v>35754.05</v>
+        <v>188179.2</v>
       </c>
     </row>
     <row r="8">
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>46008</v>
+        <v>195534</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -8548,10 +8548,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>120042</v>
+        <v>243048</v>
       </c>
       <c r="Q8" t="n">
-        <v>22691.02</v>
+        <v>119426.4</v>
       </c>
     </row>
     <row r="9">
@@ -8589,7 +8589,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>21870</v>
+        <v>126846</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -8601,10 +8601,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>141375</v>
+        <v>385125</v>
       </c>
       <c r="Q9" t="n">
-        <v>14928.3</v>
+        <v>78570</v>
       </c>
     </row>
     <row r="10">
@@ -8642,7 +8642,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>4806</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -8654,10 +8654,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>28177.5</v>
+        <v>79560</v>
       </c>
       <c r="Q10" t="n">
-        <v>492.48</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="11">
@@ -9604,7 +9604,7 @@
         <v>42450</v>
       </c>
       <c r="H4" t="n">
-        <v>3390</v>
+        <v>3360</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -9616,22 +9616,22 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>53880</v>
+        <v>70620</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>17370</v>
+        <v>21420</v>
       </c>
       <c r="O4" t="n">
-        <v>26940</v>
+        <v>28380</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18343.68</v>
+        <v>99539.37</v>
       </c>
     </row>
     <row r="5">
@@ -9657,7 +9657,7 @@
         <v>10380</v>
       </c>
       <c r="H5" t="n">
-        <v>2520</v>
+        <v>3060</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -9669,22 +9669,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>13770</v>
+        <v>16830</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>6360</v>
+        <v>6870</v>
       </c>
       <c r="O5" t="n">
-        <v>27480</v>
+        <v>26160</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2957.53</v>
+        <v>16048.62</v>
       </c>
     </row>
     <row r="6">
@@ -9710,7 +9710,7 @@
         <v>2820</v>
       </c>
       <c r="H6" t="n">
-        <v>420</v>
+        <v>660</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -9722,22 +9722,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>2640</v>
+        <v>5880</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2460</v>
+        <v>3870</v>
       </c>
       <c r="O6" t="n">
-        <v>20130</v>
+        <v>23730</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>473.57</v>
+        <v>2569.77</v>
       </c>
     </row>
     <row r="7">
@@ -9763,7 +9763,7 @@
         <v>750</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>330</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -9775,22 +9775,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>510</v>
+        <v>1170</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>150</v>
+        <v>1230</v>
       </c>
       <c r="O7" t="n">
-        <v>6000</v>
+        <v>8040</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>90.56</v>
+        <v>491.4</v>
       </c>
     </row>
     <row r="8">
@@ -9837,13 +9837,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>990</v>
+        <v>2040</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15.09</v>
+        <v>81.90000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -9890,13 +9890,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>240</v>
+        <v>540</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.86</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="10">
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>907.2</v>
+        <v>1101.6</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -10961,22 +10961,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2891.7</v>
+        <v>3534.3</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>63.6</v>
+        <v>68.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1374</v>
+        <v>1308</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>147.88</v>
+        <v>802.4299999999999</v>
       </c>
     </row>
     <row r="6">
@@ -11002,7 +11002,7 @@
         <v>141</v>
       </c>
       <c r="H6" t="n">
-        <v>239.4</v>
+        <v>376.2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -11014,22 +11014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>976.8</v>
+        <v>2175.6</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>123</v>
+        <v>193.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5032.5</v>
+        <v>5932.5</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>355.18</v>
+        <v>1927.33</v>
       </c>
     </row>
     <row r="7">
@@ -11055,7 +11055,7 @@
         <v>112.5</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>240.9</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -11067,22 +11067,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>306</v>
+        <v>702</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>10.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>2100</v>
+        <v>2814</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>72.45</v>
+        <v>393.12</v>
       </c>
     </row>
     <row r="8">
@@ -11129,13 +11129,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>445.5</v>
+        <v>918</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>14.34</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="9">
@@ -11182,13 +11182,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>132</v>
+        <v>297</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -12241,7 +12241,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5171040</v>
+        <v>6279120</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -12253,22 +12253,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>520506</v>
+        <v>636174</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10812</v>
+        <v>11679</v>
       </c>
       <c r="O5" t="n">
-        <v>233580</v>
+        <v>222360</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>88725.94</v>
+        <v>481458.6</v>
       </c>
     </row>
     <row r="6">
@@ -12294,7 +12294,7 @@
         <v>7614</v>
       </c>
       <c r="H6" t="n">
-        <v>1364580</v>
+        <v>2144340</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -12306,22 +12306,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>175824</v>
+        <v>391608</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>20910</v>
+        <v>32895</v>
       </c>
       <c r="O6" t="n">
-        <v>855525</v>
+        <v>1008525</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>213107.36</v>
+        <v>1156396.5</v>
       </c>
     </row>
     <row r="7">
@@ -12347,7 +12347,7 @@
         <v>6075</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1373130</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -12359,22 +12359,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>55080</v>
+        <v>126360</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1785</v>
+        <v>14637</v>
       </c>
       <c r="O7" t="n">
-        <v>357000</v>
+        <v>478380</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>43467.84</v>
+        <v>235872</v>
       </c>
     </row>
     <row r="8">
@@ -12421,13 +12421,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>75735</v>
+        <v>156060</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>8603.01</v>
+        <v>46683</v>
       </c>
     </row>
     <row r="9">
@@ -12474,13 +12474,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>22440</v>
+        <v>50490</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1081.12</v>
+        <v>5866.56</v>
       </c>
     </row>
     <row r="10">
@@ -13480,7 +13480,7 @@
         <v>100320</v>
       </c>
       <c r="H4" t="n">
-        <v>10080</v>
+        <v>11520</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -13492,19 +13492,19 @@
         <v>125</v>
       </c>
       <c r="L4" t="n">
-        <v>230880</v>
+        <v>223350</v>
       </c>
       <c r="M4" t="n">
-        <v>19110</v>
+        <v>1470</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>38670</v>
+        <v>41700</v>
       </c>
       <c r="P4" t="n">
-        <v>33090</v>
+        <v>6840</v>
       </c>
       <c r="Q4" t="n">
         <v>43376.02</v>
@@ -13533,7 +13533,7 @@
         <v>100080</v>
       </c>
       <c r="H5" t="n">
-        <v>12930</v>
+        <v>13350</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -13545,19 +13545,19 @@
         <v>102</v>
       </c>
       <c r="L5" t="n">
-        <v>265440</v>
+        <v>256620</v>
       </c>
       <c r="M5" t="n">
-        <v>14970</v>
+        <v>4350</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>42840</v>
+        <v>49350</v>
       </c>
       <c r="P5" t="n">
-        <v>42390</v>
+        <v>23970</v>
       </c>
       <c r="Q5" t="n">
         <v>51587.21</v>
@@ -13586,7 +13586,7 @@
         <v>62160</v>
       </c>
       <c r="H6" t="n">
-        <v>5250</v>
+        <v>5880</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
@@ -13598,19 +13598,19 @@
         <v>30</v>
       </c>
       <c r="L6" t="n">
-        <v>124110</v>
+        <v>118320</v>
       </c>
       <c r="M6" t="n">
-        <v>6900</v>
+        <v>5550</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>26670</v>
+        <v>27450</v>
       </c>
       <c r="P6" t="n">
-        <v>36900</v>
+        <v>31920</v>
       </c>
       <c r="Q6" t="n">
         <v>36820.52</v>
@@ -13639,7 +13639,7 @@
         <v>39810</v>
       </c>
       <c r="H7" t="n">
-        <v>780</v>
+        <v>660</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -13651,19 +13651,19 @@
         <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>69540</v>
+        <v>71910</v>
       </c>
       <c r="M7" t="n">
-        <v>3750</v>
+        <v>9510</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>24570</v>
+        <v>26160</v>
       </c>
       <c r="P7" t="n">
-        <v>33420</v>
+        <v>31710</v>
       </c>
       <c r="Q7" t="n">
         <v>26386.48</v>
@@ -13692,7 +13692,7 @@
         <v>10890</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -13704,19 +13704,19 @@
         <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>32610</v>
+        <v>41880</v>
       </c>
       <c r="M8" t="n">
-        <v>2130</v>
+        <v>12030</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>8790</v>
+        <v>12750</v>
       </c>
       <c r="P8" t="n">
-        <v>39180</v>
+        <v>41370</v>
       </c>
       <c r="Q8" t="n">
         <v>10481.47</v>
@@ -13757,19 +13757,19 @@
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>8430</v>
+        <v>21300</v>
       </c>
       <c r="M9" t="n">
-        <v>1020</v>
+        <v>12600</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>390</v>
+        <v>1530</v>
       </c>
       <c r="P9" t="n">
-        <v>37890</v>
+        <v>41760</v>
       </c>
       <c r="Q9" t="n">
         <v>856.2</v>
@@ -13810,10 +13810,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3720</v>
+        <v>24330</v>
       </c>
       <c r="M10" t="n">
-        <v>240</v>
+        <v>10080</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -13822,7 +13822,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>34980</v>
+        <v>56430</v>
       </c>
       <c r="Q10" t="n">
         <v>281.79</v>
@@ -13863,19 +13863,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3540</v>
+        <v>25890</v>
       </c>
       <c r="M11" t="n">
-        <v>360</v>
+        <v>6330</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P11" t="n">
-        <v>25350</v>
+        <v>49200</v>
       </c>
       <c r="Q11" t="n">
         <v>258.8</v>
@@ -13904,7 +13904,7 @@
         <v>240</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -13916,10 +13916,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1530</v>
+        <v>15450</v>
       </c>
       <c r="M12" t="n">
-        <v>120</v>
+        <v>9720</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -13928,7 +13928,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14430</v>
+        <v>25110</v>
       </c>
       <c r="Q12" t="n">
         <v>49.1</v>
@@ -13969,10 +13969,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>450</v>
+        <v>5940</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>810</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -13981,7 +13981,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12150</v>
+        <v>14700</v>
       </c>
       <c r="Q13" t="n">
         <v>20.31</v>
@@ -14022,10 +14022,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>180</v>
+        <v>5220</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -14034,7 +14034,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14790</v>
+        <v>27000</v>
       </c>
       <c r="Q14" t="n">
         <v>20.42</v>
@@ -14075,10 +14075,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>270</v>
+        <v>2160</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -14087,7 +14087,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5850</v>
+        <v>16380</v>
       </c>
       <c r="Q15" t="n">
         <v>9.82</v>
@@ -14128,7 +14128,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>360</v>
+        <v>2400</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2880</v>
+        <v>6690</v>
       </c>
       <c r="Q16" t="n">
         <v>5.36</v>
@@ -14181,7 +14181,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>450</v>
+        <v>660</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -14193,7 +14193,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>420</v>
+        <v>660</v>
       </c>
       <c r="Q17" t="n">
         <v>0.67</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -14825,7 +14825,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>23619.6</v>
+        <v>25336.8</v>
       </c>
       <c r="I5" t="n">
         <v>0.66</v>
@@ -14837,22 +14837,22 @@
         <v>83.73999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>195501.6</v>
+        <v>203017.5</v>
       </c>
       <c r="M5" t="n">
-        <v>914.4</v>
+        <v>753.6</v>
       </c>
       <c r="N5" t="n">
-        <v>210.3</v>
+        <v>305.1</v>
       </c>
       <c r="O5" t="n">
-        <v>8806.5</v>
+        <v>9970.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1437.6</v>
+        <v>985.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>7172.5</v>
+        <v>74327.91</v>
       </c>
     </row>
     <row r="6">
@@ -14878,7 +14878,7 @@
         <v>12184.5</v>
       </c>
       <c r="H6" t="n">
-        <v>10858.5</v>
+        <v>12465.9</v>
       </c>
       <c r="I6" t="n">
         <v>2.03</v>
@@ -14890,22 +14890,22 @@
         <v>52.73</v>
       </c>
       <c r="L6" t="n">
-        <v>208802.1</v>
+        <v>220912.2</v>
       </c>
       <c r="M6" t="n">
-        <v>1768.8</v>
+        <v>2472</v>
       </c>
       <c r="N6" t="n">
-        <v>249</v>
+        <v>466.5</v>
       </c>
       <c r="O6" t="n">
-        <v>24945</v>
+        <v>28972.5</v>
       </c>
       <c r="P6" t="n">
-        <v>10381.5</v>
+        <v>8118</v>
       </c>
       <c r="Q6" t="n">
-        <v>78930.52</v>
+        <v>817949.37</v>
       </c>
     </row>
     <row r="7">
@@ -14931,7 +14931,7 @@
         <v>21694.5</v>
       </c>
       <c r="H7" t="n">
-        <v>4248.6</v>
+        <v>5080.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -14943,22 +14943,22 @@
         <v>56.14</v>
       </c>
       <c r="L7" t="n">
-        <v>200772</v>
+        <v>222174</v>
       </c>
       <c r="M7" t="n">
-        <v>4987.5</v>
+        <v>11151</v>
       </c>
       <c r="N7" t="n">
-        <v>50.4</v>
+        <v>199.5</v>
       </c>
       <c r="O7" t="n">
-        <v>24685.5</v>
+        <v>27310.5</v>
       </c>
       <c r="P7" t="n">
-        <v>18517.5</v>
+        <v>15562.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>64555.78</v>
+        <v>668985.29</v>
       </c>
     </row>
     <row r="8">
@@ -14984,7 +14984,7 @@
         <v>73281</v>
       </c>
       <c r="H8" t="n">
-        <v>4870.5</v>
+        <v>4743</v>
       </c>
       <c r="I8" t="n">
         <v>2.21</v>
@@ -14996,22 +14996,22 @@
         <v>27.97</v>
       </c>
       <c r="L8" t="n">
-        <v>167439.3</v>
+        <v>188824.5</v>
       </c>
       <c r="M8" t="n">
-        <v>5230.5</v>
+        <v>19222.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O8" t="n">
-        <v>13581</v>
+        <v>22396.5</v>
       </c>
       <c r="P8" t="n">
-        <v>30882.6</v>
+        <v>29742.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>50277.23</v>
+        <v>521018.05</v>
       </c>
     </row>
     <row r="9">
@@ -15037,7 +15037,7 @@
         <v>61404</v>
       </c>
       <c r="H9" t="n">
-        <v>3330</v>
+        <v>4290</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -15049,22 +15049,22 @@
         <v>26.5</v>
       </c>
       <c r="L9" t="n">
-        <v>153454.5</v>
+        <v>183489.3</v>
       </c>
       <c r="M9" t="n">
-        <v>3444</v>
+        <v>20202</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>4785</v>
+        <v>11104.5</v>
       </c>
       <c r="P9" t="n">
-        <v>40620</v>
+        <v>47655</v>
       </c>
       <c r="Q9" t="n">
-        <v>32959.05</v>
+        <v>341551.48</v>
       </c>
     </row>
     <row r="10">
@@ -15090,7 +15090,7 @@
         <v>40740</v>
       </c>
       <c r="H10" t="n">
-        <v>930</v>
+        <v>1470</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -15102,22 +15102,22 @@
         <v>6.96</v>
       </c>
       <c r="L10" t="n">
-        <v>87255.60000000001</v>
+        <v>130349.4</v>
       </c>
       <c r="M10" t="n">
-        <v>2371.5</v>
+        <v>23485.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2625</v>
+        <v>8022</v>
       </c>
       <c r="P10" t="n">
-        <v>61761</v>
+        <v>96313.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>21428.76</v>
+        <v>222064.19</v>
       </c>
     </row>
     <row r="11">
@@ -15143,7 +15143,7 @@
         <v>26250</v>
       </c>
       <c r="H11" t="n">
-        <v>810</v>
+        <v>1080</v>
       </c>
       <c r="I11" t="n">
         <v>0.9</v>
@@ -15155,22 +15155,22 @@
         <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>47190</v>
+        <v>87750</v>
       </c>
       <c r="M11" t="n">
-        <v>2565</v>
+        <v>14526</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3009</v>
+        <v>3952.5</v>
       </c>
       <c r="P11" t="n">
-        <v>43362</v>
+        <v>73332</v>
       </c>
       <c r="Q11" t="n">
-        <v>12402</v>
+        <v>128520.69</v>
       </c>
     </row>
     <row r="12">
@@ -15196,7 +15196,7 @@
         <v>9060</v>
       </c>
       <c r="H12" t="n">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -15208,22 +15208,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>16920</v>
+        <v>43530</v>
       </c>
       <c r="M12" t="n">
-        <v>627</v>
+        <v>17698.5</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>390</v>
+        <v>720</v>
       </c>
       <c r="P12" t="n">
-        <v>38820</v>
+        <v>62790</v>
       </c>
       <c r="Q12" t="n">
-        <v>6094.25</v>
+        <v>63154.15</v>
       </c>
     </row>
     <row r="13">
@@ -15249,7 +15249,7 @@
         <v>2340</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -15261,22 +15261,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>5400</v>
+        <v>18660</v>
       </c>
       <c r="M13" t="n">
-        <v>180</v>
+        <v>5130</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P13" t="n">
-        <v>28050</v>
+        <v>32280</v>
       </c>
       <c r="Q13" t="n">
-        <v>2447.83</v>
+        <v>25366.67</v>
       </c>
     </row>
     <row r="14">
@@ -15302,7 +15302,7 @@
         <v>1620</v>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -15314,10 +15314,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>2520</v>
+        <v>12690</v>
       </c>
       <c r="M14" t="n">
-        <v>300</v>
+        <v>1710</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -15326,10 +15326,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>41610</v>
+        <v>61620</v>
       </c>
       <c r="Q14" t="n">
-        <v>1760.38</v>
+        <v>18242.63</v>
       </c>
     </row>
     <row r="15">
@@ -15355,7 +15355,7 @@
         <v>300</v>
       </c>
       <c r="H15" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -15367,10 +15367,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1470</v>
+        <v>6210</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>1050</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -15379,10 +15379,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>17910</v>
+        <v>31740</v>
       </c>
       <c r="Q15" t="n">
-        <v>736</v>
+        <v>7627.12</v>
       </c>
     </row>
     <row r="16">
@@ -15420,10 +15420,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1470</v>
+        <v>5910</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>1980</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -15432,10 +15432,10 @@
         <v>30</v>
       </c>
       <c r="P16" t="n">
-        <v>17250</v>
+        <v>21030</v>
       </c>
       <c r="Q16" t="n">
-        <v>351.43</v>
+        <v>3641.82</v>
       </c>
     </row>
     <row r="17">
@@ -15461,7 +15461,7 @@
         <v>360</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -15473,22 +15473,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>570</v>
+        <v>3000</v>
       </c>
       <c r="M17" t="n">
+        <v>450</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>90</v>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>30</v>
-      </c>
       <c r="P17" t="n">
-        <v>19620</v>
+        <v>35520</v>
       </c>
       <c r="Q17" t="n">
-        <v>198.65</v>
+        <v>2058.57</v>
       </c>
     </row>
     <row r="18">
@@ -15526,10 +15526,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>930</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -15538,10 +15538,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>330</v>
+        <v>1680</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.54</v>
+        <v>223.2</v>
       </c>
     </row>
     <row r="19">
@@ -15594,7 +15594,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>7.03</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="20">
@@ -15647,7 +15647,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.11</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="21">
@@ -16117,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4654.8</v>
+        <v>4806</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -16129,19 +16129,19 @@
         <v>33.76</v>
       </c>
       <c r="L5" t="n">
-        <v>55742.4</v>
+        <v>53890.2</v>
       </c>
       <c r="M5" t="n">
-        <v>299.4</v>
+        <v>87</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2142</v>
+        <v>2467.5</v>
       </c>
       <c r="P5" t="n">
-        <v>847.8</v>
+        <v>479.4</v>
       </c>
       <c r="Q5" t="n">
         <v>2579.36</v>
@@ -16170,7 +16170,7 @@
         <v>3108</v>
       </c>
       <c r="H6" t="n">
-        <v>2992.5</v>
+        <v>3351.6</v>
       </c>
       <c r="I6" t="n">
         <v>1.52</v>
@@ -16182,19 +16182,19 @@
         <v>15.21</v>
       </c>
       <c r="L6" t="n">
-        <v>45920.7</v>
+        <v>43778.4</v>
       </c>
       <c r="M6" t="n">
-        <v>552</v>
+        <v>444</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>6667.5</v>
+        <v>6862.5</v>
       </c>
       <c r="P6" t="n">
-        <v>5535</v>
+        <v>4788</v>
       </c>
       <c r="Q6" t="n">
         <v>27615.39</v>
@@ -16223,7 +16223,7 @@
         <v>5971.5</v>
       </c>
       <c r="H7" t="n">
-        <v>569.4</v>
+        <v>481.8</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -16235,19 +16235,19 @@
         <v>19.78</v>
       </c>
       <c r="L7" t="n">
-        <v>41724</v>
+        <v>43146</v>
       </c>
       <c r="M7" t="n">
-        <v>1312.5</v>
+        <v>3328.5</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8599.5</v>
+        <v>9156</v>
       </c>
       <c r="P7" t="n">
-        <v>8355</v>
+        <v>7927.5</v>
       </c>
       <c r="Q7" t="n">
         <v>21109.18</v>
@@ -16276,7 +16276,7 @@
         <v>7078.5</v>
       </c>
       <c r="H8" t="n">
-        <v>51</v>
+        <v>357</v>
       </c>
       <c r="I8" t="n">
         <v>0.74</v>
@@ -16288,19 +16288,19 @@
         <v>2.94</v>
       </c>
       <c r="L8" t="n">
-        <v>23153.1</v>
+        <v>29734.8</v>
       </c>
       <c r="M8" t="n">
-        <v>1171.5</v>
+        <v>6616.5</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3955.5</v>
+        <v>5737.5</v>
       </c>
       <c r="P8" t="n">
-        <v>14888.4</v>
+        <v>15720.6</v>
       </c>
       <c r="Q8" t="n">
         <v>9957.4</v>
@@ -16341,19 +16341,19 @@
         <v>3.21</v>
       </c>
       <c r="L9" t="n">
-        <v>6828.3</v>
+        <v>17253</v>
       </c>
       <c r="M9" t="n">
-        <v>714</v>
+        <v>8820</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>214.5</v>
+        <v>841.5</v>
       </c>
       <c r="P9" t="n">
-        <v>18945</v>
+        <v>20880</v>
       </c>
       <c r="Q9" t="n">
         <v>830.51</v>
@@ -16394,10 +16394,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>3310.8</v>
+        <v>21653.7</v>
       </c>
       <c r="M10" t="n">
-        <v>204</v>
+        <v>8568</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>29733</v>
+        <v>47965.5</v>
       </c>
       <c r="Q10" t="n">
         <v>281.79</v>
@@ -16447,19 +16447,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>3540</v>
+        <v>25890</v>
       </c>
       <c r="M11" t="n">
-        <v>324</v>
+        <v>5697</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>25.5</v>
       </c>
       <c r="P11" t="n">
-        <v>22815</v>
+        <v>44280</v>
       </c>
       <c r="Q11" t="n">
         <v>258.8</v>
@@ -16488,7 +16488,7 @@
         <v>240</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -16500,10 +16500,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1530</v>
+        <v>15450</v>
       </c>
       <c r="M12" t="n">
-        <v>114</v>
+        <v>9234</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -16512,7 +16512,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>14430</v>
+        <v>25110</v>
       </c>
       <c r="Q12" t="n">
         <v>49.1</v>
@@ -16553,10 +16553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>450</v>
+        <v>5940</v>
       </c>
       <c r="M13" t="n">
-        <v>30</v>
+        <v>810</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -16565,7 +16565,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>12150</v>
+        <v>14700</v>
       </c>
       <c r="Q13" t="n">
         <v>20.31</v>
@@ -16606,10 +16606,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>180</v>
+        <v>5220</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -16618,7 +16618,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>14790</v>
+        <v>27000</v>
       </c>
       <c r="Q14" t="n">
         <v>20.42</v>
@@ -16659,10 +16659,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>270</v>
+        <v>2160</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -16671,7 +16671,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5850</v>
+        <v>16380</v>
       </c>
       <c r="Q15" t="n">
         <v>9.82</v>
@@ -16712,7 +16712,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>360</v>
+        <v>2400</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -16724,7 +16724,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2880</v>
+        <v>6690</v>
       </c>
       <c r="Q16" t="n">
         <v>5.36</v>
@@ -16765,7 +16765,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>450</v>
+        <v>660</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -16777,7 +16777,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>420</v>
+        <v>660</v>
       </c>
       <c r="Q17" t="n">
         <v>0.67</v>
@@ -16818,7 +16818,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>360</v>
+        <v>780</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -17409,7 +17409,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>26532360</v>
+        <v>27394200</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -17421,19 +17421,19 @@
         <v>1639347.67</v>
       </c>
       <c r="L5" t="n">
-        <v>10033632</v>
+        <v>9700236</v>
       </c>
       <c r="M5" t="n">
-        <v>104790</v>
+        <v>30450</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>364140</v>
+        <v>419475</v>
       </c>
       <c r="P5" t="n">
-        <v>55107</v>
+        <v>31161</v>
       </c>
       <c r="Q5" t="n">
         <v>1547616.35</v>
@@ -17462,7 +17462,7 @@
         <v>167832</v>
       </c>
       <c r="H6" t="n">
-        <v>17057250</v>
+        <v>19104120</v>
       </c>
       <c r="I6" t="n">
         <v>295414.7</v>
@@ -17474,19 +17474,19 @@
         <v>738536.76</v>
       </c>
       <c r="L6" t="n">
-        <v>8265726</v>
+        <v>7880112</v>
       </c>
       <c r="M6" t="n">
-        <v>193200</v>
+        <v>155400</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1133475</v>
+        <v>1166625</v>
       </c>
       <c r="P6" t="n">
-        <v>359775</v>
+        <v>311220</v>
       </c>
       <c r="Q6" t="n">
         <v>16569235.26</v>
@@ -17515,7 +17515,7 @@
         <v>322461</v>
       </c>
       <c r="H7" t="n">
-        <v>3245580</v>
+        <v>2746260</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -17527,19 +17527,19 @@
         <v>960340.5699999999</v>
       </c>
       <c r="L7" t="n">
-        <v>7510320</v>
+        <v>7766280</v>
       </c>
       <c r="M7" t="n">
-        <v>459375</v>
+        <v>1164975</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1461915</v>
+        <v>1556520</v>
       </c>
       <c r="P7" t="n">
-        <v>543075</v>
+        <v>515287.5</v>
       </c>
       <c r="Q7" t="n">
         <v>12665510.78</v>
@@ -17568,7 +17568,7 @@
         <v>382239</v>
       </c>
       <c r="H8" t="n">
-        <v>290700</v>
+        <v>2034900</v>
       </c>
       <c r="I8" t="n">
         <v>142948.86</v>
@@ -17580,19 +17580,19 @@
         <v>142948.86</v>
       </c>
       <c r="L8" t="n">
-        <v>4167558</v>
+        <v>5352264</v>
       </c>
       <c r="M8" t="n">
-        <v>410025</v>
+        <v>2315775</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>672435</v>
+        <v>975375</v>
       </c>
       <c r="P8" t="n">
-        <v>967746</v>
+        <v>1021839</v>
       </c>
       <c r="Q8" t="n">
         <v>5974439.04</v>
@@ -17633,19 +17633,19 @@
         <v>155961.87</v>
       </c>
       <c r="L9" t="n">
-        <v>1229094</v>
+        <v>3105540</v>
       </c>
       <c r="M9" t="n">
-        <v>249900</v>
+        <v>3087000</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>36465</v>
+        <v>143055</v>
       </c>
       <c r="P9" t="n">
-        <v>1231425</v>
+        <v>1357200</v>
       </c>
       <c r="Q9" t="n">
         <v>498305.61</v>
@@ -17686,10 +17686,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>595944</v>
+        <v>3897666</v>
       </c>
       <c r="M10" t="n">
-        <v>71400</v>
+        <v>2998800</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -17698,7 +17698,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1932645</v>
+        <v>3117757.5</v>
       </c>
       <c r="Q10" t="n">
         <v>169074</v>
@@ -17739,19 +17739,19 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>637200</v>
+        <v>4660200</v>
       </c>
       <c r="M11" t="n">
-        <v>113400</v>
+        <v>1993950</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4335</v>
       </c>
       <c r="P11" t="n">
-        <v>1482975</v>
+        <v>2878200</v>
       </c>
       <c r="Q11" t="n">
         <v>155280.24</v>
@@ -17780,7 +17780,7 @@
         <v>12960</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>513000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -17792,10 +17792,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>275400</v>
+        <v>2781000</v>
       </c>
       <c r="M12" t="n">
-        <v>39900</v>
+        <v>3231900</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -17804,7 +17804,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>937950</v>
+        <v>1632150</v>
       </c>
       <c r="Q12" t="n">
         <v>29462.4</v>
@@ -17845,10 +17845,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>81000</v>
+        <v>1069200</v>
       </c>
       <c r="M13" t="n">
-        <v>10500</v>
+        <v>283500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -17857,7 +17857,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>789750</v>
+        <v>955500</v>
       </c>
       <c r="Q13" t="n">
         <v>12186.72</v>
@@ -17898,10 +17898,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>32400</v>
+        <v>939600</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -17910,7 +17910,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>961350</v>
+        <v>1755000</v>
       </c>
       <c r="Q14" t="n">
         <v>12253.68</v>
@@ -17951,10 +17951,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>48600</v>
+        <v>388800</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>21000</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -17963,7 +17963,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>380250</v>
+        <v>1064700</v>
       </c>
       <c r="Q15" t="n">
         <v>5892.48</v>
@@ -18004,7 +18004,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>64800</v>
+        <v>432000</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>187200</v>
+        <v>434850</v>
       </c>
       <c r="Q16" t="n">
         <v>3214.08</v>
@@ -18057,7 +18057,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>81000</v>
+        <v>118800</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -18069,7 +18069,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>27300</v>
+        <v>42900</v>
       </c>
       <c r="Q17" t="n">
         <v>401.76</v>
@@ -18110,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>64800</v>
+        <v>140400</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -18648,7 +18648,7 @@
         <v>61800</v>
       </c>
       <c r="H4" t="n">
-        <v>4620</v>
+        <v>6180</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -18660,22 +18660,22 @@
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>225150</v>
+        <v>267540</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>2370</v>
+        <v>2610</v>
       </c>
       <c r="O4" t="n">
-        <v>48240</v>
+        <v>53340</v>
       </c>
       <c r="P4" t="n">
-        <v>5520</v>
+        <v>2130</v>
       </c>
       <c r="Q4" t="n">
-        <v>21190.12</v>
+        <v>242803.44</v>
       </c>
     </row>
     <row r="5">
@@ -18701,7 +18701,7 @@
         <v>13050</v>
       </c>
       <c r="H5" t="n">
-        <v>1140</v>
+        <v>1530</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -18713,22 +18713,22 @@
         <v>11</v>
       </c>
       <c r="L5" t="n">
-        <v>62640</v>
+        <v>81780</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1020</v>
+        <v>1860</v>
       </c>
       <c r="O5" t="n">
-        <v>21900</v>
+        <v>31110</v>
       </c>
       <c r="P5" t="n">
-        <v>4170</v>
+        <v>6600</v>
       </c>
       <c r="Q5" t="n">
-        <v>5343.49</v>
+        <v>61227.54</v>
       </c>
     </row>
     <row r="6">
@@ -18754,7 +18754,7 @@
         <v>1500</v>
       </c>
       <c r="H6" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -18766,22 +18766,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>10290</v>
+        <v>17760</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>30</v>
+        <v>420</v>
       </c>
       <c r="O6" t="n">
-        <v>3360</v>
+        <v>5460</v>
       </c>
       <c r="P6" t="n">
-        <v>2730</v>
+        <v>5610</v>
       </c>
       <c r="Q6" t="n">
-        <v>506.65</v>
+        <v>5805.36</v>
       </c>
     </row>
     <row r="7">
@@ -18819,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>630</v>
+        <v>2610</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -18828,13 +18828,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>60</v>
+        <v>330</v>
       </c>
       <c r="P7" t="n">
-        <v>3060</v>
+        <v>7530</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.56999999999999</v>
+        <v>991.98</v>
       </c>
     </row>
     <row r="8">
@@ -18872,7 +18872,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>180</v>
+        <v>480</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -18884,10 +18884,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>960</v>
+        <v>3600</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.05</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="9">
@@ -18925,22 +18925,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
+        <v>210</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
         <v>90</v>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>30</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.09</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="10">
@@ -19031,7 +19031,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -19993,7 +19993,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>410.4</v>
+        <v>550.8</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -20005,22 +20005,22 @@
         <v>3.64</v>
       </c>
       <c r="L5" t="n">
-        <v>13154.4</v>
+        <v>17173.8</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>10.2</v>
+        <v>18.6</v>
       </c>
       <c r="O5" t="n">
-        <v>1095</v>
+        <v>1555.5</v>
       </c>
       <c r="P5" t="n">
-        <v>83.40000000000001</v>
+        <v>132</v>
       </c>
       <c r="Q5" t="n">
-        <v>267.17</v>
+        <v>3061.38</v>
       </c>
     </row>
     <row r="6">
@@ -20046,7 +20046,7 @@
         <v>75</v>
       </c>
       <c r="H6" t="n">
-        <v>119.7</v>
+        <v>153.9</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -20058,22 +20058,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>3807.3</v>
+        <v>6571.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.5</v>
+        <v>21</v>
       </c>
       <c r="O6" t="n">
-        <v>840</v>
+        <v>1365</v>
       </c>
       <c r="P6" t="n">
-        <v>409.5</v>
+        <v>841.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>379.99</v>
+        <v>4354.02</v>
       </c>
     </row>
     <row r="7">
@@ -20111,7 +20111,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>378</v>
+        <v>1566</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -20120,13 +20120,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>21</v>
+        <v>115.5</v>
       </c>
       <c r="P7" t="n">
-        <v>765</v>
+        <v>1882.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>69.26000000000001</v>
+        <v>793.58</v>
       </c>
     </row>
     <row r="8">
@@ -20164,7 +20164,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>127.8</v>
+        <v>340.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -20176,10 +20176,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>364.8</v>
+        <v>1368</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.75</v>
+        <v>65.83</v>
       </c>
     </row>
     <row r="9">
@@ -20217,7 +20217,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>72.90000000000001</v>
+        <v>170.1</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -20229,10 +20229,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.08</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="10">
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2339280</v>
+        <v>3139560</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -21297,22 +21297,22 @@
         <v>176792.4</v>
       </c>
       <c r="L5" t="n">
-        <v>2367792</v>
+        <v>3091284</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1734</v>
+        <v>3162</v>
       </c>
       <c r="O5" t="n">
-        <v>186150</v>
+        <v>264435</v>
       </c>
       <c r="P5" t="n">
-        <v>5421</v>
+        <v>8580</v>
       </c>
       <c r="Q5" t="n">
-        <v>160304.83</v>
+        <v>1836826.2</v>
       </c>
     </row>
     <row r="6">
@@ -21338,7 +21338,7 @@
         <v>4050</v>
       </c>
       <c r="H6" t="n">
-        <v>682290</v>
+        <v>877230</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -21350,22 +21350,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>685314</v>
+        <v>1182816</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>255</v>
+        <v>3570</v>
       </c>
       <c r="O6" t="n">
-        <v>142800</v>
+        <v>232050</v>
       </c>
       <c r="P6" t="n">
-        <v>26617.5</v>
+        <v>54697.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>227992.32</v>
+        <v>2612412</v>
       </c>
     </row>
     <row r="7">
@@ -21403,7 +21403,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>68040</v>
+        <v>281880</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -21412,13 +21412,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3570</v>
+        <v>19635</v>
       </c>
       <c r="P7" t="n">
-        <v>49725</v>
+        <v>122362.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>41554.94</v>
+        <v>476150.4</v>
       </c>
     </row>
     <row r="8">
@@ -21456,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>23004</v>
+        <v>61344</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -21468,10 +21468,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>23712</v>
+        <v>88920</v>
       </c>
       <c r="Q8" t="n">
-        <v>3447.36</v>
+        <v>39501</v>
       </c>
     </row>
     <row r="9">
@@ -21509,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>13122</v>
+        <v>30618</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -21521,10 +21521,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="Q9" t="n">
-        <v>50.28</v>
+        <v>576.1799999999999</v>
       </c>
     </row>
     <row r="10">
@@ -21615,7 +21615,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>16200</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -22577,7 +22577,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>134631720</v>
+        <v>144419760</v>
       </c>
       <c r="I5" t="n">
         <v>128576.29</v>
@@ -22589,22 +22589,22 @@
         <v>4066225.11</v>
       </c>
       <c r="L5" t="n">
-        <v>35190288</v>
+        <v>36543150</v>
       </c>
       <c r="M5" t="n">
-        <v>320040</v>
+        <v>263760</v>
       </c>
       <c r="N5" t="n">
-        <v>35751</v>
+        <v>51867</v>
       </c>
       <c r="O5" t="n">
-        <v>1497105</v>
+        <v>1694985</v>
       </c>
       <c r="P5" t="n">
-        <v>93444</v>
+        <v>64038</v>
       </c>
       <c r="Q5" t="n">
-        <v>4303499.11</v>
+        <v>44596744.83</v>
       </c>
     </row>
     <row r="6">
@@ -22630,7 +22630,7 @@
         <v>657963</v>
       </c>
       <c r="H6" t="n">
-        <v>61893450</v>
+        <v>71055630</v>
       </c>
       <c r="I6" t="n">
         <v>393886.27</v>
@@ -22642,22 +22642,22 @@
         <v>2560260.77</v>
       </c>
       <c r="L6" t="n">
-        <v>37584378</v>
+        <v>39764196</v>
       </c>
       <c r="M6" t="n">
-        <v>619080</v>
+        <v>865200</v>
       </c>
       <c r="N6" t="n">
-        <v>42330</v>
+        <v>79305</v>
       </c>
       <c r="O6" t="n">
-        <v>4240650</v>
+        <v>4925325</v>
       </c>
       <c r="P6" t="n">
-        <v>674797.5</v>
+        <v>527670</v>
       </c>
       <c r="Q6" t="n">
-        <v>47358313.74</v>
+        <v>490769622.22</v>
       </c>
     </row>
     <row r="7">
@@ -22683,7 +22683,7 @@
         <v>1171503</v>
       </c>
       <c r="H7" t="n">
-        <v>24217020</v>
+        <v>28960560</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -22695,22 +22695,22 @@
         <v>2726128.06</v>
       </c>
       <c r="L7" t="n">
-        <v>36138960</v>
+        <v>39991320</v>
       </c>
       <c r="M7" t="n">
-        <v>1745625</v>
+        <v>3902850</v>
       </c>
       <c r="N7" t="n">
-        <v>8568</v>
+        <v>33915</v>
       </c>
       <c r="O7" t="n">
-        <v>4196535</v>
+        <v>4642785</v>
       </c>
       <c r="P7" t="n">
-        <v>1203637.5</v>
+        <v>1011562.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>38733467.33</v>
+        <v>401391173.52</v>
       </c>
     </row>
     <row r="8">
@@ -22736,7 +22736,7 @@
         <v>3957174</v>
       </c>
       <c r="H8" t="n">
-        <v>27761850</v>
+        <v>27035100</v>
       </c>
       <c r="I8" t="n">
         <v>428846.59</v>
@@ -22748,22 +22748,22 @@
         <v>1358014.21</v>
       </c>
       <c r="L8" t="n">
-        <v>30139074</v>
+        <v>33988410</v>
       </c>
       <c r="M8" t="n">
-        <v>1830675</v>
+        <v>6727875</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3060</v>
       </c>
       <c r="O8" t="n">
-        <v>2308770</v>
+        <v>3807405</v>
       </c>
       <c r="P8" t="n">
-        <v>2007369</v>
+        <v>1933269</v>
       </c>
       <c r="Q8" t="n">
-        <v>30166337.09</v>
+        <v>312610831.92</v>
       </c>
     </row>
     <row r="9">
@@ -22789,7 +22789,7 @@
         <v>3315816</v>
       </c>
       <c r="H9" t="n">
-        <v>18981000</v>
+        <v>24453000</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -22801,22 +22801,22 @@
         <v>1286685.44</v>
       </c>
       <c r="L9" t="n">
-        <v>27621810</v>
+        <v>33028074</v>
       </c>
       <c r="M9" t="n">
-        <v>1205400</v>
+        <v>7070700</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>813450</v>
+        <v>1887765</v>
       </c>
       <c r="P9" t="n">
-        <v>2640300</v>
+        <v>3097575</v>
       </c>
       <c r="Q9" t="n">
-        <v>19775432.06</v>
+        <v>204930888.68</v>
       </c>
     </row>
     <row r="10">
@@ -22842,7 +22842,7 @@
         <v>2199960</v>
       </c>
       <c r="H10" t="n">
-        <v>5301000</v>
+        <v>8379000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -22854,22 +22854,22 @@
         <v>337949.76</v>
       </c>
       <c r="L10" t="n">
-        <v>15706008</v>
+        <v>23462892</v>
       </c>
       <c r="M10" t="n">
-        <v>830025</v>
+        <v>8219925</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>446250</v>
+        <v>1363740</v>
       </c>
       <c r="P10" t="n">
-        <v>4014465</v>
+        <v>6260377.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>12857257.44</v>
+        <v>133238514.6</v>
       </c>
     </row>
     <row r="11">
@@ -22895,7 +22895,7 @@
         <v>1417500</v>
       </c>
       <c r="H11" t="n">
-        <v>4617000</v>
+        <v>6156000</v>
       </c>
       <c r="I11" t="n">
         <v>174510.26</v>
@@ -22907,22 +22907,22 @@
         <v>43627.57</v>
       </c>
       <c r="L11" t="n">
-        <v>8494200</v>
+        <v>15795000</v>
       </c>
       <c r="M11" t="n">
-        <v>897750</v>
+        <v>5084100</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>511530</v>
+        <v>671925</v>
       </c>
       <c r="P11" t="n">
-        <v>2818530</v>
+        <v>4766580</v>
       </c>
       <c r="Q11" t="n">
-        <v>7441197.84</v>
+        <v>77112413.09999999</v>
       </c>
     </row>
     <row r="12">
@@ -22948,7 +22948,7 @@
         <v>489240</v>
       </c>
       <c r="H12" t="n">
-        <v>855000</v>
+        <v>1539000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -22960,22 +22960,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>3045600</v>
+        <v>7835400</v>
       </c>
       <c r="M12" t="n">
-        <v>219450</v>
+        <v>6194475</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>66300</v>
+        <v>122400</v>
       </c>
       <c r="P12" t="n">
-        <v>2523300</v>
+        <v>4081350</v>
       </c>
       <c r="Q12" t="n">
-        <v>3656551.68</v>
+        <v>37892491.2</v>
       </c>
     </row>
     <row r="13">
@@ -23001,7 +23001,7 @@
         <v>126360</v>
       </c>
       <c r="H13" t="n">
-        <v>342000</v>
+        <v>855000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23013,22 +23013,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>972000</v>
+        <v>3358800</v>
       </c>
       <c r="M13" t="n">
-        <v>63000</v>
+        <v>1795500</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="P13" t="n">
-        <v>1823250</v>
+        <v>2098200</v>
       </c>
       <c r="Q13" t="n">
-        <v>1468700.64</v>
+        <v>15220002.6</v>
       </c>
     </row>
     <row r="14">
@@ -23054,7 +23054,7 @@
         <v>87480</v>
       </c>
       <c r="H14" t="n">
-        <v>513000</v>
+        <v>342000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23066,10 +23066,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>453600</v>
+        <v>2284200</v>
       </c>
       <c r="M14" t="n">
-        <v>105000</v>
+        <v>598500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -23078,10 +23078,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2704650</v>
+        <v>4005300</v>
       </c>
       <c r="Q14" t="n">
-        <v>1056227.04</v>
+        <v>10945578.6</v>
       </c>
     </row>
     <row r="15">
@@ -23107,7 +23107,7 @@
         <v>16200</v>
       </c>
       <c r="H15" t="n">
-        <v>171000</v>
+        <v>1026000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -23119,10 +23119,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>264600</v>
+        <v>1117800</v>
       </c>
       <c r="M15" t="n">
-        <v>10500</v>
+        <v>367500</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -23131,10 +23131,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1164150</v>
+        <v>2063100</v>
       </c>
       <c r="Q15" t="n">
-        <v>441601.2</v>
+        <v>4576270.5</v>
       </c>
     </row>
     <row r="16">
@@ -23172,10 +23172,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>264600</v>
+        <v>1063800</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>693000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23184,10 +23184,10 @@
         <v>5100</v>
       </c>
       <c r="P16" t="n">
-        <v>1121250</v>
+        <v>1366950</v>
       </c>
       <c r="Q16" t="n">
-        <v>210857.04</v>
+        <v>2185091.1</v>
       </c>
     </row>
     <row r="17">
@@ -23213,7 +23213,7 @@
         <v>19440</v>
       </c>
       <c r="H17" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23225,22 +23225,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>102600</v>
+        <v>540000</v>
       </c>
       <c r="M17" t="n">
-        <v>31500</v>
+        <v>157500</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5100</v>
+        <v>15300</v>
       </c>
       <c r="P17" t="n">
-        <v>1275300</v>
+        <v>2308800</v>
       </c>
       <c r="Q17" t="n">
-        <v>119188.8</v>
+        <v>1235142</v>
       </c>
     </row>
     <row r="18">
@@ -23278,10 +23278,10 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>64800</v>
+        <v>167400</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -23290,10 +23290,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>21450</v>
+        <v>109200</v>
       </c>
       <c r="Q18" t="n">
-        <v>12923.28</v>
+        <v>133922.7</v>
       </c>
     </row>
     <row r="19">
@@ -23346,7 +23346,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>4218.48</v>
+        <v>43715.7</v>
       </c>
     </row>
     <row r="20">
@@ -23399,7 +23399,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>66.95999999999999</v>
+        <v>693.9</v>
       </c>
     </row>
     <row r="21">
@@ -23816,7 +23816,7 @@
         <v>70140</v>
       </c>
       <c r="H4" t="n">
-        <v>20820</v>
+        <v>20370</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -23828,22 +23828,22 @@
         <v>72</v>
       </c>
       <c r="L4" t="n">
-        <v>217650</v>
+        <v>197520</v>
       </c>
       <c r="M4" t="n">
-        <v>32790</v>
+        <v>41310</v>
       </c>
       <c r="N4" t="n">
-        <v>18990</v>
+        <v>20340</v>
       </c>
       <c r="O4" t="n">
-        <v>15690</v>
+        <v>15360</v>
       </c>
       <c r="P4" t="n">
-        <v>3750</v>
+        <v>1320</v>
       </c>
       <c r="Q4" t="n">
-        <v>18914.93</v>
+        <v>185440.5</v>
       </c>
     </row>
     <row r="5">
@@ -23869,7 +23869,7 @@
         <v>97380</v>
       </c>
       <c r="H5" t="n">
-        <v>16710</v>
+        <v>19170</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -23881,22 +23881,22 @@
         <v>74</v>
       </c>
       <c r="L5" t="n">
-        <v>275010</v>
+        <v>277890</v>
       </c>
       <c r="M5" t="n">
-        <v>11100</v>
+        <v>22230</v>
       </c>
       <c r="N5" t="n">
-        <v>6480</v>
+        <v>11010</v>
       </c>
       <c r="O5" t="n">
-        <v>24360</v>
+        <v>25470</v>
       </c>
       <c r="P5" t="n">
-        <v>5310</v>
+        <v>3600</v>
       </c>
       <c r="Q5" t="n">
-        <v>31126.81</v>
+        <v>305164.8</v>
       </c>
     </row>
     <row r="6">
@@ -23922,7 +23922,7 @@
         <v>104370</v>
       </c>
       <c r="H6" t="n">
-        <v>2190</v>
+        <v>2700</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -23934,22 +23934,22 @@
         <v>58</v>
       </c>
       <c r="L6" t="n">
-        <v>258240</v>
+        <v>271050</v>
       </c>
       <c r="M6" t="n">
-        <v>5460</v>
+        <v>15750</v>
       </c>
       <c r="N6" t="n">
-        <v>1050</v>
+        <v>2190</v>
       </c>
       <c r="O6" t="n">
-        <v>22500</v>
+        <v>25560</v>
       </c>
       <c r="P6" t="n">
-        <v>6870</v>
+        <v>5640</v>
       </c>
       <c r="Q6" t="n">
-        <v>32250.44</v>
+        <v>316180.8</v>
       </c>
     </row>
     <row r="7">
@@ -23975,7 +23975,7 @@
         <v>76980</v>
       </c>
       <c r="H7" t="n">
-        <v>720</v>
+        <v>870</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -23987,22 +23987,22 @@
         <v>53</v>
       </c>
       <c r="L7" t="n">
-        <v>178560</v>
+        <v>199320</v>
       </c>
       <c r="M7" t="n">
-        <v>4440</v>
+        <v>13110</v>
       </c>
       <c r="N7" t="n">
-        <v>180</v>
+        <v>390</v>
       </c>
       <c r="O7" t="n">
-        <v>23370</v>
+        <v>22290</v>
       </c>
       <c r="P7" t="n">
-        <v>9690</v>
+        <v>6060</v>
       </c>
       <c r="Q7" t="n">
-        <v>30841.31</v>
+        <v>302365.8</v>
       </c>
     </row>
     <row r="8">
@@ -24028,7 +24028,7 @@
         <v>68670</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -24040,22 +24040,22 @@
         <v>31</v>
       </c>
       <c r="L8" t="n">
-        <v>116610</v>
+        <v>132330</v>
       </c>
       <c r="M8" t="n">
-        <v>3990</v>
+        <v>10560</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>16860</v>
+        <v>25170</v>
       </c>
       <c r="P8" t="n">
-        <v>14190</v>
+        <v>7320</v>
       </c>
       <c r="Q8" t="n">
-        <v>24478.1</v>
+        <v>239981.4</v>
       </c>
     </row>
     <row r="9">
@@ -24093,22 +24093,22 @@
         <v>21</v>
       </c>
       <c r="L9" t="n">
-        <v>84540</v>
+        <v>98760</v>
       </c>
       <c r="M9" t="n">
-        <v>3060</v>
+        <v>7320</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>7230</v>
+        <v>13950</v>
       </c>
       <c r="P9" t="n">
-        <v>14580</v>
+        <v>12090</v>
       </c>
       <c r="Q9" t="n">
-        <v>17395.37</v>
+        <v>170542.8</v>
       </c>
     </row>
     <row r="10">
@@ -24134,7 +24134,7 @@
         <v>15240</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -24146,22 +24146,22 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>42030</v>
+        <v>55830</v>
       </c>
       <c r="M10" t="n">
-        <v>1890</v>
+        <v>6630</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3750</v>
+        <v>11190</v>
       </c>
       <c r="P10" t="n">
-        <v>14550</v>
+        <v>13080</v>
       </c>
       <c r="Q10" t="n">
-        <v>10717.37</v>
+        <v>105072.3</v>
       </c>
     </row>
     <row r="11">
@@ -24199,22 +24199,22 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>19110</v>
+        <v>27150</v>
       </c>
       <c r="M11" t="n">
-        <v>2310</v>
+        <v>5100</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3540</v>
+        <v>4620</v>
       </c>
       <c r="P11" t="n">
-        <v>13410</v>
+        <v>12270</v>
       </c>
       <c r="Q11" t="n">
-        <v>6944.85</v>
+        <v>68086.8</v>
       </c>
     </row>
     <row r="12">
@@ -24252,22 +24252,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4470</v>
+        <v>10650</v>
       </c>
       <c r="M12" t="n">
-        <v>390</v>
+        <v>3120</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>390</v>
+        <v>720</v>
       </c>
       <c r="P12" t="n">
-        <v>16140</v>
+        <v>19860</v>
       </c>
       <c r="Q12" t="n">
-        <v>3017.56</v>
+        <v>29583.9</v>
       </c>
     </row>
     <row r="13">
@@ -24305,22 +24305,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1320</v>
+        <v>4560</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>1080</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P13" t="n">
-        <v>13020</v>
+        <v>11250</v>
       </c>
       <c r="Q13" t="n">
-        <v>862.55</v>
+        <v>8456.4</v>
       </c>
     </row>
     <row r="14">
@@ -24358,10 +24358,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>510</v>
+        <v>3720</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -24370,10 +24370,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>25590</v>
+        <v>32520</v>
       </c>
       <c r="Q14" t="n">
-        <v>366.47</v>
+        <v>3592.8</v>
       </c>
     </row>
     <row r="15">
@@ -24411,7 +24411,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>1710</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
@@ -24423,10 +24423,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12060</v>
+        <v>15360</v>
       </c>
       <c r="Q15" t="n">
-        <v>149.54</v>
+        <v>1466.1</v>
       </c>
     </row>
     <row r="16">
@@ -24464,10 +24464,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>1140</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -24476,10 +24476,10 @@
         <v>30</v>
       </c>
       <c r="P16" t="n">
-        <v>14400</v>
+        <v>14370</v>
       </c>
       <c r="Q16" t="n">
-        <v>115.3</v>
+        <v>1130.4</v>
       </c>
     </row>
     <row r="17">
@@ -24517,22 +24517,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>1470</v>
+      </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>90</v>
       </c>
-      <c r="M17" t="n">
-        <v>90</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>30</v>
-      </c>
       <c r="P17" t="n">
-        <v>19200</v>
+        <v>34860</v>
       </c>
       <c r="Q17" t="n">
-        <v>109.06</v>
+        <v>1069.2</v>
       </c>
     </row>
     <row r="18">
@@ -24573,7 +24573,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -24582,10 +24582,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>330</v>
+        <v>1680</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.74</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="19">
@@ -24638,7 +24638,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.32</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="20">
@@ -24691,7 +24691,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -25161,7 +25161,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>6015.6</v>
+        <v>6901.2</v>
       </c>
       <c r="I5" t="n">
         <v>0.33</v>
@@ -25173,22 +25173,22 @@
         <v>24.49</v>
       </c>
       <c r="L5" t="n">
-        <v>57752.1</v>
+        <v>58356.9</v>
       </c>
       <c r="M5" t="n">
-        <v>222</v>
+        <v>444.6</v>
       </c>
       <c r="N5" t="n">
-        <v>64.8</v>
+        <v>110.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1218</v>
+        <v>1273.5</v>
       </c>
       <c r="P5" t="n">
-        <v>106.2</v>
+        <v>72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1556.34</v>
+        <v>15258.24</v>
       </c>
     </row>
     <row r="6">
@@ -25214,7 +25214,7 @@
         <v>5218.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1248.3</v>
+        <v>1539</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -25226,22 +25226,22 @@
         <v>29.41</v>
       </c>
       <c r="L6" t="n">
-        <v>95548.8</v>
+        <v>100288.5</v>
       </c>
       <c r="M6" t="n">
-        <v>436.8</v>
+        <v>1260</v>
       </c>
       <c r="N6" t="n">
-        <v>52.5</v>
+        <v>109.5</v>
       </c>
       <c r="O6" t="n">
-        <v>5625</v>
+        <v>6390</v>
       </c>
       <c r="P6" t="n">
-        <v>1030.5</v>
+        <v>846</v>
       </c>
       <c r="Q6" t="n">
-        <v>24187.83</v>
+        <v>237135.6</v>
       </c>
     </row>
     <row r="7">
@@ -25267,7 +25267,7 @@
         <v>11547</v>
       </c>
       <c r="H7" t="n">
-        <v>525.6</v>
+        <v>635.1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -25279,22 +25279,22 @@
         <v>33.81</v>
       </c>
       <c r="L7" t="n">
-        <v>107136</v>
+        <v>119592</v>
       </c>
       <c r="M7" t="n">
-        <v>1554</v>
+        <v>4588.5</v>
       </c>
       <c r="N7" t="n">
-        <v>12.6</v>
+        <v>27.3</v>
       </c>
       <c r="O7" t="n">
-        <v>8179.5</v>
+        <v>7801.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2422.5</v>
+        <v>1515</v>
       </c>
       <c r="Q7" t="n">
-        <v>24673.05</v>
+        <v>241892.64</v>
       </c>
     </row>
     <row r="8">
@@ -25320,7 +25320,7 @@
         <v>44635.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>76.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -25332,22 +25332,22 @@
         <v>22.82</v>
       </c>
       <c r="L8" t="n">
-        <v>82793.10000000001</v>
+        <v>93954.3</v>
       </c>
       <c r="M8" t="n">
-        <v>2194.5</v>
+        <v>5808</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>7587</v>
+        <v>11326.5</v>
       </c>
       <c r="P8" t="n">
-        <v>5392.2</v>
+        <v>2781.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>23254.2</v>
+        <v>227982.33</v>
       </c>
     </row>
     <row r="9">
@@ -25385,22 +25385,22 @@
         <v>16.86</v>
       </c>
       <c r="L9" t="n">
-        <v>68477.39999999999</v>
+        <v>79995.60000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>2142</v>
+        <v>5124</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3976.5</v>
+        <v>7672.5</v>
       </c>
       <c r="P9" t="n">
-        <v>7290</v>
+        <v>6045</v>
       </c>
       <c r="Q9" t="n">
-        <v>16873.5</v>
+        <v>165426.52</v>
       </c>
     </row>
     <row r="10">
@@ -25426,7 +25426,7 @@
         <v>15240</v>
       </c>
       <c r="H10" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -25438,22 +25438,22 @@
         <v>4.35</v>
       </c>
       <c r="L10" t="n">
-        <v>37406.7</v>
+        <v>49688.7</v>
       </c>
       <c r="M10" t="n">
-        <v>1606.5</v>
+        <v>5635.5</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2625</v>
+        <v>7833</v>
       </c>
       <c r="P10" t="n">
-        <v>12367.5</v>
+        <v>11118</v>
       </c>
       <c r="Q10" t="n">
-        <v>10717.37</v>
+        <v>105072.3</v>
       </c>
     </row>
     <row r="11">
@@ -25491,22 +25491,22 @@
         <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>19110</v>
+        <v>27150</v>
       </c>
       <c r="M11" t="n">
-        <v>2079</v>
+        <v>4590</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3009</v>
+        <v>3927</v>
       </c>
       <c r="P11" t="n">
-        <v>12069</v>
+        <v>11043</v>
       </c>
       <c r="Q11" t="n">
-        <v>6944.85</v>
+        <v>68086.8</v>
       </c>
     </row>
     <row r="12">
@@ -25544,22 +25544,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4470</v>
+        <v>10650</v>
       </c>
       <c r="M12" t="n">
-        <v>370.5</v>
+        <v>2964</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>390</v>
+        <v>720</v>
       </c>
       <c r="P12" t="n">
-        <v>16140</v>
+        <v>19860</v>
       </c>
       <c r="Q12" t="n">
-        <v>3017.56</v>
+        <v>29583.9</v>
       </c>
     </row>
     <row r="13">
@@ -25597,22 +25597,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1320</v>
+        <v>4560</v>
       </c>
       <c r="M13" t="n">
-        <v>90</v>
+        <v>1080</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="P13" t="n">
-        <v>13020</v>
+        <v>11250</v>
       </c>
       <c r="Q13" t="n">
-        <v>862.55</v>
+        <v>8456.4</v>
       </c>
     </row>
     <row r="14">
@@ -25650,10 +25650,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>510</v>
+        <v>3720</v>
       </c>
       <c r="M14" t="n">
-        <v>120</v>
+        <v>630</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>25590</v>
+        <v>32520</v>
       </c>
       <c r="Q14" t="n">
-        <v>366.47</v>
+        <v>3592.8</v>
       </c>
     </row>
     <row r="15">
@@ -25703,7 +25703,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>300</v>
+        <v>1710</v>
       </c>
       <c r="M15" t="n">
         <v>30</v>
@@ -25715,10 +25715,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>12060</v>
+        <v>15360</v>
       </c>
       <c r="Q15" t="n">
-        <v>149.54</v>
+        <v>1466.1</v>
       </c>
     </row>
     <row r="16">
@@ -25756,10 +25756,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>60</v>
+        <v>1140</v>
       </c>
       <c r="M16" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -25768,10 +25768,10 @@
         <v>30</v>
       </c>
       <c r="P16" t="n">
-        <v>14400</v>
+        <v>14370</v>
       </c>
       <c r="Q16" t="n">
-        <v>115.3</v>
+        <v>1130.4</v>
       </c>
     </row>
     <row r="17">
@@ -25809,22 +25809,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
+        <v>1470</v>
+      </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
         <v>90</v>
       </c>
-      <c r="M17" t="n">
-        <v>90</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>30</v>
-      </c>
       <c r="P17" t="n">
-        <v>19200</v>
+        <v>34860</v>
       </c>
       <c r="Q17" t="n">
-        <v>109.06</v>
+        <v>1069.2</v>
       </c>
     </row>
     <row r="18">
@@ -25865,7 +25865,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -25874,10 +25874,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>330</v>
+        <v>1680</v>
       </c>
       <c r="Q18" t="n">
-        <v>10.74</v>
+        <v>105.3</v>
       </c>
     </row>
     <row r="19">
@@ -25930,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.32</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="20">
@@ -25983,7 +25983,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>34288920</v>
+        <v>39336840</v>
       </c>
       <c r="I5" t="n">
         <v>64288.14</v>
@@ -26465,22 +26465,22 @@
         <v>1189330.66</v>
       </c>
       <c r="L5" t="n">
-        <v>10395378</v>
+        <v>10504242</v>
       </c>
       <c r="M5" t="n">
-        <v>77700</v>
+        <v>155610</v>
       </c>
       <c r="N5" t="n">
-        <v>11016</v>
+        <v>18717</v>
       </c>
       <c r="O5" t="n">
-        <v>207060</v>
+        <v>216495</v>
       </c>
       <c r="P5" t="n">
-        <v>6903</v>
+        <v>4680</v>
       </c>
       <c r="Q5" t="n">
-        <v>933804.29</v>
+        <v>9154944</v>
       </c>
     </row>
     <row r="6">
@@ -26506,7 +26506,7 @@
         <v>281799</v>
       </c>
       <c r="H6" t="n">
-        <v>7115310</v>
+        <v>8772300</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -26518,22 +26518,22 @@
         <v>1427837.74</v>
       </c>
       <c r="L6" t="n">
-        <v>17198784</v>
+        <v>18051930</v>
       </c>
       <c r="M6" t="n">
-        <v>152880</v>
+        <v>441000</v>
       </c>
       <c r="N6" t="n">
-        <v>8925</v>
+        <v>18615</v>
       </c>
       <c r="O6" t="n">
-        <v>956250</v>
+        <v>1086300</v>
       </c>
       <c r="P6" t="n">
-        <v>66982.5</v>
+        <v>54990</v>
       </c>
       <c r="Q6" t="n">
-        <v>14512698.72</v>
+        <v>142281360</v>
       </c>
     </row>
     <row r="7">
@@ -26559,7 +26559,7 @@
         <v>623538</v>
       </c>
       <c r="H7" t="n">
-        <v>2995920</v>
+        <v>3620070</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -26571,22 +26571,22 @@
         <v>1641872.58</v>
       </c>
       <c r="L7" t="n">
-        <v>19284480</v>
+        <v>21526560</v>
       </c>
       <c r="M7" t="n">
-        <v>543900</v>
+        <v>1605975</v>
       </c>
       <c r="N7" t="n">
-        <v>2142</v>
+        <v>4641</v>
       </c>
       <c r="O7" t="n">
-        <v>1390515</v>
+        <v>1326255</v>
       </c>
       <c r="P7" t="n">
-        <v>157462.5</v>
+        <v>98475</v>
       </c>
       <c r="Q7" t="n">
-        <v>14803829.57</v>
+        <v>145135584</v>
       </c>
     </row>
     <row r="8">
@@ -26612,7 +26612,7 @@
         <v>2410317</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>436050</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -26624,22 +26624,22 @@
         <v>1107853.7</v>
       </c>
       <c r="L8" t="n">
-        <v>14902758</v>
+        <v>16911774</v>
       </c>
       <c r="M8" t="n">
-        <v>768075</v>
+        <v>2032800</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1289790</v>
+        <v>1925505</v>
       </c>
       <c r="P8" t="n">
-        <v>350493</v>
+        <v>180804</v>
       </c>
       <c r="Q8" t="n">
-        <v>13952518.6</v>
+        <v>136789398</v>
       </c>
     </row>
     <row r="9">
@@ -26677,22 +26677,22 @@
         <v>818799.83</v>
       </c>
       <c r="L9" t="n">
-        <v>12325932</v>
+        <v>14399208</v>
       </c>
       <c r="M9" t="n">
-        <v>749700</v>
+        <v>1793400</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>676005</v>
+        <v>1304325</v>
       </c>
       <c r="P9" t="n">
-        <v>473850</v>
+        <v>392925</v>
       </c>
       <c r="Q9" t="n">
-        <v>10124102.78</v>
+        <v>99255909.59999999</v>
       </c>
     </row>
     <row r="10">
@@ -26718,7 +26718,7 @@
         <v>822960</v>
       </c>
       <c r="H10" t="n">
-        <v>171000</v>
+        <v>513000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -26730,22 +26730,22 @@
         <v>211218.6</v>
       </c>
       <c r="L10" t="n">
-        <v>6733206</v>
+        <v>8943966</v>
       </c>
       <c r="M10" t="n">
-        <v>562275</v>
+        <v>1972425</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>446250</v>
+        <v>1331610</v>
       </c>
       <c r="P10" t="n">
-        <v>803887.5</v>
+        <v>722670</v>
       </c>
       <c r="Q10" t="n">
-        <v>6430424.76</v>
+        <v>63043380</v>
       </c>
     </row>
     <row r="11">
@@ -26783,22 +26783,22 @@
         <v>43627.57</v>
       </c>
       <c r="L11" t="n">
-        <v>3439800</v>
+        <v>4887000</v>
       </c>
       <c r="M11" t="n">
-        <v>727650</v>
+        <v>1606500</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>511530</v>
+        <v>667590</v>
       </c>
       <c r="P11" t="n">
-        <v>784485</v>
+        <v>717795</v>
       </c>
       <c r="Q11" t="n">
-        <v>4166912.16</v>
+        <v>40852080</v>
       </c>
     </row>
     <row r="12">
@@ -26836,22 +26836,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>804600</v>
+        <v>1917000</v>
       </c>
       <c r="M12" t="n">
-        <v>129675</v>
+        <v>1037400</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>66300</v>
+        <v>122400</v>
       </c>
       <c r="P12" t="n">
-        <v>1049100</v>
+        <v>1290900</v>
       </c>
       <c r="Q12" t="n">
-        <v>1810534.68</v>
+        <v>17750340</v>
       </c>
     </row>
     <row r="13">
@@ -26889,22 +26889,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>237600</v>
+        <v>820800</v>
       </c>
       <c r="M13" t="n">
-        <v>31500</v>
+        <v>378000</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>20400</v>
       </c>
       <c r="P13" t="n">
-        <v>846300</v>
+        <v>731250</v>
       </c>
       <c r="Q13" t="n">
-        <v>517531.68</v>
+        <v>5073840</v>
       </c>
     </row>
     <row r="14">
@@ -26942,10 +26942,10 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>91800</v>
+        <v>669600</v>
       </c>
       <c r="M14" t="n">
-        <v>42000</v>
+        <v>220500</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -26954,10 +26954,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1663350</v>
+        <v>2113800</v>
       </c>
       <c r="Q14" t="n">
-        <v>219879.36</v>
+        <v>2155680</v>
       </c>
     </row>
     <row r="15">
@@ -26995,7 +26995,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>54000</v>
+        <v>307800</v>
       </c>
       <c r="M15" t="n">
         <v>10500</v>
@@ -27007,10 +27007,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>783900</v>
+        <v>998400</v>
       </c>
       <c r="Q15" t="n">
-        <v>89725.32000000001</v>
+        <v>879660</v>
       </c>
     </row>
     <row r="16">
@@ -27048,10 +27048,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10800</v>
+        <v>205200</v>
       </c>
       <c r="M16" t="n">
-        <v>21000</v>
+        <v>42000</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -27060,10 +27060,10 @@
         <v>5100</v>
       </c>
       <c r="P16" t="n">
-        <v>936000</v>
+        <v>934050</v>
       </c>
       <c r="Q16" t="n">
-        <v>69180.48</v>
+        <v>678240</v>
       </c>
     </row>
     <row r="17">
@@ -27101,22 +27101,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>16200</v>
+        <v>264600</v>
       </c>
       <c r="M17" t="n">
-        <v>31500</v>
+        <v>21000</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>5100</v>
+        <v>15300</v>
       </c>
       <c r="P17" t="n">
-        <v>1248000</v>
+        <v>2265900</v>
       </c>
       <c r="Q17" t="n">
-        <v>65435.04</v>
+        <v>641520</v>
       </c>
     </row>
     <row r="18">
@@ -27157,7 +27157,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
@@ -27166,10 +27166,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>21450</v>
+        <v>109200</v>
       </c>
       <c r="Q18" t="n">
-        <v>6444.36</v>
+        <v>63180</v>
       </c>
     </row>
     <row r="19">
@@ -27222,7 +27222,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3194.64</v>
+        <v>31320</v>
       </c>
     </row>
     <row r="20">
@@ -27275,7 +27275,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>55.08</v>
+        <v>540</v>
       </c>
     </row>
     <row r="21">
@@ -27692,7 +27692,7 @@
         <v>130320</v>
       </c>
       <c r="H4" t="n">
-        <v>27900</v>
+        <v>29550</v>
       </c>
       <c r="I4" t="n">
         <v>2</v>
@@ -27704,7 +27704,7 @@
         <v>71</v>
       </c>
       <c r="L4" t="n">
-        <v>357900</v>
+        <v>407790</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27713,13 +27713,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>77400</v>
+        <v>79920</v>
       </c>
       <c r="P4" t="n">
-        <v>630</v>
+        <v>60</v>
       </c>
       <c r="Q4" t="n">
-        <v>38131.5</v>
+        <v>530944.92</v>
       </c>
     </row>
     <row r="5">
@@ -27745,7 +27745,7 @@
         <v>75300</v>
       </c>
       <c r="H5" t="n">
-        <v>25680</v>
+        <v>26250</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27757,7 +27757,7 @@
         <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>166560</v>
+        <v>179760</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -27766,13 +27766,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>47670</v>
+        <v>51030</v>
       </c>
       <c r="P5" t="n">
-        <v>2340</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>15143.38</v>
+        <v>210857.13</v>
       </c>
     </row>
     <row r="6">
@@ -27798,7 +27798,7 @@
         <v>28200</v>
       </c>
       <c r="H6" t="n">
-        <v>4380</v>
+        <v>5130</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -27810,7 +27810,7 @@
         <v>7</v>
       </c>
       <c r="L6" t="n">
-        <v>61590</v>
+        <v>69450</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -27819,13 +27819,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>22890</v>
+        <v>28920</v>
       </c>
       <c r="P6" t="n">
-        <v>2580</v>
+        <v>150</v>
       </c>
       <c r="Q6" t="n">
-        <v>5742.25</v>
+        <v>79955.37</v>
       </c>
     </row>
     <row r="7">
@@ -27851,7 +27851,7 @@
         <v>900</v>
       </c>
       <c r="H7" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -27863,7 +27863,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>8640</v>
+        <v>11190</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -27872,13 +27872,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>8070</v>
+        <v>11580</v>
       </c>
       <c r="P7" t="n">
-        <v>4500</v>
+        <v>510</v>
       </c>
       <c r="Q7" t="n">
-        <v>347.61</v>
+        <v>4840.11</v>
       </c>
     </row>
     <row r="8">
@@ -27904,7 +27904,7 @@
         <v>300</v>
       </c>
       <c r="H8" t="n">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -27916,7 +27916,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2850</v>
+        <v>4500</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -27925,13 +27925,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3030</v>
+        <v>9420</v>
       </c>
       <c r="P8" t="n">
-        <v>5250</v>
+        <v>2400</v>
       </c>
       <c r="Q8" t="n">
-        <v>60.72</v>
+        <v>845.46</v>
       </c>
     </row>
     <row r="9">
@@ -27969,7 +27969,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>630</v>
+        <v>2280</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -27978,13 +27978,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>690</v>
+        <v>3780</v>
       </c>
       <c r="P9" t="n">
-        <v>6300</v>
+        <v>8670</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.9</v>
+        <v>304.92</v>
       </c>
     </row>
     <row r="10">
@@ -28010,7 +28010,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -28022,22 +28022,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
+        <v>1830</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>270</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
       <c r="P10" t="n">
-        <v>3090</v>
+        <v>7620</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.76</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="11">
@@ -28063,7 +28063,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -28075,7 +28075,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -28087,10 +28087,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2070</v>
+        <v>6150</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.92</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="12">
@@ -28128,7 +28128,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -28140,10 +28140,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>540</v>
+        <v>2160</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="13">
@@ -28181,7 +28181,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28193,7 +28193,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -29037,7 +29037,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9244.799999999999</v>
+        <v>9450</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -29049,7 +29049,7 @@
         <v>12.58</v>
       </c>
       <c r="L5" t="n">
-        <v>34977.6</v>
+        <v>37749.6</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -29058,13 +29058,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2383.5</v>
+        <v>2551.5</v>
       </c>
       <c r="P5" t="n">
-        <v>46.8</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>757.17</v>
+        <v>10542.86</v>
       </c>
     </row>
     <row r="6">
@@ -29090,7 +29090,7 @@
         <v>1410</v>
       </c>
       <c r="H6" t="n">
-        <v>2496.6</v>
+        <v>2924.1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -29102,7 +29102,7 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>22788.3</v>
+        <v>25696.5</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -29111,13 +29111,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5722.5</v>
+        <v>7230</v>
       </c>
       <c r="P6" t="n">
-        <v>387</v>
+        <v>22.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>4306.69</v>
+        <v>59966.53</v>
       </c>
     </row>
     <row r="7">
@@ -29143,7 +29143,7 @@
         <v>135</v>
       </c>
       <c r="H7" t="n">
-        <v>438</v>
+        <v>657</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -29155,7 +29155,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5184</v>
+        <v>6714</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -29164,13 +29164,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2824.5</v>
+        <v>4053</v>
       </c>
       <c r="P7" t="n">
-        <v>1125</v>
+        <v>127.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>278.09</v>
+        <v>3872.09</v>
       </c>
     </row>
     <row r="8">
@@ -29196,7 +29196,7 @@
         <v>195</v>
       </c>
       <c r="H8" t="n">
-        <v>229.5</v>
+        <v>280.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -29208,7 +29208,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2023.5</v>
+        <v>3195</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -29217,13 +29217,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>1363.5</v>
+        <v>4239</v>
       </c>
       <c r="P8" t="n">
-        <v>1995</v>
+        <v>912</v>
       </c>
       <c r="Q8" t="n">
-        <v>57.68</v>
+        <v>803.1900000000001</v>
       </c>
     </row>
     <row r="9">
@@ -29261,7 +29261,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>510.3</v>
+        <v>1846.8</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -29270,13 +29270,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>379.5</v>
+        <v>2079</v>
       </c>
       <c r="P9" t="n">
-        <v>3150</v>
+        <v>4335</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.24</v>
+        <v>295.77</v>
       </c>
     </row>
     <row r="10">
@@ -29302,7 +29302,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -29314,7 +29314,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>240.3</v>
+        <v>1628.7</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -29323,13 +29323,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>189</v>
       </c>
       <c r="P10" t="n">
-        <v>2626.5</v>
+        <v>6477</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.76</v>
+        <v>80.19</v>
       </c>
     </row>
     <row r="11">
@@ -29355,7 +29355,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -29367,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>30</v>
+        <v>1230</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -29379,10 +29379,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1863</v>
+        <v>5535</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.92</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="12">
@@ -29420,7 +29420,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -29432,10 +29432,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>540</v>
+        <v>2160</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.21</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="13">
@@ -29473,7 +29473,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -29485,7 +29485,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -30329,7 +30329,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>52695360</v>
+        <v>53865000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -30341,7 +30341,7 @@
         <v>610737.37</v>
       </c>
       <c r="L5" t="n">
-        <v>6295968</v>
+        <v>6794928</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -30350,13 +30350,13 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>405195</v>
+        <v>433755</v>
       </c>
       <c r="P5" t="n">
-        <v>3042</v>
+        <v>39</v>
       </c>
       <c r="Q5" t="n">
-        <v>454301.27</v>
+        <v>6325713.9</v>
       </c>
     </row>
     <row r="6">
@@ -30382,7 +30382,7 @@
         <v>76140</v>
       </c>
       <c r="H6" t="n">
-        <v>14230620</v>
+        <v>16667370</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -30394,7 +30394,7 @@
         <v>172325.24</v>
       </c>
       <c r="L6" t="n">
-        <v>4101894</v>
+        <v>4625370</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -30403,13 +30403,13 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>972825</v>
+        <v>1229100</v>
       </c>
       <c r="P6" t="n">
-        <v>25155</v>
+        <v>1462.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2584012.19</v>
+        <v>35979916.5</v>
       </c>
     </row>
     <row r="7">
@@ -30435,7 +30435,7 @@
         <v>7290</v>
       </c>
       <c r="H7" t="n">
-        <v>2496600</v>
+        <v>3744900</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -30447,7 +30447,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>933120</v>
+        <v>1208520</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -30456,13 +30456,13 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>480165</v>
+        <v>689010</v>
       </c>
       <c r="P7" t="n">
-        <v>73125</v>
+        <v>8287.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>166851.79</v>
+        <v>2323252.8</v>
       </c>
     </row>
     <row r="8">
@@ -30488,7 +30488,7 @@
         <v>10530</v>
       </c>
       <c r="H8" t="n">
-        <v>1308150</v>
+        <v>1598850</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>364230</v>
+        <v>575100</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -30509,13 +30509,13 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>231795</v>
+        <v>720630</v>
       </c>
       <c r="P8" t="n">
-        <v>129675</v>
+        <v>59280</v>
       </c>
       <c r="Q8" t="n">
-        <v>34610.06</v>
+        <v>481912.2</v>
       </c>
     </row>
     <row r="9">
@@ -30553,7 +30553,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>91854</v>
+        <v>332424</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -30562,13 +30562,13 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>64515</v>
+        <v>353430</v>
       </c>
       <c r="P9" t="n">
-        <v>204750</v>
+        <v>281775</v>
       </c>
       <c r="Q9" t="n">
-        <v>12745.1</v>
+        <v>177463.44</v>
       </c>
     </row>
     <row r="10">
@@ -30594,7 +30594,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1710000</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -30606,7 +30606,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>43254</v>
+        <v>293166</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -30615,13 +30615,13 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>32130</v>
       </c>
       <c r="P10" t="n">
-        <v>170722.5</v>
+        <v>421005</v>
       </c>
       <c r="Q10" t="n">
-        <v>3455.46</v>
+        <v>48114</v>
       </c>
     </row>
     <row r="11">
@@ -30647,7 +30647,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>171000</v>
+        <v>855000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -30659,7 +30659,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5400</v>
+        <v>221400</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -30671,10 +30671,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>121095</v>
+        <v>359775</v>
       </c>
       <c r="Q11" t="n">
-        <v>554.58</v>
+        <v>7722</v>
       </c>
     </row>
     <row r="12">
@@ -30712,7 +30712,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>97200</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -30724,10 +30724,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>35100</v>
+        <v>140400</v>
       </c>
       <c r="Q12" t="n">
-        <v>127.98</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="13">
@@ -30765,7 +30765,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>16200</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -30777,7 +30777,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3900</v>
+        <v>27300</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
